--- a/server/BIOMETRICEMPLOYEE.xlsx
+++ b/server/BIOMETRICEMPLOYEE.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ML Cabigas\dmbbhr\server\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F413E040-B4EE-42C8-9F8E-D19C394D1BE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="168">
   <si>
     <t>ID</t>
   </si>
@@ -488,27 +497,81 @@
   </si>
   <si>
     <t>Abalo, Oliver</t>
+  </si>
+  <si>
+    <t>CONTRACT DATE</t>
+  </si>
+  <si>
+    <t>March 03,2026</t>
+  </si>
+  <si>
+    <t>March 17,2017</t>
+  </si>
+  <si>
+    <t>January 09,2025</t>
+  </si>
+  <si>
+    <t>July 7,2021</t>
+  </si>
+  <si>
+    <t>October 27, 2014</t>
+  </si>
+  <si>
+    <t>August 14,2023</t>
+  </si>
+  <si>
+    <t>March 26,2026</t>
+  </si>
+  <si>
+    <t>February 11,2019</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -516,35 +579,48 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -552,7 +628,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -742,22 +818,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E148"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="20.88"/>
-    <col customWidth="1" min="3" max="3" width="14.38"/>
-    <col customWidth="1" min="4" max="4" width="19.63"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -770,10 +850,13 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="E1" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>25069.0</v>
+        <v>25069</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -782,9 +865,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>50008.0</v>
+        <v>50008</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -793,9 +876,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>50046.0</v>
+        <v>50046</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -804,9 +887,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>50048.0</v>
+        <v>50048</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
@@ -815,9 +898,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>50071.0</v>
+        <v>50071</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
@@ -826,9 +909,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>50113.0</v>
+        <v>50113</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -837,9 +920,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>50190.0</v>
+        <v>50190</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>11</v>
@@ -848,9 +931,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>25041.0</v>
+        <v>25041</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -859,9 +942,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>25065.0</v>
+        <v>25065</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -870,9 +953,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>50329.0</v>
+        <v>50329</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -881,9 +964,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>50336.0</v>
+        <v>50336</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
@@ -892,9 +975,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>58337.0</v>
+        <v>58337</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>18</v>
@@ -903,9 +986,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>25001.0</v>
+        <v>25001</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>19</v>
@@ -914,9 +997,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>25003.0</v>
+        <v>25003</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>21</v>
@@ -925,9 +1008,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>25021.0</v>
+        <v>25021</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>22</v>
@@ -936,9 +1019,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>25024.0</v>
+        <v>25024</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>23</v>
@@ -947,9 +1030,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>25025.0</v>
+        <v>25025</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>24</v>
@@ -958,9 +1041,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>25027.0</v>
+        <v>25027</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>25</v>
@@ -969,9 +1052,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>25032.0</v>
+        <v>25032</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>26</v>
@@ -980,9 +1063,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>25034.0</v>
+        <v>25034</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
@@ -991,9 +1074,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>25036.0</v>
+        <v>25036</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
@@ -1002,9 +1085,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>25037.0</v>
+        <v>25037</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
@@ -1013,9 +1096,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>25042.0</v>
+        <v>25042</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>30</v>
@@ -1024,9 +1107,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>25043.0</v>
+        <v>25043</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>31</v>
@@ -1035,9 +1118,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>25044.0</v>
+        <v>25044</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>32</v>
@@ -1046,9 +1129,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>25045.0</v>
+        <v>25045</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>33</v>
@@ -1057,9 +1140,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>25046.0</v>
+        <v>25046</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>34</v>
@@ -1068,9 +1151,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>25050.0</v>
+        <v>25050</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>35</v>
@@ -1079,9 +1162,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>25054.0</v>
+        <v>25054</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>36</v>
@@ -1090,9 +1173,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>25058.0</v>
+        <v>25058</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>37</v>
@@ -1101,9 +1184,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>25059.0</v>
+        <v>25059</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>38</v>
@@ -1112,9 +1195,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>25062.0</v>
+        <v>25062</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
@@ -1123,9 +1206,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>25063.0</v>
+        <v>25063</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>40</v>
@@ -1134,9 +1217,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>25068.0</v>
+        <v>25068</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>41</v>
@@ -1145,9 +1228,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>25070.0</v>
+        <v>25070</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>42</v>
@@ -1156,9 +1239,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>25071.0</v>
+        <v>25071</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>43</v>
@@ -1167,9 +1250,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>25072.0</v>
+        <v>25072</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>44</v>
@@ -1178,9 +1261,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>25073.0</v>
+        <v>25073</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>45</v>
@@ -1189,9 +1272,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>25074.0</v>
+        <v>25074</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>46</v>
@@ -1200,9 +1283,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>50059.0</v>
+        <v>50059</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>47</v>
@@ -1211,9 +1294,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>50189.0</v>
+        <v>50189</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>48</v>
@@ -1222,9 +1305,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>50350.0</v>
+        <v>50350</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>49</v>
@@ -1233,9 +1316,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>5021.0</v>
+        <v>5021</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>50</v>
@@ -1243,10 +1326,13 @@
       <c r="D44" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="E44" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>25017.0</v>
+        <v>25017</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>52</v>
@@ -1255,9 +1341,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>25028.0</v>
+        <v>25028</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>53</v>
@@ -1266,9 +1352,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>25031.0</v>
+        <v>25031</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>54</v>
@@ -1277,9 +1363,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>25039.0</v>
+        <v>25039</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>55</v>
@@ -1288,9 +1374,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>25040.0</v>
+        <v>25040</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>56</v>
@@ -1298,10 +1384,13 @@
       <c r="D49" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="E49" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>25053.0</v>
+        <v>25053</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>57</v>
@@ -1310,9 +1399,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>25060.0</v>
+        <v>25060</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>58</v>
@@ -1321,9 +1410,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>50007.0</v>
+        <v>50007</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>59</v>
@@ -1332,9 +1421,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>50014.0</v>
+        <v>50014</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>60</v>
@@ -1343,9 +1432,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>50015.0</v>
+        <v>50015</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>61</v>
@@ -1354,9 +1443,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>50016.0</v>
+        <v>50016</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>62</v>
@@ -1365,9 +1454,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>50017.0</v>
+        <v>50017</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>63</v>
@@ -1375,10 +1464,13 @@
       <c r="D56" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="57">
+      <c r="E56" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>50018.0</v>
+        <v>50018</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>64</v>
@@ -1387,9 +1479,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>50020.0</v>
+        <v>50020</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>65</v>
@@ -1398,9 +1490,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>50026.0</v>
+        <v>50026</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>66</v>
@@ -1409,9 +1501,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>50140.0</v>
+        <v>50140</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>67</v>
@@ -1419,10 +1511,13 @@
       <c r="D60" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="61">
+      <c r="E60" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>50160.0</v>
+        <v>50160</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>68</v>
@@ -1431,9 +1526,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>50253.0</v>
+        <v>50253</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>69</v>
@@ -1442,9 +1537,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>50347.0</v>
+        <v>50347</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>70</v>
@@ -1453,9 +1548,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>50351.0</v>
+        <v>50351</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>71</v>
@@ -1464,9 +1559,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>50363.0</v>
+        <v>50363</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>72</v>
@@ -1475,9 +1570,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>500386.0</v>
+        <v>500386</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>73</v>
@@ -1485,10 +1580,13 @@
       <c r="D66" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="67">
+      <c r="E66" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>500387.0</v>
+        <v>500387</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>74</v>
@@ -1497,9 +1595,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>500388.0</v>
+        <v>500388</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>75</v>
@@ -1508,9 +1606,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>500389.0</v>
+        <v>500389</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>76</v>
@@ -1519,9 +1617,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>500390.0</v>
+        <v>500390</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>77</v>
@@ -1529,10 +1627,13 @@
       <c r="D70" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="71">
+      <c r="E70" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>500391.0</v>
+        <v>500391</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>78</v>
@@ -1541,9 +1642,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>500392.0</v>
+        <v>500392</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>79</v>
@@ -1552,9 +1653,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>500393.0</v>
+        <v>500393</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>80</v>
@@ -1563,9 +1664,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>500394.0</v>
+        <v>500394</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>81</v>
@@ -1574,9 +1675,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>500395.0</v>
+        <v>500395</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>82</v>
@@ -1585,9 +1686,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>500396.0</v>
+        <v>500396</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>83</v>
@@ -1596,9 +1697,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>500397.0</v>
+        <v>500397</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>66</v>
@@ -1607,9 +1708,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>500398.0</v>
+        <v>500398</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>84</v>
@@ -1618,9 +1719,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>500399.0</v>
+        <v>500399</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>85</v>
@@ -1629,9 +1730,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>25005.0</v>
+        <v>25005</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>86</v>
@@ -1640,9 +1741,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>25013.0</v>
+        <v>25013</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>88</v>
@@ -1651,9 +1752,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>25019.0</v>
+        <v>25019</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>89</v>
@@ -1662,9 +1763,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>25057.0</v>
+        <v>25057</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>86</v>
@@ -1673,9 +1774,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>50030.0</v>
+        <v>50030</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>90</v>
@@ -1684,9 +1785,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>50031.0</v>
+        <v>50031</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>91</v>
@@ -1695,9 +1796,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>50038.0</v>
+        <v>50038</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>92</v>
@@ -1706,9 +1807,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>50039.0</v>
+        <v>50039</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>93</v>
@@ -1717,9 +1818,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>50050.0</v>
+        <v>50050</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>94</v>
@@ -1728,9 +1829,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>50060.0</v>
+        <v>50060</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>95</v>
@@ -1739,9 +1840,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>50062.0</v>
+        <v>50062</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>96</v>
@@ -1750,9 +1851,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>50065.0</v>
+        <v>50065</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>97</v>
@@ -1761,9 +1862,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>50099.0</v>
+        <v>50099</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>98</v>
@@ -1772,9 +1873,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>50218.0</v>
+        <v>50218</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>99</v>
@@ -1783,9 +1884,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>50245.0</v>
+        <v>50245</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>100</v>
@@ -1794,9 +1895,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>50263.0</v>
+        <v>50263</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>101</v>
@@ -1805,9 +1906,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>50281.0</v>
+        <v>50281</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>102</v>
@@ -1816,9 +1917,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>50294.0</v>
+        <v>50294</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>103</v>
@@ -1827,9 +1928,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>50323.0</v>
+        <v>50323</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>104</v>
@@ -1838,9 +1939,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>50341.0</v>
+        <v>50341</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>105</v>
@@ -1849,9 +1950,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>50343.0</v>
+        <v>50343</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>106</v>
@@ -1860,9 +1961,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>50358.0</v>
+        <v>50358</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>107</v>
@@ -1871,9 +1972,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>500401.0</v>
+        <v>500401</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>108</v>
@@ -1882,9 +1983,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>500402.0</v>
+        <v>500402</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>109</v>
@@ -1893,9 +1994,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>500404.0</v>
+        <v>500404</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>110</v>
@@ -1904,9 +2005,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>50166.0</v>
+        <v>50166</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>111</v>
@@ -1915,9 +2016,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>50220.0</v>
+        <v>50220</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>113</v>
@@ -1926,9 +2027,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>25035.0</v>
+        <v>25035</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>114</v>
@@ -1936,10 +2037,13 @@
       <c r="D107" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="108">
+      <c r="E107" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>25048.0</v>
+        <v>25048</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>116</v>
@@ -1948,9 +2052,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>25049.0</v>
+        <v>25049</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>117</v>
@@ -1959,9 +2063,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>25052.0</v>
+        <v>25052</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>118</v>
@@ -1970,9 +2074,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
-        <v>25055.0</v>
+        <v>25055</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>119</v>
@@ -1981,9 +2085,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
-        <v>25056.0</v>
+        <v>25056</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>120</v>
@@ -1992,9 +2096,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
-        <v>25061.0</v>
+        <v>25061</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>121</v>
@@ -2003,9 +2107,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
-        <v>50033.0</v>
+        <v>50033</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>122</v>
@@ -2014,9 +2118,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
-        <v>50052.0</v>
+        <v>50052</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>123</v>
@@ -2025,9 +2129,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
-        <v>50063.0</v>
+        <v>50063</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>124</v>
@@ -2036,9 +2140,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
-        <v>50069.0</v>
+        <v>50069</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>125</v>
@@ -2046,10 +2150,13 @@
       <c r="D117" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="118">
+      <c r="E117" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
-        <v>50192.0</v>
+        <v>50192</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>126</v>
@@ -2058,9 +2165,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
-        <v>50252.0</v>
+        <v>50252</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>127</v>
@@ -2069,9 +2176,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
-        <v>50303.0</v>
+        <v>50303</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>128</v>
@@ -2080,9 +2187,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
-        <v>50304.0</v>
+        <v>50304</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>129</v>
@@ -2091,9 +2198,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
-        <v>50305.0</v>
+        <v>50305</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>130</v>
@@ -2102,9 +2209,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
-        <v>50307.0</v>
+        <v>50307</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>131</v>
@@ -2113,9 +2220,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
-        <v>50322.0</v>
+        <v>50322</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>132</v>
@@ -2124,9 +2231,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
-        <v>50364.0</v>
+        <v>50364</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>133</v>
@@ -2135,9 +2242,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
-        <v>50380.0</v>
+        <v>50380</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>134</v>
@@ -2146,9 +2253,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
-        <v>50381.0</v>
+        <v>50381</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>135</v>
@@ -2157,9 +2264,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
-        <v>5007.0</v>
+        <v>5007</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>136</v>
@@ -2168,9 +2275,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
-        <v>25016.0</v>
+        <v>25016</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>138</v>
@@ -2179,9 +2286,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
-        <v>25022.0</v>
+        <v>25022</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>139</v>
@@ -2190,9 +2297,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
-        <v>25033.0</v>
+        <v>25033</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>140</v>
@@ -2201,9 +2308,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
-        <v>25047.0</v>
+        <v>25047</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>141</v>
@@ -2212,9 +2319,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
-        <v>25066.0</v>
+        <v>25066</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>142</v>
@@ -2223,9 +2330,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
-        <v>25067.0</v>
+        <v>25067</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>143</v>
@@ -2234,9 +2341,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
-        <v>50289.0</v>
+        <v>50289</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>144</v>
@@ -2245,9 +2352,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
-        <v>50291.0</v>
+        <v>50291</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>145</v>
@@ -2256,9 +2363,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
-        <v>50295.0</v>
+        <v>50295</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>146</v>
@@ -2267,9 +2374,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
-        <v>50320.0</v>
+        <v>50320</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>147</v>
@@ -2278,9 +2385,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
-        <v>50365.0</v>
+        <v>50365</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>148</v>
@@ -2289,9 +2396,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
-        <v>50366.0</v>
+        <v>50366</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>149</v>
@@ -2300,9 +2407,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
-        <v>50367.0</v>
+        <v>50367</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>150</v>
@@ -2311,9 +2418,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
-        <v>50374.0</v>
+        <v>50374</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>151</v>
@@ -2322,9 +2429,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
-        <v>500400.0</v>
+        <v>500400</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>152</v>
@@ -2333,9 +2440,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
-        <v>500403.0</v>
+        <v>500403</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>153</v>
@@ -2344,9 +2451,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
-        <v>25023.0</v>
+        <v>25023</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>154</v>
@@ -2355,9 +2462,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
-        <v>50003.0</v>
+        <v>50003</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>156</v>
@@ -2366,9 +2473,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
-        <v>50044.0</v>
+        <v>50044</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>157</v>
@@ -2377,9 +2484,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
-        <v>50208.0</v>
+        <v>50208</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>158</v>
@@ -2389,6 +2496,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/server/BIOMETRICEMPLOYEE.xlsx
+++ b/server/BIOMETRICEMPLOYEE.xlsx
@@ -1,33 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ML Cabigas\dmbbhr\server\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81C9A07-AB26-422B-82C1-E872A39FCD48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="7800"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="174">
   <si>
     <t>ID</t>
   </si>
@@ -546,20 +539,19 @@
   </si>
   <si>
     <t>Abalo, Oliver</t>
+  </si>
+  <si>
+    <t>Cabalan, Janrey</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -616,353 +608,16 @@
       <charset val="134"/>
       <scheme val="major"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -970,251 +625,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1226,68 +639,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1485,24 +854,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
-  <sheetFormatPr defaultColWidth="12.5740740740741" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="A1:F149"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="20.8518518518519" customWidth="1"/>
-    <col min="3" max="3" width="14.4259259259259" customWidth="1"/>
-    <col min="4" max="4" width="19.5740740740741" customWidth="1"/>
-    <col min="5" max="5" width="16.8518518518519" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:6">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="5">
         <v>25069</v>
       </c>
@@ -1536,7 +906,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="5">
         <v>50008</v>
       </c>
@@ -1550,7 +920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="5">
         <v>50046</v>
       </c>
@@ -1564,7 +934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="5">
         <v>50048</v>
       </c>
@@ -1578,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="5">
         <v>50071</v>
       </c>
@@ -1592,7 +962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:6">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="5">
         <v>50113</v>
       </c>
@@ -1606,7 +976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:6">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="5">
         <v>50190</v>
       </c>
@@ -1620,7 +990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="5">
         <v>25041</v>
       </c>
@@ -1634,7 +1004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="5">
         <v>25065</v>
       </c>
@@ -1648,7 +1018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:6">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="5">
         <v>50329</v>
       </c>
@@ -1662,7 +1032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:6">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="5">
         <v>50336</v>
       </c>
@@ -1676,7 +1046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:6">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="5">
         <v>58337</v>
       </c>
@@ -1690,7 +1060,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:6">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="5">
         <v>25001</v>
       </c>
@@ -1704,7 +1074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="5">
         <v>25003</v>
       </c>
@@ -1718,7 +1088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:6">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="5">
         <v>25021</v>
       </c>
@@ -1732,7 +1102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:6">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="5">
         <v>25024</v>
       </c>
@@ -1746,7 +1116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:6">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="5">
         <v>25025</v>
       </c>
@@ -1760,7 +1130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:6">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="5">
         <v>25027</v>
       </c>
@@ -1774,7 +1144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:6">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="5">
         <v>25032</v>
       </c>
@@ -1788,7 +1158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:6">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="5">
         <v>25034</v>
       </c>
@@ -1802,7 +1172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:6">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="5">
         <v>25036</v>
       </c>
@@ -1816,7 +1186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:6">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="5">
         <v>25037</v>
       </c>
@@ -1830,7 +1200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:6">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="5">
         <v>25042</v>
       </c>
@@ -1844,7 +1214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:6">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="5">
         <v>25043</v>
       </c>
@@ -1858,7 +1228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:6">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="5">
         <v>25044</v>
       </c>
@@ -1872,7 +1242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:6">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="5">
         <v>25045</v>
       </c>
@@ -1886,7 +1256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:6">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="5">
         <v>25046</v>
       </c>
@@ -1900,7 +1270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:6">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="5">
         <v>25050</v>
       </c>
@@ -1914,7 +1284,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:6">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="5">
         <v>25054</v>
       </c>
@@ -1928,7 +1298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:6">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="5">
         <v>25058</v>
       </c>
@@ -1942,7 +1312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:6">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="A32" s="5">
         <v>25059</v>
       </c>
@@ -1956,7 +1326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:6">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1">
       <c r="A33" s="5">
         <v>25062</v>
       </c>
@@ -1970,7 +1340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:6">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1">
       <c r="A34" s="5">
         <v>25063</v>
       </c>
@@ -1984,7 +1354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:6">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
       <c r="A35" s="5">
         <v>25068</v>
       </c>
@@ -1998,7 +1368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:6">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1">
       <c r="A36" s="5">
         <v>25070</v>
       </c>
@@ -2012,7 +1382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:6">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1">
       <c r="A37" s="5">
         <v>25071</v>
       </c>
@@ -2026,7 +1396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:6">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1">
       <c r="A38" s="5">
         <v>25072</v>
       </c>
@@ -2040,7 +1410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:6">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1">
       <c r="A39" s="5">
         <v>25073</v>
       </c>
@@ -2054,7 +1424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:6">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1">
       <c r="A40" s="5">
         <v>25074</v>
       </c>
@@ -2068,7 +1438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:6">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1">
       <c r="A41" s="5">
         <v>50059</v>
       </c>
@@ -2082,7 +1452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:6">
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
       <c r="A42" s="5">
         <v>50189</v>
       </c>
@@ -2096,7 +1466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:6">
+    <row r="43" spans="1:6" ht="15.75" customHeight="1">
       <c r="A43" s="5">
         <v>50350</v>
       </c>
@@ -2110,7 +1480,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:6">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1">
       <c r="A44" s="5">
         <v>5021</v>
       </c>
@@ -2127,7 +1497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:6">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1">
       <c r="A45" s="5">
         <v>25017</v>
       </c>
@@ -2141,7 +1511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:6">
+    <row r="46" spans="1:6" ht="15.75" customHeight="1">
       <c r="A46" s="5">
         <v>25028</v>
       </c>
@@ -2155,7 +1525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:6">
+    <row r="47" spans="1:6" ht="15.75" customHeight="1">
       <c r="A47" s="5">
         <v>25031</v>
       </c>
@@ -2169,7 +1539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:6">
+    <row r="48" spans="1:6" ht="15.75" customHeight="1">
       <c r="A48" s="5">
         <v>25039</v>
       </c>
@@ -2183,7 +1553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:6">
+    <row r="49" spans="1:6" ht="15.75" customHeight="1">
       <c r="A49" s="5">
         <v>25040</v>
       </c>
@@ -2200,7 +1570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:6">
+    <row r="50" spans="1:6" ht="15.75" customHeight="1">
       <c r="A50" s="5">
         <v>25053</v>
       </c>
@@ -2214,7 +1584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:6">
+    <row r="51" spans="1:6" ht="15.75" customHeight="1">
       <c r="A51" s="5">
         <v>25060</v>
       </c>
@@ -2228,7 +1598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:6">
+    <row r="52" spans="1:6" ht="15.75" customHeight="1">
       <c r="A52" s="5">
         <v>50007</v>
       </c>
@@ -2242,7 +1612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:6">
+    <row r="53" spans="1:6" ht="15.75" customHeight="1">
       <c r="A53" s="5">
         <v>50014</v>
       </c>
@@ -2256,7 +1626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:6">
+    <row r="54" spans="1:6" ht="15.75" customHeight="1">
       <c r="A54" s="5">
         <v>50015</v>
       </c>
@@ -2270,7 +1640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:6">
+    <row r="55" spans="1:6" ht="15.75" customHeight="1">
       <c r="A55" s="5">
         <v>50016</v>
       </c>
@@ -2284,7 +1654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:6">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1">
       <c r="A56" s="5">
         <v>50017</v>
       </c>
@@ -2301,7 +1671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:6">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1">
       <c r="A57" s="5">
         <v>50018</v>
       </c>
@@ -2315,7 +1685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:6">
+    <row r="58" spans="1:6" ht="15.75" customHeight="1">
       <c r="A58" s="5">
         <v>50020</v>
       </c>
@@ -2329,7 +1699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:6">
+    <row r="59" spans="1:6" ht="15.75" customHeight="1">
       <c r="A59" s="5">
         <v>50026</v>
       </c>
@@ -2343,7 +1713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:6">
+    <row r="60" spans="1:6" ht="15.75" customHeight="1">
       <c r="A60" s="5">
         <v>50140</v>
       </c>
@@ -2360,7 +1730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:6">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1">
       <c r="A61" s="5">
         <v>50160</v>
       </c>
@@ -2374,7 +1744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:6">
+    <row r="62" spans="1:6" ht="15.75" customHeight="1">
       <c r="A62" s="5">
         <v>50253</v>
       </c>
@@ -2388,7 +1758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:6">
+    <row r="63" spans="1:6" ht="15.75" customHeight="1">
       <c r="A63" s="5">
         <v>50347</v>
       </c>
@@ -2402,7 +1772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:6">
+    <row r="64" spans="1:6" ht="15.75" customHeight="1">
       <c r="A64" s="5">
         <v>50351</v>
       </c>
@@ -2416,7 +1786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:6">
+    <row r="65" spans="1:6" ht="15.75" customHeight="1">
       <c r="A65" s="5">
         <v>50363</v>
       </c>
@@ -2430,7 +1800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:6">
+    <row r="66" spans="1:6" ht="15.75" customHeight="1">
       <c r="A66" s="5">
         <v>500386</v>
       </c>
@@ -2447,7 +1817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:6">
+    <row r="67" spans="1:6" ht="15.75" customHeight="1">
       <c r="A67" s="5">
         <v>500387</v>
       </c>
@@ -2461,7 +1831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:6">
+    <row r="68" spans="1:6" ht="15.75" customHeight="1">
       <c r="A68" s="5">
         <v>500388</v>
       </c>
@@ -2475,7 +1845,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="1:6">
+    <row r="69" spans="1:6" ht="15.75" customHeight="1">
       <c r="A69" s="5">
         <v>500389</v>
       </c>
@@ -2489,7 +1859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:6">
+    <row r="70" spans="1:6" ht="15.75" customHeight="1">
       <c r="A70" s="5">
         <v>500390</v>
       </c>
@@ -2506,7 +1876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:6">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1">
       <c r="A71" s="5">
         <v>500391</v>
       </c>
@@ -2520,7 +1890,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:6">
+    <row r="72" spans="1:6" ht="15.75" customHeight="1">
       <c r="A72" s="5">
         <v>500392</v>
       </c>
@@ -2534,7 +1904,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:6">
+    <row r="73" spans="1:6" ht="15.75" customHeight="1">
       <c r="A73" s="5">
         <v>500393</v>
       </c>
@@ -2548,7 +1918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:6">
+    <row r="74" spans="1:6" ht="15.75" customHeight="1">
       <c r="A74" s="5">
         <v>500394</v>
       </c>
@@ -2562,7 +1932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:6">
+    <row r="75" spans="1:6" ht="15.75" customHeight="1">
       <c r="A75" s="5">
         <v>500395</v>
       </c>
@@ -2576,7 +1946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:6">
+    <row r="76" spans="1:6" ht="15.75" customHeight="1">
       <c r="A76" s="5">
         <v>500396</v>
       </c>
@@ -2590,7 +1960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:6">
+    <row r="77" spans="1:6" ht="15.75" customHeight="1">
       <c r="A77" s="5">
         <v>500397</v>
       </c>
@@ -2604,7 +1974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="1:6">
+    <row r="78" spans="1:6" ht="15.75" customHeight="1">
       <c r="A78" s="5">
         <v>500398</v>
       </c>
@@ -2618,7 +1988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:6">
+    <row r="79" spans="1:6" ht="15.75" customHeight="1">
       <c r="A79" s="5">
         <v>500399</v>
       </c>
@@ -2632,7 +2002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="1:6">
+    <row r="80" spans="1:6" ht="15.75" customHeight="1">
       <c r="A80" s="5">
         <v>25005</v>
       </c>
@@ -2646,7 +2016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="1:6">
+    <row r="81" spans="1:6" ht="15.75" customHeight="1">
       <c r="A81" s="5">
         <v>25013</v>
       </c>
@@ -2660,7 +2030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="1:6">
+    <row r="82" spans="1:6" ht="15.75" customHeight="1">
       <c r="A82" s="5">
         <v>25019</v>
       </c>
@@ -2674,7 +2044,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="1:6">
+    <row r="83" spans="1:6" ht="15.75" customHeight="1">
       <c r="A83" s="5">
         <v>25057</v>
       </c>
@@ -2688,7 +2058,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="1:6">
+    <row r="84" spans="1:6" ht="15.75" customHeight="1">
       <c r="A84" s="5">
         <v>50030</v>
       </c>
@@ -2702,7 +2072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="1:6">
+    <row r="85" spans="1:6" ht="15.75" customHeight="1">
       <c r="A85" s="5">
         <v>50031</v>
       </c>
@@ -2716,7 +2086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="1:6">
+    <row r="86" spans="1:6" ht="15.75" customHeight="1">
       <c r="A86" s="5">
         <v>50038</v>
       </c>
@@ -2730,7 +2100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="1:6">
+    <row r="87" spans="1:6" ht="15.75" customHeight="1">
       <c r="A87" s="5">
         <v>50039</v>
       </c>
@@ -2744,7 +2114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="1:6">
+    <row r="88" spans="1:6" ht="15.75" customHeight="1">
       <c r="A88" s="5">
         <v>50050</v>
       </c>
@@ -2758,7 +2128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="1:6">
+    <row r="89" spans="1:6" ht="15.75" customHeight="1">
       <c r="A89" s="5">
         <v>50060</v>
       </c>
@@ -2772,7 +2142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:6">
+    <row r="90" spans="1:6" ht="15.75" customHeight="1">
       <c r="A90" s="5">
         <v>50062</v>
       </c>
@@ -2786,7 +2156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="1:6">
+    <row r="91" spans="1:6" ht="15.75" customHeight="1">
       <c r="A91" s="5">
         <v>50065</v>
       </c>
@@ -2800,7 +2170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:6">
+    <row r="92" spans="1:6" ht="15.75" customHeight="1">
       <c r="A92" s="5">
         <v>50099</v>
       </c>
@@ -2814,7 +2184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:6">
+    <row r="93" spans="1:6" ht="15.75" customHeight="1">
       <c r="A93" s="5">
         <v>50218</v>
       </c>
@@ -2828,7 +2198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="1:6">
+    <row r="94" spans="1:6" ht="15.75" customHeight="1">
       <c r="A94" s="5">
         <v>50245</v>
       </c>
@@ -2842,7 +2212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="1:6">
+    <row r="95" spans="1:6" ht="15.75" customHeight="1">
       <c r="A95" s="5">
         <v>50263</v>
       </c>
@@ -2856,7 +2226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:6">
+    <row r="96" spans="1:6" ht="15.75" customHeight="1">
       <c r="A96" s="5">
         <v>50281</v>
       </c>
@@ -2870,7 +2240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="1:6">
+    <row r="97" spans="1:6" ht="15.75" customHeight="1">
       <c r="A97" s="5">
         <v>50294</v>
       </c>
@@ -2884,7 +2254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="1:6">
+    <row r="98" spans="1:6" ht="15.75" customHeight="1">
       <c r="A98" s="5">
         <v>50323</v>
       </c>
@@ -2898,7 +2268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="1:6">
+    <row r="99" spans="1:6" ht="15.75" customHeight="1">
       <c r="A99" s="5">
         <v>50341</v>
       </c>
@@ -2912,7 +2282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="1:6">
+    <row r="100" spans="1:6" ht="15.75" customHeight="1">
       <c r="A100" s="5">
         <v>50343</v>
       </c>
@@ -2926,7 +2296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="1:6">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1">
       <c r="A101" s="5">
         <v>50358</v>
       </c>
@@ -2940,7 +2310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="1:6">
+    <row r="102" spans="1:6" ht="15.75" customHeight="1">
       <c r="A102" s="5">
         <v>500401</v>
       </c>
@@ -2954,7 +2324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="1:6">
+    <row r="103" spans="1:6" ht="15.75" customHeight="1">
       <c r="A103" s="5">
         <v>500402</v>
       </c>
@@ -2968,7 +2338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="1:6">
+    <row r="104" spans="1:6" ht="15.75" customHeight="1">
       <c r="A104" s="5">
         <v>500404</v>
       </c>
@@ -2982,7 +2352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="1:6">
+    <row r="105" spans="1:6" ht="15.75" customHeight="1">
       <c r="A105" s="5">
         <v>50166</v>
       </c>
@@ -2996,7 +2366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" customHeight="1" spans="1:6">
+    <row r="106" spans="1:6" ht="15.75" customHeight="1">
       <c r="A106" s="5">
         <v>50220</v>
       </c>
@@ -3010,7 +2380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="1:6">
+    <row r="107" spans="1:6" ht="15.75" customHeight="1">
       <c r="A107" s="5">
         <v>25035</v>
       </c>
@@ -3027,7 +2397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="1:6">
+    <row r="108" spans="1:6" ht="15.75" customHeight="1">
       <c r="A108" s="5">
         <v>25048</v>
       </c>
@@ -3041,7 +2411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="1:6">
+    <row r="109" spans="1:6" ht="15.75" customHeight="1">
       <c r="A109" s="5">
         <v>25049</v>
       </c>
@@ -3055,7 +2425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="1:6">
+    <row r="110" spans="1:6" ht="15.75" customHeight="1">
       <c r="A110" s="5">
         <v>25052</v>
       </c>
@@ -3069,7 +2439,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="1:6">
+    <row r="111" spans="1:6" ht="15.75" customHeight="1">
       <c r="A111" s="5">
         <v>25055</v>
       </c>
@@ -3083,7 +2453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="1:6">
+    <row r="112" spans="1:6" ht="15.75" customHeight="1">
       <c r="A112" s="5">
         <v>25056</v>
       </c>
@@ -3097,7 +2467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" customHeight="1" spans="1:6">
+    <row r="113" spans="1:6" ht="15.75" customHeight="1">
       <c r="A113" s="5">
         <v>25061</v>
       </c>
@@ -3111,7 +2481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="1:6">
+    <row r="114" spans="1:6" ht="15.75" customHeight="1">
       <c r="A114" s="5">
         <v>50033</v>
       </c>
@@ -3125,7 +2495,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" customHeight="1" spans="1:6">
+    <row r="115" spans="1:6" ht="15.75" customHeight="1">
       <c r="A115" s="5">
         <v>50052</v>
       </c>
@@ -3139,7 +2509,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" customHeight="1" spans="1:6">
+    <row r="116" spans="1:6" ht="15.75" customHeight="1">
       <c r="A116" s="5">
         <v>50063</v>
       </c>
@@ -3153,7 +2523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" customHeight="1" spans="1:6">
+    <row r="117" spans="1:6" ht="15.75" customHeight="1">
       <c r="A117" s="5">
         <v>50069</v>
       </c>
@@ -3170,7 +2540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" customHeight="1" spans="1:6">
+    <row r="118" spans="1:6" ht="15.75" customHeight="1">
       <c r="A118" s="5">
         <v>50192</v>
       </c>
@@ -3184,7 +2554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" customHeight="1" spans="1:6">
+    <row r="119" spans="1:6" ht="15.75" customHeight="1">
       <c r="A119" s="5">
         <v>50252</v>
       </c>
@@ -3198,7 +2568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" customHeight="1" spans="1:6">
+    <row r="120" spans="1:6" ht="15.75" customHeight="1">
       <c r="A120" s="5">
         <v>50303</v>
       </c>
@@ -3212,7 +2582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" customHeight="1" spans="1:6">
+    <row r="121" spans="1:6" ht="15.75" customHeight="1">
       <c r="A121" s="5">
         <v>50304</v>
       </c>
@@ -3226,7 +2596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" customHeight="1" spans="1:6">
+    <row r="122" spans="1:6" ht="15.75" customHeight="1">
       <c r="A122" s="5">
         <v>50305</v>
       </c>
@@ -3240,7 +2610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" customHeight="1" spans="1:6">
+    <row r="123" spans="1:6" ht="15.75" customHeight="1">
       <c r="A123" s="5">
         <v>50307</v>
       </c>
@@ -3254,7 +2624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" customHeight="1" spans="1:6">
+    <row r="124" spans="1:6" ht="15.75" customHeight="1">
       <c r="A124" s="5">
         <v>50322</v>
       </c>
@@ -3268,7 +2638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" customHeight="1" spans="1:6">
+    <row r="125" spans="1:6" ht="15.75" customHeight="1">
       <c r="A125" s="5">
         <v>50364</v>
       </c>
@@ -3282,7 +2652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" customHeight="1" spans="1:6">
+    <row r="126" spans="1:6" ht="15.75" customHeight="1">
       <c r="A126" s="5">
         <v>50380</v>
       </c>
@@ -3296,7 +2666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" customHeight="1" spans="1:6">
+    <row r="127" spans="1:6" ht="15.75" customHeight="1">
       <c r="A127" s="5">
         <v>50381</v>
       </c>
@@ -3310,7 +2680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="1:6">
+    <row r="128" spans="1:6" ht="15.75" customHeight="1">
       <c r="A128" s="5">
         <v>5007</v>
       </c>
@@ -3324,7 +2694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="1:6">
+    <row r="129" spans="1:6" ht="15.75" customHeight="1">
       <c r="A129" s="5">
         <v>25016</v>
       </c>
@@ -3338,7 +2708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="1:6">
+    <row r="130" spans="1:6" ht="15.75" customHeight="1">
       <c r="A130" s="5">
         <v>25022</v>
       </c>
@@ -3352,7 +2722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="1:6">
+    <row r="131" spans="1:6" ht="15.75" customHeight="1">
       <c r="A131" s="5">
         <v>25033</v>
       </c>
@@ -3366,7 +2736,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="1:6">
+    <row r="132" spans="1:6" ht="15.75" customHeight="1">
       <c r="A132" s="5">
         <v>25047</v>
       </c>
@@ -3380,7 +2750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="1:6">
+    <row r="133" spans="1:6" ht="15.75" customHeight="1">
       <c r="A133" s="5">
         <v>25066</v>
       </c>
@@ -3394,7 +2764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="1:6">
+    <row r="134" spans="1:6" ht="15.75" customHeight="1">
       <c r="A134" s="5">
         <v>25067</v>
       </c>
@@ -3408,7 +2778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="1:6">
+    <row r="135" spans="1:6" ht="15.75" customHeight="1">
       <c r="A135" s="5">
         <v>50289</v>
       </c>
@@ -3422,7 +2792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="1:6">
+    <row r="136" spans="1:6" ht="15.75" customHeight="1">
       <c r="A136" s="5">
         <v>50291</v>
       </c>
@@ -3436,7 +2806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="1:6">
+    <row r="137" spans="1:6" ht="15.75" customHeight="1">
       <c r="A137" s="5">
         <v>50295</v>
       </c>
@@ -3450,7 +2820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="1:6">
+    <row r="138" spans="1:6" ht="15.75" customHeight="1">
       <c r="A138" s="5">
         <v>50320</v>
       </c>
@@ -3464,7 +2834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="1:6">
+    <row r="139" spans="1:6" ht="15.75" customHeight="1">
       <c r="A139" s="5">
         <v>50365</v>
       </c>
@@ -3478,7 +2848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="1:6">
+    <row r="140" spans="1:6" ht="15.75" customHeight="1">
       <c r="A140" s="5">
         <v>50366</v>
       </c>
@@ -3492,7 +2862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="1:6">
+    <row r="141" spans="1:6" ht="15.75" customHeight="1">
       <c r="A141" s="5">
         <v>50367</v>
       </c>
@@ -3506,7 +2876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" customHeight="1" spans="1:6">
+    <row r="142" spans="1:6" ht="15.75" customHeight="1">
       <c r="A142" s="5">
         <v>50374</v>
       </c>
@@ -3520,7 +2890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" customHeight="1" spans="1:6">
+    <row r="143" spans="1:6" ht="15.75" customHeight="1">
       <c r="A143" s="5">
         <v>500400</v>
       </c>
@@ -3534,7 +2904,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" customHeight="1" spans="1:6">
+    <row r="144" spans="1:6" ht="15.75" customHeight="1">
       <c r="A144" s="5">
         <v>500403</v>
       </c>
@@ -3548,7 +2918,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="1:6">
+    <row r="145" spans="1:6" ht="15.75" customHeight="1">
       <c r="A145" s="5">
         <v>25023</v>
       </c>
@@ -3562,7 +2932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="1:6">
+    <row r="146" spans="1:6" ht="15.75" customHeight="1">
       <c r="A146" s="5">
         <v>50003</v>
       </c>
@@ -3576,7 +2946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="1:6">
+    <row r="147" spans="1:6" ht="15.75" customHeight="1">
       <c r="A147" s="5">
         <v>50044</v>
       </c>
@@ -3590,7 +2960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="1:6">
+    <row r="148" spans="1:6" ht="15.75" customHeight="1">
       <c r="A148" s="5">
         <v>50208</v>
       </c>
@@ -3601,12 +2971,25 @@
         <v>169</v>
       </c>
       <c r="F148" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A149" s="5">
+        <v>25051</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F149" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/server/BIOMETRICEMPLOYEE.xlsx
+++ b/server/BIOMETRICEMPLOYEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ML Cabigas\dmbbhr\server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81C9A07-AB26-422B-82C1-E872A39FCD48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FDC173-AD24-41FB-ACC2-7E18B851FC10}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="177">
   <si>
     <t>ID</t>
   </si>
@@ -487,9 +487,6 @@
     <t>Gabiana, Jayson</t>
   </si>
   <si>
-    <t>Saramosing, Julius Olive</t>
-  </si>
-  <si>
     <t>Cañalita, Janely Mae</t>
   </si>
   <si>
@@ -542,6 +539,18 @@
   </si>
   <si>
     <t>Cabalan, Janrey</t>
+  </si>
+  <si>
+    <t>B-DAY</t>
+  </si>
+  <si>
+    <t>Saramosing, Julius Oliver</t>
+  </si>
+  <si>
+    <t>July 16, 1985</t>
+  </si>
+  <si>
+    <t>July 09, 1996</t>
   </si>
 </sst>
 </file>
@@ -863,16 +872,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -891,8 +900,11 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="G1" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="5">
         <v>25069</v>
       </c>
@@ -906,7 +918,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="5">
         <v>50008</v>
       </c>
@@ -920,7 +932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="5">
         <v>50046</v>
       </c>
@@ -934,7 +946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="5">
         <v>50048</v>
       </c>
@@ -948,7 +960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="5">
         <v>50071</v>
       </c>
@@ -962,7 +974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="5">
         <v>50113</v>
       </c>
@@ -976,7 +988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="5">
         <v>50190</v>
       </c>
@@ -990,7 +1002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="5">
         <v>25041</v>
       </c>
@@ -1004,7 +1016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="5">
         <v>25065</v>
       </c>
@@ -1017,8 +1029,11 @@
       <c r="F10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="G10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="5">
         <v>50329</v>
       </c>
@@ -1032,7 +1047,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="5">
         <v>50336</v>
       </c>
@@ -1046,7 +1061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="5">
         <v>58337</v>
       </c>
@@ -1060,7 +1075,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="5">
         <v>25001</v>
       </c>
@@ -1074,7 +1089,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="5">
         <v>25003</v>
       </c>
@@ -1088,7 +1103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="5">
         <v>25021</v>
       </c>
@@ -2694,7 +2709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="15.75" customHeight="1">
+    <row r="129" spans="1:7" ht="15.75" customHeight="1">
       <c r="A129" s="5">
         <v>25016</v>
       </c>
@@ -2708,7 +2723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="15.75" customHeight="1">
+    <row r="130" spans="1:7" ht="15.75" customHeight="1">
       <c r="A130" s="5">
         <v>25022</v>
       </c>
@@ -2722,7 +2737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="15.75" customHeight="1">
+    <row r="131" spans="1:7" ht="15.75" customHeight="1">
       <c r="A131" s="5">
         <v>25033</v>
       </c>
@@ -2736,12 +2751,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="15.75" customHeight="1">
+    <row r="132" spans="1:7" ht="15.75" customHeight="1">
       <c r="A132" s="5">
         <v>25047</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>151</v>
@@ -2749,13 +2764,16 @@
       <c r="F132" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" ht="15.75" customHeight="1">
+      <c r="G132" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="15.75" customHeight="1">
       <c r="A133" s="5">
         <v>25066</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>151</v>
@@ -2764,12 +2782,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="15.75" customHeight="1">
+    <row r="134" spans="1:7" ht="15.75" customHeight="1">
       <c r="A134" s="5">
         <v>25067</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>151</v>
@@ -2778,12 +2796,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="15.75" customHeight="1">
+    <row r="135" spans="1:7" ht="15.75" customHeight="1">
       <c r="A135" s="5">
         <v>50289</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>151</v>
@@ -2792,12 +2810,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="15.75" customHeight="1">
+    <row r="136" spans="1:7" ht="15.75" customHeight="1">
       <c r="A136" s="5">
         <v>50291</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>151</v>
@@ -2806,12 +2824,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="15.75" customHeight="1">
+    <row r="137" spans="1:7" ht="15.75" customHeight="1">
       <c r="A137" s="5">
         <v>50295</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>151</v>
@@ -2820,12 +2838,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="15.75" customHeight="1">
+    <row r="138" spans="1:7" ht="15.75" customHeight="1">
       <c r="A138" s="5">
         <v>50320</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>151</v>
@@ -2834,12 +2852,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="15.75" customHeight="1">
+    <row r="139" spans="1:7" ht="15.75" customHeight="1">
       <c r="A139" s="5">
         <v>50365</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>151</v>
@@ -2848,12 +2866,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="15.75" customHeight="1">
+    <row r="140" spans="1:7" ht="15.75" customHeight="1">
       <c r="A140" s="5">
         <v>50366</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>151</v>
@@ -2862,12 +2880,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="15.75" customHeight="1">
+    <row r="141" spans="1:7" ht="15.75" customHeight="1">
       <c r="A141" s="5">
         <v>50367</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>151</v>
@@ -2876,12 +2894,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="15.75" customHeight="1">
+    <row r="142" spans="1:7" ht="15.75" customHeight="1">
       <c r="A142" s="5">
         <v>50374</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>151</v>
@@ -2890,12 +2908,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="15.75" customHeight="1">
+    <row r="143" spans="1:7" ht="15.75" customHeight="1">
       <c r="A143" s="5">
         <v>500400</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>151</v>
@@ -2904,12 +2922,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="15.75" customHeight="1">
+    <row r="144" spans="1:7" ht="15.75" customHeight="1">
       <c r="A144" s="5">
         <v>500403</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>151</v>
@@ -2923,10 +2941,10 @@
         <v>25023</v>
       </c>
       <c r="B145" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D145" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="F145" t="s">
         <v>10</v>
@@ -2937,10 +2955,10 @@
         <v>50003</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F146" t="s">
         <v>10</v>
@@ -2951,10 +2969,10 @@
         <v>50044</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F147" t="s">
         <v>10</v>
@@ -2965,10 +2983,10 @@
         <v>50208</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F148" t="s">
         <v>10</v>
@@ -2979,7 +2997,7 @@
         <v>25051</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>127</v>

--- a/server/BIOMETRICEMPLOYEE.xlsx
+++ b/server/BIOMETRICEMPLOYEE.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ML Cabigas\dmbbhr\server\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CAAA17-BABE-4B5E-8896-CAE5E3D59655}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="436">
   <si>
     <t>ID</t>
   </si>
@@ -1307,56 +1316,70 @@
   </si>
   <si>
     <t>Yu, Merry Joy</t>
+  </si>
+  <si>
+    <t>Paran, Jayde Jhoshua</t>
+  </si>
+  <si>
+    <t>DMBB</t>
+  </si>
+  <si>
+    <t>SO2</t>
+  </si>
+  <si>
+    <t>January 14, 2001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="mmmm d, yyyy"/>
+    <numFmt numFmtId="165" formatCode="mmmm\ d\,\ yyyy"/>
   </numFmts>
   <fonts count="8">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Inter"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Inter"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Inter"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Inter"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Inter"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Inter"/>
     </font>
@@ -1366,74 +1389,72 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1441,7 +1462,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1631,30 +1652,32 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.75"/>
-    <col customWidth="1" min="2" max="2" width="20.75"/>
-    <col customWidth="1" min="3" max="3" width="7.75"/>
-    <col customWidth="1" min="4" max="4" width="19.63"/>
-    <col customWidth="1" min="5" max="5" width="15.5"/>
-    <col customWidth="1" min="7" max="7" width="10.63"/>
-    <col customWidth="1" min="8" max="8" width="9.13"/>
-    <col customWidth="1" min="9" max="9" width="10.38"/>
-    <col customWidth="1" min="10" max="10" width="8.63"/>
-    <col customWidth="1" min="11" max="11" width="11.25"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:25" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1705,9 +1728,9 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:25" ht="15.75" customHeight="1">
       <c r="A2" s="5">
-        <v>5007.0</v>
+        <v>5007</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>12</v>
@@ -1741,9 +1764,9 @@
       </c>
       <c r="L2" s="10"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:25" ht="15.75" customHeight="1">
       <c r="A3" s="5">
-        <v>50113.0</v>
+        <v>50113</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
@@ -1771,9 +1794,9 @@
       </c>
       <c r="L3" s="10"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1">
       <c r="A4" s="5">
-        <v>50208.0</v>
+        <v>50208</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>28</v>
@@ -1807,9 +1830,9 @@
       </c>
       <c r="L4" s="10"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:25" ht="15.75" customHeight="1">
       <c r="A5" s="5">
-        <v>25061.0</v>
+        <v>25061</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>37</v>
@@ -1843,9 +1866,9 @@
       </c>
       <c r="L5" s="10"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1">
       <c r="A6" s="5">
-        <v>50305.0</v>
+        <v>50305</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>46</v>
@@ -1865,9 +1888,9 @@
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:25" ht="15.75" customHeight="1">
       <c r="A7" s="5">
-        <v>500390.0</v>
+        <v>500390</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>48</v>
@@ -1901,9 +1924,9 @@
       </c>
       <c r="L7" s="10"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:25" ht="15.75" customHeight="1">
       <c r="A8" s="5">
-        <v>50347.0</v>
+        <v>50347</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>56</v>
@@ -1923,9 +1946,9 @@
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:25" ht="15.75" customHeight="1">
       <c r="A9" s="5">
-        <v>50291.0</v>
+        <v>50291</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>58</v>
@@ -1937,7 +1960,7 @@
         <v>59</v>
       </c>
       <c r="E9" s="13">
-        <v>44893.0</v>
+        <v>44893</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>60</v>
@@ -1959,9 +1982,9 @@
       </c>
       <c r="L9" s="10"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:25" ht="15.75" customHeight="1">
       <c r="A10" s="5">
-        <v>50263.0</v>
+        <v>50263</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>66</v>
@@ -1981,9 +2004,9 @@
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:25" ht="15.75" customHeight="1">
       <c r="A11" s="5">
-        <v>50329.0</v>
+        <v>50329</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>68</v>
@@ -2003,9 +2026,9 @@
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:25" ht="15.75" customHeight="1">
       <c r="A12" s="5">
-        <v>25053.0</v>
+        <v>25053</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>70</v>
@@ -2039,9 +2062,9 @@
       </c>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:25" ht="15.75" customHeight="1">
       <c r="A13" s="5">
-        <v>50294.0</v>
+        <v>50294</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>78</v>
@@ -2075,9 +2098,9 @@
       </c>
       <c r="L13" s="10"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1">
       <c r="A14" s="5">
-        <v>50062.0</v>
+        <v>50062</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>86</v>
@@ -2111,9 +2134,9 @@
       </c>
       <c r="L14" s="10"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:25" ht="15.75" customHeight="1">
       <c r="A15" s="5">
-        <v>50044.0</v>
+        <v>50044</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>94</v>
@@ -2147,9 +2170,9 @@
       </c>
       <c r="L15" s="10"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:25" ht="15.75" customHeight="1">
       <c r="A16" s="5">
-        <v>500401.0</v>
+        <v>500401</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>103</v>
@@ -2181,9 +2204,9 @@
       <c r="K16" s="9"/>
       <c r="L16" s="10"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:12" ht="15.75" customHeight="1">
       <c r="A17" s="5">
-        <v>50039.0</v>
+        <v>50039</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -2217,9 +2240,9 @@
       </c>
       <c r="L17" s="10"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:12" ht="15.75" customHeight="1">
       <c r="A18" s="5">
-        <v>50295.0</v>
+        <v>50295</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>118</v>
@@ -2253,9 +2276,9 @@
       </c>
       <c r="L18" s="10"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:12" ht="15.75" customHeight="1">
       <c r="A19" s="5">
-        <v>50320.0</v>
+        <v>50320</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>125</v>
@@ -2289,9 +2312,9 @@
       </c>
       <c r="L19" s="10"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:12" ht="15.75" customHeight="1">
       <c r="A20" s="5">
-        <v>25032.0</v>
+        <v>25032</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>133</v>
@@ -2311,9 +2334,9 @@
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:12" ht="15.75" customHeight="1">
       <c r="A21" s="5">
-        <v>25039.0</v>
+        <v>25039</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>135</v>
@@ -2333,9 +2356,9 @@
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:12" ht="15.75" customHeight="1">
       <c r="A22" s="5">
-        <v>25058.0</v>
+        <v>25058</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>136</v>
@@ -2355,9 +2378,9 @@
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:12" ht="15.75" customHeight="1">
       <c r="A23" s="5">
-        <v>50060.0</v>
+        <v>50060</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>137</v>
@@ -2391,9 +2414,9 @@
       </c>
       <c r="L23" s="10"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:12" ht="15.75" customHeight="1">
       <c r="A24" s="5">
-        <v>25054.0</v>
+        <v>25054</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>145</v>
@@ -2413,9 +2436,9 @@
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:12" ht="15.75" customHeight="1">
       <c r="A25" s="5">
-        <v>25060.0</v>
+        <v>25060</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>146</v>
@@ -2449,9 +2472,9 @@
       </c>
       <c r="L25" s="10"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:12" ht="15.75" customHeight="1">
       <c r="A26" s="5">
-        <v>25041.0</v>
+        <v>25041</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>153</v>
@@ -2471,9 +2494,9 @@
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:12" ht="15.75" customHeight="1">
       <c r="A27" s="5">
-        <v>50190.0</v>
+        <v>50190</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>154</v>
@@ -2497,7 +2520,7 @@
         <v>159</v>
       </c>
       <c r="I27" s="14">
-        <v>1.21099542722E11</v>
+        <v>121099542722</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>160</v>
@@ -2507,9 +2530,9 @@
       </c>
       <c r="L27" s="10"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:12" ht="15.75" customHeight="1">
       <c r="A28" s="5">
-        <v>500400.0</v>
+        <v>500400</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>162</v>
@@ -2543,9 +2566,9 @@
       </c>
       <c r="L28" s="10"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:12" ht="15.75" customHeight="1">
       <c r="A29" s="5">
-        <v>25074.0</v>
+        <v>25074</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>168</v>
@@ -2565,9 +2588,9 @@
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:12" ht="15.75" customHeight="1">
       <c r="A30" s="5">
-        <v>50050.0</v>
+        <v>50050</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>169</v>
@@ -2601,9 +2624,9 @@
       </c>
       <c r="L30" s="10"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:12" ht="15.75" customHeight="1">
       <c r="A31" s="5">
-        <v>50059.0</v>
+        <v>50059</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>176</v>
@@ -2637,9 +2660,9 @@
       </c>
       <c r="L31" s="10"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:12" ht="15.75" customHeight="1">
       <c r="A32" s="5">
-        <v>25051.0</v>
+        <v>25051</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>182</v>
@@ -2673,9 +2696,9 @@
       </c>
       <c r="L32" s="10"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:12" ht="15.75" customHeight="1">
       <c r="A33" s="5">
-        <v>25052.0</v>
+        <v>25052</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>189</v>
@@ -2695,9 +2718,9 @@
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:12" ht="15.75" customHeight="1">
       <c r="A34" s="5">
-        <v>25017.0</v>
+        <v>25017</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>190</v>
@@ -2729,9 +2752,9 @@
       <c r="K34" s="9"/>
       <c r="L34" s="10"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:12" ht="15.75" customHeight="1">
       <c r="A35" s="5">
-        <v>50380.0</v>
+        <v>50380</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>196</v>
@@ -2765,9 +2788,9 @@
       </c>
       <c r="L35" s="10"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:12" ht="15.75" customHeight="1">
       <c r="A36" s="5">
-        <v>25045.0</v>
+        <v>25045</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>203</v>
@@ -2793,9 +2816,9 @@
       <c r="K36" s="9"/>
       <c r="L36" s="10"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:12" ht="15.75" customHeight="1">
       <c r="A37" s="5">
-        <v>25065.0</v>
+        <v>25065</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>206</v>
@@ -2807,7 +2830,7 @@
         <v>207</v>
       </c>
       <c r="E37" s="16">
-        <v>46230.0</v>
+        <v>46230</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>208</v>
@@ -2819,9 +2842,9 @@
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:12" ht="15.75" customHeight="1">
       <c r="A38" s="5">
-        <v>25066.0</v>
+        <v>25066</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>209</v>
@@ -2849,9 +2872,9 @@
       <c r="K38" s="9"/>
       <c r="L38" s="10"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:12" ht="15.75" customHeight="1">
       <c r="A39" s="5">
-        <v>50052.0</v>
+        <v>50052</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>213</v>
@@ -2885,9 +2908,9 @@
       </c>
       <c r="L39" s="10"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:12" ht="15.75" customHeight="1">
       <c r="A40" s="5">
-        <v>50341.0</v>
+        <v>50341</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>220</v>
@@ -2919,9 +2942,9 @@
       <c r="K40" s="9"/>
       <c r="L40" s="10"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:12" ht="15.75" customHeight="1">
       <c r="A41" s="5">
-        <v>25024.0</v>
+        <v>25024</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>227</v>
@@ -2949,9 +2972,9 @@
       <c r="K41" s="9"/>
       <c r="L41" s="10"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:12" ht="15.75" customHeight="1">
       <c r="A42" s="5">
-        <v>50218.0</v>
+        <v>50218</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>231</v>
@@ -2985,9 +3008,9 @@
       </c>
       <c r="L42" s="10"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:12" ht="15.75" customHeight="1">
       <c r="A43" s="5">
-        <v>25046.0</v>
+        <v>25046</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>239</v>
@@ -3021,9 +3044,9 @@
       </c>
       <c r="L43" s="10"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:12" ht="15.75" customHeight="1">
       <c r="A44" s="5">
-        <v>25069.0</v>
+        <v>25069</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>245</v>
@@ -3043,9 +3066,9 @@
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:12" ht="15.75" customHeight="1">
       <c r="A45" s="5">
-        <v>500387.0</v>
+        <v>500387</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>246</v>
@@ -3065,9 +3088,9 @@
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:12" ht="15.75" customHeight="1">
       <c r="A46" s="5">
-        <v>25049.0</v>
+        <v>25049</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>247</v>
@@ -3087,9 +3110,9 @@
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:12" ht="15.75" customHeight="1">
       <c r="A47" s="5">
-        <v>25040.0</v>
+        <v>25040</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>248</v>
@@ -3123,9 +3146,9 @@
       </c>
       <c r="L47" s="10"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:12" ht="15.75" customHeight="1">
       <c r="A48" s="5">
-        <v>50071.0</v>
+        <v>50071</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>256</v>
@@ -3145,9 +3168,9 @@
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:12" ht="15.75" customHeight="1">
       <c r="A49" s="5">
-        <v>50366.0</v>
+        <v>50366</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>257</v>
@@ -3181,9 +3204,9 @@
       </c>
       <c r="L49" s="10"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:12" ht="15.75" customHeight="1">
       <c r="A50" s="5">
-        <v>50307.0</v>
+        <v>50307</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>265</v>
@@ -3203,9 +3226,9 @@
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:12" ht="15.75" customHeight="1">
       <c r="A51" s="5">
-        <v>25031.0</v>
+        <v>25031</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>266</v>
@@ -3225,9 +3248,9 @@
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:12" ht="15.75" customHeight="1">
       <c r="A52" s="5">
-        <v>25070.0</v>
+        <v>25070</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>267</v>
@@ -3247,9 +3270,9 @@
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:12" ht="15.75" customHeight="1">
       <c r="A53" s="5">
-        <v>50322.0</v>
+        <v>50322</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>268</v>
@@ -3269,9 +3292,9 @@
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:12" ht="15.75" customHeight="1">
       <c r="A54" s="5">
-        <v>25023.0</v>
+        <v>25023</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>269</v>
@@ -3305,9 +3328,9 @@
       </c>
       <c r="L54" s="10"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:12" ht="15.75" customHeight="1">
       <c r="A55" s="5">
-        <v>500389.0</v>
+        <v>500389</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>277</v>
@@ -3341,9 +3364,9 @@
       </c>
       <c r="L55" s="10"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:12" ht="15.75" customHeight="1">
       <c r="A56" s="5">
-        <v>25043.0</v>
+        <v>25043</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>284</v>
@@ -3363,9 +3386,9 @@
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="5">
-        <v>25027.0</v>
+        <v>25027</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>285</v>
@@ -3395,9 +3418,9 @@
       <c r="K57" s="9"/>
       <c r="L57" s="10"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="5">
-        <v>50099.0</v>
+        <v>50099</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>290</v>
@@ -3431,9 +3454,9 @@
       </c>
       <c r="L58" s="10"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:12" ht="15.75" customHeight="1">
       <c r="A59" s="5">
-        <v>50252.0</v>
+        <v>50252</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>299</v>
@@ -3467,9 +3490,9 @@
       </c>
       <c r="L59" s="10"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:12" ht="15.75" customHeight="1">
       <c r="A60" s="5">
-        <v>25056.0</v>
+        <v>25056</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>306</v>
@@ -3489,9 +3512,9 @@
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="5">
-        <v>50033.0</v>
+        <v>50033</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>306</v>
@@ -3511,9 +3534,9 @@
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="5">
-        <v>25044.0</v>
+        <v>25044</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>307</v>
@@ -3533,9 +3556,9 @@
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:12" ht="15.75" customHeight="1">
       <c r="A63" s="5">
-        <v>50351.0</v>
+        <v>50351</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>308</v>
@@ -3555,9 +3578,9 @@
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="5">
-        <v>500386.0</v>
+        <v>500386</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>309</v>
@@ -3579,9 +3602,9 @@
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:12" ht="15.75" customHeight="1">
       <c r="A65" s="5">
-        <v>500399.0</v>
+        <v>500399</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>311</v>
@@ -3601,9 +3624,9 @@
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:12" ht="15.75" customHeight="1">
       <c r="A66" s="5">
-        <v>25021.0</v>
+        <v>25021</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>312</v>
@@ -3623,9 +3646,9 @@
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:12" ht="15.75" customHeight="1">
       <c r="A67" s="5">
-        <v>50017.0</v>
+        <v>50017</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>277</v>
@@ -3659,9 +3682,9 @@
       </c>
       <c r="L67" s="10"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:12" ht="15.75" customHeight="1">
       <c r="A68" s="5">
-        <v>50069.0</v>
+        <v>50069</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>313</v>
@@ -3695,9 +3718,9 @@
       </c>
       <c r="L68" s="10"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:12" ht="15.75" customHeight="1">
       <c r="A69" s="5">
-        <v>50046.0</v>
+        <v>50046</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>321</v>
@@ -3731,9 +3754,9 @@
       </c>
       <c r="L69" s="10"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:12" ht="15.75" customHeight="1">
       <c r="A70" s="5">
-        <v>50007.0</v>
+        <v>50007</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>329</v>
@@ -3767,9 +3790,9 @@
       </c>
       <c r="L70" s="10"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:12" ht="15.75" customHeight="1">
       <c r="A71" s="5">
-        <v>25033.0</v>
+        <v>25033</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>337</v>
@@ -3789,9 +3812,9 @@
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:12" ht="15.75" customHeight="1">
       <c r="A72" s="5">
-        <v>50304.0</v>
+        <v>50304</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>338</v>
@@ -3811,9 +3834,9 @@
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:12" ht="15.75" customHeight="1">
       <c r="A73" s="5">
-        <v>500403.0</v>
+        <v>500403</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>339</v>
@@ -3833,9 +3856,9 @@
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:12" ht="15.75" customHeight="1">
       <c r="A74" s="5">
-        <v>25016.0</v>
+        <v>25016</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>340</v>
@@ -3855,9 +3878,9 @@
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:12" ht="15.75" customHeight="1">
       <c r="A75" s="5">
-        <v>50245.0</v>
+        <v>50245</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>341</v>
@@ -3891,9 +3914,9 @@
       </c>
       <c r="L75" s="10"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:12" ht="15.75" customHeight="1">
       <c r="A76" s="5">
-        <v>500391.0</v>
+        <v>500391</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>348</v>
@@ -3913,9 +3936,9 @@
       <c r="K76" s="10"/>
       <c r="L76" s="10"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:12" ht="15.75" customHeight="1">
       <c r="A77" s="5">
-        <v>50367.0</v>
+        <v>50367</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>349</v>
@@ -3949,9 +3972,9 @@
       </c>
       <c r="L77" s="10"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:12" ht="15.75" customHeight="1">
       <c r="A78" s="5">
-        <v>25022.0</v>
+        <v>25022</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>355</v>
@@ -3971,9 +3994,9 @@
       <c r="K78" s="10"/>
       <c r="L78" s="10"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:12" ht="15.75" customHeight="1">
       <c r="A79" s="5">
-        <v>25034.0</v>
+        <v>25034</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>356</v>
@@ -4005,9 +4028,9 @@
       <c r="K79" s="9"/>
       <c r="L79" s="10"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:12" ht="15.75" customHeight="1">
       <c r="A80" s="5">
-        <v>50003.0</v>
+        <v>50003</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>362</v>
@@ -4027,9 +4050,9 @@
       <c r="K80" s="10"/>
       <c r="L80" s="10"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:12" ht="15.75" customHeight="1">
       <c r="A81" s="5">
-        <v>50038.0</v>
+        <v>50038</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>363</v>
@@ -4049,9 +4072,9 @@
       <c r="K81" s="10"/>
       <c r="L81" s="10"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:12" ht="15.75" customHeight="1">
       <c r="A82" s="5">
-        <v>50020.0</v>
+        <v>50020</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>311</v>
@@ -4071,9 +4094,9 @@
       <c r="K82" s="10"/>
       <c r="L82" s="10"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:12" ht="15.75" customHeight="1">
       <c r="A83" s="5">
-        <v>50008.0</v>
+        <v>50008</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>364</v>
@@ -4093,9 +4116,9 @@
       <c r="K83" s="10"/>
       <c r="L83" s="10"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:12" ht="15.75" customHeight="1">
       <c r="A84" s="5">
-        <v>500395.0</v>
+        <v>500395</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>365</v>
@@ -4115,9 +4138,9 @@
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:12" ht="15.75" customHeight="1">
       <c r="A85" s="5">
-        <v>25059.0</v>
+        <v>25059</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>366</v>
@@ -4137,9 +4160,9 @@
       <c r="K85" s="10"/>
       <c r="L85" s="10"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:12" ht="15.75" customHeight="1">
       <c r="A86" s="5">
-        <v>5021.0</v>
+        <v>5021</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>367</v>
@@ -4161,9 +4184,9 @@
       <c r="K86" s="10"/>
       <c r="L86" s="10"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:12" ht="15.75" customHeight="1">
       <c r="A87" s="5">
-        <v>50016.0</v>
+        <v>50016</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>365</v>
@@ -4183,9 +4206,9 @@
       <c r="K87" s="10"/>
       <c r="L87" s="10"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:12" ht="15.75" customHeight="1">
       <c r="A88" s="5">
-        <v>50015.0</v>
+        <v>50015</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>369</v>
@@ -4205,9 +4228,9 @@
       <c r="K88" s="10"/>
       <c r="L88" s="10"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:12" ht="15.75" customHeight="1">
       <c r="A89" s="5">
-        <v>50030.0</v>
+        <v>50030</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>370</v>
@@ -4227,9 +4250,9 @@
       <c r="K89" s="10"/>
       <c r="L89" s="10"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:12" ht="15.75" customHeight="1">
       <c r="A90" s="5">
-        <v>50160.0</v>
+        <v>50160</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>371</v>
@@ -4249,9 +4272,9 @@
       <c r="K90" s="10"/>
       <c r="L90" s="10"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:12" ht="15.75" customHeight="1">
       <c r="A91" s="5">
-        <v>50048.0</v>
+        <v>50048</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>372</v>
@@ -4271,9 +4294,9 @@
       <c r="K91" s="10"/>
       <c r="L91" s="10"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:12" ht="15.75" customHeight="1">
       <c r="A92" s="5">
-        <v>50063.0</v>
+        <v>50063</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>373</v>
@@ -4293,9 +4316,9 @@
       <c r="K92" s="10"/>
       <c r="L92" s="10"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:12" ht="15.75" customHeight="1">
       <c r="A93" s="5">
-        <v>25036.0</v>
+        <v>25036</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>374</v>
@@ -4315,9 +4338,9 @@
       <c r="K93" s="10"/>
       <c r="L93" s="10"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:12" ht="15.75" customHeight="1">
       <c r="A94" s="5">
-        <v>50365.0</v>
+        <v>50365</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>375</v>
@@ -4337,9 +4360,9 @@
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:12" ht="15.75" customHeight="1">
       <c r="A95" s="5">
-        <v>50140.0</v>
+        <v>50140</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>376</v>
@@ -4361,9 +4384,9 @@
       <c r="K95" s="10"/>
       <c r="L95" s="10"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:12" ht="15.75" customHeight="1">
       <c r="A96" s="5">
-        <v>500388.0</v>
+        <v>500388</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>369</v>
@@ -4383,9 +4406,9 @@
       <c r="K96" s="10"/>
       <c r="L96" s="10"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:12" ht="15.75" customHeight="1">
       <c r="A97" s="5">
-        <v>50189.0</v>
+        <v>50189</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>378</v>
@@ -4405,9 +4428,9 @@
       <c r="K97" s="10"/>
       <c r="L97" s="10"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:12" ht="15.75" customHeight="1">
       <c r="A98" s="5">
-        <v>500392.0</v>
+        <v>500392</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>379</v>
@@ -4427,9 +4450,9 @@
       <c r="K98" s="10"/>
       <c r="L98" s="10"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:12" ht="15.75" customHeight="1">
       <c r="A99" s="5">
-        <v>25048.0</v>
+        <v>25048</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>380</v>
@@ -4449,9 +4472,9 @@
       <c r="K99" s="10"/>
       <c r="L99" s="10"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:12" ht="15.75" customHeight="1">
       <c r="A100" s="5">
-        <v>50363.0</v>
+        <v>50363</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>381</v>
@@ -4471,9 +4494,9 @@
       <c r="K100" s="10"/>
       <c r="L100" s="10"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:12" ht="15.75" customHeight="1">
       <c r="A101" s="5">
-        <v>25003.0</v>
+        <v>25003</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>382</v>
@@ -4493,9 +4516,9 @@
       <c r="K101" s="10"/>
       <c r="L101" s="10"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:12" ht="15.75" customHeight="1">
       <c r="A102" s="5">
-        <v>500394.0</v>
+        <v>500394</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>383</v>
@@ -4515,9 +4538,9 @@
       <c r="K102" s="10"/>
       <c r="L102" s="10"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:12" ht="15.75" customHeight="1">
       <c r="A103" s="5">
-        <v>50018.0</v>
+        <v>50018</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>384</v>
@@ -4537,9 +4560,9 @@
       <c r="K103" s="10"/>
       <c r="L103" s="10"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:12" ht="15.75" customHeight="1">
       <c r="A104" s="5">
-        <v>25072.0</v>
+        <v>25072</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>385</v>
@@ -4559,9 +4582,9 @@
       <c r="K104" s="10"/>
       <c r="L104" s="10"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:12" ht="15.75" customHeight="1">
       <c r="A105" s="5">
-        <v>25019.0</v>
+        <v>25019</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>386</v>
@@ -4581,9 +4604,9 @@
       <c r="K105" s="10"/>
       <c r="L105" s="10"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:12" ht="15.75" customHeight="1">
       <c r="A106" s="5">
-        <v>50323.0</v>
+        <v>50323</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>387</v>
@@ -4603,9 +4626,9 @@
       <c r="K106" s="10"/>
       <c r="L106" s="10"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:12" ht="15.75" customHeight="1">
       <c r="A107" s="5">
-        <v>25001.0</v>
+        <v>25001</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>388</v>
@@ -4625,9 +4648,9 @@
       <c r="K107" s="10"/>
       <c r="L107" s="10"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:12" ht="15.75" customHeight="1">
       <c r="A108" s="5">
-        <v>25028.0</v>
+        <v>25028</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>389</v>
@@ -4647,9 +4670,9 @@
       <c r="K108" s="10"/>
       <c r="L108" s="10"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:12" ht="15.75" customHeight="1">
       <c r="A109" s="5">
-        <v>25063.0</v>
+        <v>25063</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>390</v>
@@ -4669,9 +4692,9 @@
       <c r="K109" s="10"/>
       <c r="L109" s="10"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:12" ht="15.75" customHeight="1">
       <c r="A110" s="5">
-        <v>50014.0</v>
+        <v>50014</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>391</v>
@@ -4691,9 +4714,9 @@
       <c r="K110" s="10"/>
       <c r="L110" s="10"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:12" ht="15.75" customHeight="1">
       <c r="A111" s="5">
-        <v>500402.0</v>
+        <v>500402</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>392</v>
@@ -4713,9 +4736,9 @@
       <c r="K111" s="10"/>
       <c r="L111" s="10"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:12" ht="15.75" customHeight="1">
       <c r="A112" s="5">
-        <v>25037.0</v>
+        <v>25037</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>393</v>
@@ -4735,9 +4758,9 @@
       <c r="K112" s="10"/>
       <c r="L112" s="10"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:12" ht="15.75" customHeight="1">
       <c r="A113" s="5">
-        <v>50166.0</v>
+        <v>50166</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>394</v>
@@ -4757,9 +4780,9 @@
       <c r="K113" s="10"/>
       <c r="L113" s="10"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:12" ht="15.75" customHeight="1">
       <c r="A114" s="5">
-        <v>500404.0</v>
+        <v>500404</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>396</v>
@@ -4779,9 +4802,9 @@
       <c r="K114" s="10"/>
       <c r="L114" s="10"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:12" ht="15.75" customHeight="1">
       <c r="A115" s="5">
-        <v>50253.0</v>
+        <v>50253</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>397</v>
@@ -4801,9 +4824,9 @@
       <c r="K115" s="10"/>
       <c r="L115" s="10"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:12" ht="15.75" customHeight="1">
       <c r="A116" s="5">
-        <v>500393.0</v>
+        <v>500393</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>398</v>
@@ -4823,9 +4846,9 @@
       <c r="K116" s="10"/>
       <c r="L116" s="10"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:12" ht="15.75" customHeight="1">
       <c r="A117" s="5">
-        <v>50303.0</v>
+        <v>50303</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>399</v>
@@ -4845,9 +4868,9 @@
       <c r="K117" s="10"/>
       <c r="L117" s="10"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:12" ht="15.75" customHeight="1">
       <c r="A118" s="5">
-        <v>25067.0</v>
+        <v>25067</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>400</v>
@@ -4867,9 +4890,9 @@
       <c r="K118" s="10"/>
       <c r="L118" s="10"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:12" ht="15.75" customHeight="1">
       <c r="A119" s="5">
-        <v>50220.0</v>
+        <v>50220</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>401</v>
@@ -4889,9 +4912,9 @@
       <c r="K119" s="10"/>
       <c r="L119" s="10"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:12" ht="15.75" customHeight="1">
       <c r="A120" s="5">
-        <v>25050.0</v>
+        <v>25050</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>402</v>
@@ -4911,9 +4934,9 @@
       <c r="K120" s="10"/>
       <c r="L120" s="10"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:12" ht="15.75" customHeight="1">
       <c r="A121" s="5">
-        <v>25042.0</v>
+        <v>25042</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>403</v>
@@ -4933,9 +4956,9 @@
       <c r="K121" s="10"/>
       <c r="L121" s="10"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:12" ht="15.75" customHeight="1">
       <c r="A122" s="5">
-        <v>25013.0</v>
+        <v>25013</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>404</v>
@@ -4955,9 +4978,9 @@
       <c r="K122" s="10"/>
       <c r="L122" s="10"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:12" ht="15.75" customHeight="1">
       <c r="A123" s="5">
-        <v>58337.0</v>
+        <v>58337</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>405</v>
@@ -4977,9 +5000,9 @@
       <c r="K123" s="10"/>
       <c r="L123" s="10"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:12" ht="15.75" customHeight="1">
       <c r="A124" s="5">
-        <v>25062.0</v>
+        <v>25062</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>407</v>
@@ -4999,9 +5022,9 @@
       <c r="K124" s="10"/>
       <c r="L124" s="10"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:12" ht="15.75" customHeight="1">
       <c r="A125" s="5">
-        <v>25047.0</v>
+        <v>25047</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>408</v>
@@ -5023,9 +5046,9 @@
       <c r="K125" s="10"/>
       <c r="L125" s="10"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:12" ht="15.75" customHeight="1">
       <c r="A126" s="5">
-        <v>25068.0</v>
+        <v>25068</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>410</v>
@@ -5045,9 +5068,9 @@
       <c r="K126" s="10"/>
       <c r="L126" s="10"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:12" ht="15.75" customHeight="1">
       <c r="A127" s="5">
-        <v>500396.0</v>
+        <v>500396</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>391</v>
@@ -5067,9 +5090,9 @@
       <c r="K127" s="10"/>
       <c r="L127" s="10"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:12" ht="15.75" customHeight="1">
       <c r="A128" s="5">
-        <v>25025.0</v>
+        <v>25025</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>411</v>
@@ -5089,9 +5112,9 @@
       <c r="K128" s="10"/>
       <c r="L128" s="10"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:12" ht="15.75" customHeight="1">
       <c r="A129" s="5">
-        <v>50381.0</v>
+        <v>50381</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>412</v>
@@ -5111,9 +5134,9 @@
       <c r="K129" s="10"/>
       <c r="L129" s="10"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:12" ht="15.75" customHeight="1">
       <c r="A130" s="5">
-        <v>50343.0</v>
+        <v>50343</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>413</v>
@@ -5133,9 +5156,9 @@
       <c r="K130" s="10"/>
       <c r="L130" s="10"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:12" ht="15.75" customHeight="1">
       <c r="A131" s="5">
-        <v>25071.0</v>
+        <v>25071</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>414</v>
@@ -5155,9 +5178,9 @@
       <c r="K131" s="10"/>
       <c r="L131" s="10"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:12" ht="15.75" customHeight="1">
       <c r="A132" s="5">
-        <v>25073.0</v>
+        <v>25073</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>415</v>
@@ -5177,9 +5200,9 @@
       <c r="K132" s="10"/>
       <c r="L132" s="10"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:12" ht="15.75" customHeight="1">
       <c r="A133" s="5">
-        <v>50364.0</v>
+        <v>50364</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>416</v>
@@ -5199,9 +5222,9 @@
       <c r="K133" s="10"/>
       <c r="L133" s="10"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:12" ht="15.75" customHeight="1">
       <c r="A134" s="5">
-        <v>25055.0</v>
+        <v>25055</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>373</v>
@@ -5221,9 +5244,9 @@
       <c r="K134" s="10"/>
       <c r="L134" s="10"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:12" ht="15.75" customHeight="1">
       <c r="A135" s="5">
-        <v>500398.0</v>
+        <v>500398</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>417</v>
@@ -5243,9 +5266,9 @@
       <c r="K135" s="10"/>
       <c r="L135" s="10"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:12" ht="15.75" customHeight="1">
       <c r="A136" s="5">
-        <v>25035.0</v>
+        <v>25035</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>418</v>
@@ -5267,9 +5290,9 @@
       <c r="K136" s="10"/>
       <c r="L136" s="10"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:12" ht="15.75" customHeight="1">
       <c r="A137" s="5">
-        <v>50026.0</v>
+        <v>50026</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>420</v>
@@ -5289,9 +5312,9 @@
       <c r="K137" s="10"/>
       <c r="L137" s="10"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:12" ht="15.75" customHeight="1">
       <c r="A138" s="5">
-        <v>500397.0</v>
+        <v>500397</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>420</v>
@@ -5311,9 +5334,9 @@
       <c r="K138" s="10"/>
       <c r="L138" s="10"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:12" ht="15.75" customHeight="1">
       <c r="A139" s="5">
-        <v>50289.0</v>
+        <v>50289</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>421</v>
@@ -5333,9 +5356,9 @@
       <c r="K139" s="10"/>
       <c r="L139" s="10"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:12" ht="15.75" customHeight="1">
       <c r="A140" s="5">
-        <v>50358.0</v>
+        <v>50358</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>422</v>
@@ -5355,9 +5378,9 @@
       <c r="K140" s="10"/>
       <c r="L140" s="10"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:12" ht="15.75" customHeight="1">
       <c r="A141" s="5">
-        <v>50031.0</v>
+        <v>50031</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>423</v>
@@ -5377,9 +5400,9 @@
       <c r="K141" s="10"/>
       <c r="L141" s="10"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:12" ht="15.75" customHeight="1">
       <c r="A142" s="5">
-        <v>50374.0</v>
+        <v>50374</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>424</v>
@@ -5399,9 +5422,9 @@
       <c r="K142" s="10"/>
       <c r="L142" s="10"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:12" ht="15.75" customHeight="1">
       <c r="A143" s="5">
-        <v>25005.0</v>
+        <v>25005</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>425</v>
@@ -5421,9 +5444,9 @@
       <c r="K143" s="10"/>
       <c r="L143" s="10"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:12" ht="15.75" customHeight="1">
       <c r="A144" s="5">
-        <v>25057.0</v>
+        <v>25057</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>425</v>
@@ -5443,9 +5466,9 @@
       <c r="K144" s="10"/>
       <c r="L144" s="10"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:12" ht="15.75" customHeight="1">
       <c r="A145" s="5">
-        <v>50350.0</v>
+        <v>50350</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>426</v>
@@ -5465,9 +5488,9 @@
       <c r="K145" s="10"/>
       <c r="L145" s="10"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:12" ht="15.75" customHeight="1">
       <c r="A146" s="5">
-        <v>50192.0</v>
+        <v>50192</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>428</v>
@@ -5487,9 +5510,9 @@
       <c r="K146" s="10"/>
       <c r="L146" s="10"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:12" ht="15.75" customHeight="1">
       <c r="A147" s="5">
-        <v>50065.0</v>
+        <v>50065</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>429</v>
@@ -5509,9 +5532,9 @@
       <c r="K147" s="10"/>
       <c r="L147" s="10"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="A148" s="5">
-        <v>50281.0</v>
+        <v>50281</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>430</v>
@@ -5531,9 +5554,9 @@
       <c r="K148" s="10"/>
       <c r="L148" s="10"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="A149" s="5">
-        <v>50336.0</v>
+        <v>50336</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>431</v>
@@ -5553,21 +5576,33 @@
       <c r="K149" s="10"/>
       <c r="L149" s="10"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="10"/>
-      <c r="B150" s="10"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="10"/>
+    <row r="150" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A150" s="10">
+        <v>25075</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C150" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>433</v>
+      </c>
       <c r="E150" s="11"/>
-      <c r="F150" s="10"/>
-      <c r="G150" s="10"/>
+      <c r="F150" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>434</v>
+      </c>
       <c r="H150" s="10"/>
       <c r="I150" s="10"/>
       <c r="J150" s="10"/>
       <c r="K150" s="10"/>
       <c r="L150" s="10"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:12" ht="15.75" customHeight="1">
       <c r="A151" s="10"/>
       <c r="B151" s="10"/>
       <c r="C151" s="7"/>
@@ -5581,7 +5616,7 @@
       <c r="K151" s="10"/>
       <c r="L151" s="10"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:12" ht="15.75" customHeight="1">
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="7"/>
@@ -5595,7 +5630,7 @@
       <c r="K152" s="10"/>
       <c r="L152" s="10"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:12" ht="15.75" customHeight="1">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="7"/>
@@ -5609,7 +5644,7 @@
       <c r="K153" s="10"/>
       <c r="L153" s="10"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="7"/>
@@ -5623,7 +5658,7 @@
       <c r="K154" s="10"/>
       <c r="L154" s="10"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="7"/>
@@ -5637,7 +5672,7 @@
       <c r="K155" s="10"/>
       <c r="L155" s="10"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
       <c r="C156" s="7"/>
@@ -5651,7 +5686,7 @@
       <c r="K156" s="10"/>
       <c r="L156" s="10"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:12" ht="15.75" customHeight="1">
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="7"/>
@@ -5665,7 +5700,7 @@
       <c r="K157" s="10"/>
       <c r="L157" s="10"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:12" ht="15.75" customHeight="1">
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="7"/>
@@ -5679,7 +5714,7 @@
       <c r="K158" s="10"/>
       <c r="L158" s="10"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:12" ht="15.75" customHeight="1">
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="7"/>
@@ -5693,7 +5728,7 @@
       <c r="K159" s="10"/>
       <c r="L159" s="10"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:12" ht="15.75" customHeight="1">
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="7"/>
@@ -5707,7 +5742,7 @@
       <c r="K160" s="10"/>
       <c r="L160" s="10"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:12" ht="15.75" customHeight="1">
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="7"/>
@@ -5721,7 +5756,7 @@
       <c r="K161" s="10"/>
       <c r="L161" s="10"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:12" ht="15.75" customHeight="1">
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="7"/>
@@ -5735,7 +5770,7 @@
       <c r="K162" s="10"/>
       <c r="L162" s="10"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:12" ht="15.75" customHeight="1">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
       <c r="C163" s="7"/>
@@ -5749,7 +5784,7 @@
       <c r="K163" s="10"/>
       <c r="L163" s="10"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:12" ht="15.75" customHeight="1">
       <c r="A164" s="10"/>
       <c r="B164" s="10"/>
       <c r="C164" s="7"/>
@@ -5763,7 +5798,7 @@
       <c r="K164" s="10"/>
       <c r="L164" s="10"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:12" ht="15.75" customHeight="1">
       <c r="A165" s="10"/>
       <c r="B165" s="10"/>
       <c r="C165" s="7"/>
@@ -5777,7 +5812,7 @@
       <c r="K165" s="10"/>
       <c r="L165" s="10"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:12" ht="15.75" customHeight="1">
       <c r="A166" s="10"/>
       <c r="B166" s="10"/>
       <c r="C166" s="7"/>
@@ -5791,7 +5826,7 @@
       <c r="K166" s="10"/>
       <c r="L166" s="10"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:12" ht="15.75" customHeight="1">
       <c r="A167" s="10"/>
       <c r="B167" s="10"/>
       <c r="C167" s="7"/>
@@ -5805,7 +5840,7 @@
       <c r="K167" s="10"/>
       <c r="L167" s="10"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:12" ht="15.75" customHeight="1">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
       <c r="C168" s="7"/>
@@ -5819,7 +5854,7 @@
       <c r="K168" s="10"/>
       <c r="L168" s="10"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:12" ht="15.75" customHeight="1">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
       <c r="C169" s="7"/>
@@ -5833,7 +5868,7 @@
       <c r="K169" s="10"/>
       <c r="L169" s="10"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:12" ht="15.75" customHeight="1">
       <c r="A170" s="10"/>
       <c r="B170" s="10"/>
       <c r="C170" s="7"/>
@@ -5847,7 +5882,7 @@
       <c r="K170" s="10"/>
       <c r="L170" s="10"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:12" ht="15.75" customHeight="1">
       <c r="A171" s="10"/>
       <c r="B171" s="10"/>
       <c r="C171" s="7"/>
@@ -5861,7 +5896,7 @@
       <c r="K171" s="10"/>
       <c r="L171" s="10"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:12" ht="15.75" customHeight="1">
       <c r="A172" s="10"/>
       <c r="B172" s="10"/>
       <c r="C172" s="7"/>
@@ -5875,7 +5910,7 @@
       <c r="K172" s="10"/>
       <c r="L172" s="10"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:12" ht="15.75" customHeight="1">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
       <c r="C173" s="7"/>
@@ -5889,7 +5924,7 @@
       <c r="K173" s="10"/>
       <c r="L173" s="10"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:12" ht="15.75" customHeight="1">
       <c r="A174" s="10"/>
       <c r="B174" s="10"/>
       <c r="C174" s="7"/>
@@ -5903,7 +5938,7 @@
       <c r="K174" s="10"/>
       <c r="L174" s="10"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:12" ht="15.75" customHeight="1">
       <c r="A175" s="10"/>
       <c r="B175" s="10"/>
       <c r="C175" s="7"/>
@@ -5917,7 +5952,7 @@
       <c r="K175" s="10"/>
       <c r="L175" s="10"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:12" ht="15.75" customHeight="1">
       <c r="A176" s="10"/>
       <c r="B176" s="10"/>
       <c r="C176" s="7"/>
@@ -5931,7 +5966,7 @@
       <c r="K176" s="10"/>
       <c r="L176" s="10"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:12" ht="15.75" customHeight="1">
       <c r="A177" s="10"/>
       <c r="B177" s="10"/>
       <c r="C177" s="7"/>
@@ -5945,7 +5980,7 @@
       <c r="K177" s="10"/>
       <c r="L177" s="10"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:12" ht="15.75" customHeight="1">
       <c r="A178" s="10"/>
       <c r="B178" s="10"/>
       <c r="C178" s="7"/>
@@ -5959,7 +5994,7 @@
       <c r="K178" s="10"/>
       <c r="L178" s="10"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:12" ht="15.75" customHeight="1">
       <c r="A179" s="10"/>
       <c r="B179" s="10"/>
       <c r="C179" s="7"/>
@@ -5973,7 +6008,7 @@
       <c r="K179" s="10"/>
       <c r="L179" s="10"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:12" ht="15.75" customHeight="1">
       <c r="A180" s="10"/>
       <c r="B180" s="10"/>
       <c r="C180" s="7"/>
@@ -5987,7 +6022,7 @@
       <c r="K180" s="10"/>
       <c r="L180" s="10"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:12" ht="15.75" customHeight="1">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
       <c r="C181" s="7"/>
@@ -6001,7 +6036,7 @@
       <c r="K181" s="10"/>
       <c r="L181" s="10"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:12" ht="15.75" customHeight="1">
       <c r="A182" s="10"/>
       <c r="B182" s="10"/>
       <c r="C182" s="7"/>
@@ -6015,7 +6050,7 @@
       <c r="K182" s="10"/>
       <c r="L182" s="10"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:12" ht="15.75" customHeight="1">
       <c r="A183" s="10"/>
       <c r="B183" s="10"/>
       <c r="C183" s="7"/>
@@ -6029,7 +6064,7 @@
       <c r="K183" s="10"/>
       <c r="L183" s="10"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:12" ht="15.75" customHeight="1">
       <c r="A184" s="10"/>
       <c r="B184" s="10"/>
       <c r="C184" s="7"/>
@@ -6043,7 +6078,7 @@
       <c r="K184" s="10"/>
       <c r="L184" s="10"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:12" ht="15.75" customHeight="1">
       <c r="A185" s="10"/>
       <c r="B185" s="10"/>
       <c r="C185" s="7"/>
@@ -6057,7 +6092,7 @@
       <c r="K185" s="10"/>
       <c r="L185" s="10"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:12" ht="15.75" customHeight="1">
       <c r="A186" s="10"/>
       <c r="B186" s="10"/>
       <c r="C186" s="7"/>
@@ -6071,7 +6106,7 @@
       <c r="K186" s="10"/>
       <c r="L186" s="10"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:12" ht="15.75" customHeight="1">
       <c r="A187" s="10"/>
       <c r="B187" s="10"/>
       <c r="C187" s="7"/>
@@ -6085,7 +6120,7 @@
       <c r="K187" s="10"/>
       <c r="L187" s="10"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:12" ht="15.75" customHeight="1">
       <c r="A188" s="10"/>
       <c r="B188" s="10"/>
       <c r="C188" s="7"/>
@@ -6099,7 +6134,7 @@
       <c r="K188" s="10"/>
       <c r="L188" s="10"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:12" ht="15.75" customHeight="1">
       <c r="A189" s="10"/>
       <c r="B189" s="10"/>
       <c r="C189" s="7"/>
@@ -6113,7 +6148,7 @@
       <c r="K189" s="10"/>
       <c r="L189" s="10"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:12" ht="15.75" customHeight="1">
       <c r="A190" s="10"/>
       <c r="B190" s="10"/>
       <c r="C190" s="7"/>
@@ -6127,7 +6162,7 @@
       <c r="K190" s="10"/>
       <c r="L190" s="10"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:12" ht="15.75" customHeight="1">
       <c r="A191" s="10"/>
       <c r="B191" s="10"/>
       <c r="C191" s="7"/>
@@ -6141,7 +6176,7 @@
       <c r="K191" s="10"/>
       <c r="L191" s="10"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:12" ht="15.75" customHeight="1">
       <c r="A192" s="10"/>
       <c r="B192" s="10"/>
       <c r="C192" s="7"/>
@@ -6155,7 +6190,7 @@
       <c r="K192" s="10"/>
       <c r="L192" s="10"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:12" ht="15.75" customHeight="1">
       <c r="A193" s="10"/>
       <c r="B193" s="10"/>
       <c r="C193" s="7"/>
@@ -6169,7 +6204,7 @@
       <c r="K193" s="10"/>
       <c r="L193" s="10"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:12" ht="15.75" customHeight="1">
       <c r="A194" s="10"/>
       <c r="B194" s="10"/>
       <c r="C194" s="7"/>
@@ -6183,7 +6218,7 @@
       <c r="K194" s="10"/>
       <c r="L194" s="10"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:12" ht="15.75" customHeight="1">
       <c r="A195" s="10"/>
       <c r="B195" s="10"/>
       <c r="C195" s="7"/>
@@ -6197,7 +6232,7 @@
       <c r="K195" s="10"/>
       <c r="L195" s="10"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:12" ht="15.75" customHeight="1">
       <c r="A196" s="10"/>
       <c r="B196" s="10"/>
       <c r="C196" s="7"/>
@@ -6211,7 +6246,7 @@
       <c r="K196" s="10"/>
       <c r="L196" s="10"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:12" ht="15.75" customHeight="1">
       <c r="A197" s="10"/>
       <c r="B197" s="10"/>
       <c r="C197" s="7"/>
@@ -6225,7 +6260,7 @@
       <c r="K197" s="10"/>
       <c r="L197" s="10"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:12" ht="15.75" customHeight="1">
       <c r="A198" s="10"/>
       <c r="B198" s="10"/>
       <c r="C198" s="7"/>
@@ -6239,7 +6274,7 @@
       <c r="K198" s="10"/>
       <c r="L198" s="10"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:12" ht="15.75" customHeight="1">
       <c r="A199" s="10"/>
       <c r="B199" s="10"/>
       <c r="C199" s="7"/>
@@ -6253,7 +6288,7 @@
       <c r="K199" s="10"/>
       <c r="L199" s="10"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:12" ht="15.75" customHeight="1">
       <c r="A200" s="10"/>
       <c r="B200" s="10"/>
       <c r="C200" s="7"/>
@@ -6267,7 +6302,7 @@
       <c r="K200" s="10"/>
       <c r="L200" s="10"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:12" ht="15.75" customHeight="1">
       <c r="A201" s="10"/>
       <c r="B201" s="10"/>
       <c r="C201" s="7"/>
@@ -6281,7 +6316,7 @@
       <c r="K201" s="10"/>
       <c r="L201" s="10"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:12" ht="15.75" customHeight="1">
       <c r="A202" s="10"/>
       <c r="B202" s="10"/>
       <c r="C202" s="7"/>
@@ -6295,7 +6330,7 @@
       <c r="K202" s="10"/>
       <c r="L202" s="10"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:12" ht="15.75" customHeight="1">
       <c r="A203" s="10"/>
       <c r="B203" s="10"/>
       <c r="C203" s="7"/>
@@ -6309,7 +6344,7 @@
       <c r="K203" s="10"/>
       <c r="L203" s="10"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:12" ht="15.75" customHeight="1">
       <c r="A204" s="10"/>
       <c r="B204" s="10"/>
       <c r="C204" s="7"/>
@@ -6323,7 +6358,7 @@
       <c r="K204" s="10"/>
       <c r="L204" s="10"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:12" ht="15.75" customHeight="1">
       <c r="A205" s="10"/>
       <c r="B205" s="10"/>
       <c r="C205" s="7"/>
@@ -6337,7 +6372,7 @@
       <c r="K205" s="10"/>
       <c r="L205" s="10"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:12" ht="15.75" customHeight="1">
       <c r="A206" s="10"/>
       <c r="B206" s="10"/>
       <c r="C206" s="7"/>
@@ -6351,7 +6386,7 @@
       <c r="K206" s="10"/>
       <c r="L206" s="10"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:12" ht="15.75" customHeight="1">
       <c r="A207" s="10"/>
       <c r="B207" s="10"/>
       <c r="C207" s="7"/>
@@ -6365,7 +6400,7 @@
       <c r="K207" s="10"/>
       <c r="L207" s="10"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:12" ht="15.75" customHeight="1">
       <c r="A208" s="10"/>
       <c r="B208" s="10"/>
       <c r="C208" s="7"/>
@@ -6379,7 +6414,7 @@
       <c r="K208" s="10"/>
       <c r="L208" s="10"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:12" ht="15.75" customHeight="1">
       <c r="A209" s="10"/>
       <c r="B209" s="10"/>
       <c r="C209" s="7"/>
@@ -6393,7 +6428,7 @@
       <c r="K209" s="10"/>
       <c r="L209" s="10"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:12" ht="15.75" customHeight="1">
       <c r="A210" s="10"/>
       <c r="B210" s="10"/>
       <c r="C210" s="7"/>
@@ -6407,7 +6442,7 @@
       <c r="K210" s="10"/>
       <c r="L210" s="10"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:12" ht="15.75" customHeight="1">
       <c r="A211" s="10"/>
       <c r="B211" s="10"/>
       <c r="C211" s="7"/>
@@ -6421,7 +6456,7 @@
       <c r="K211" s="10"/>
       <c r="L211" s="10"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:12" ht="15.75" customHeight="1">
       <c r="A212" s="10"/>
       <c r="B212" s="10"/>
       <c r="C212" s="7"/>
@@ -6435,7 +6470,7 @@
       <c r="K212" s="10"/>
       <c r="L212" s="10"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:12" ht="15.75" customHeight="1">
       <c r="A213" s="10"/>
       <c r="B213" s="10"/>
       <c r="C213" s="7"/>
@@ -6449,7 +6484,7 @@
       <c r="K213" s="10"/>
       <c r="L213" s="10"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:12" ht="15.75" customHeight="1">
       <c r="A214" s="10"/>
       <c r="B214" s="10"/>
       <c r="C214" s="7"/>
@@ -6463,7 +6498,7 @@
       <c r="K214" s="10"/>
       <c r="L214" s="10"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:12" ht="15.75" customHeight="1">
       <c r="A215" s="10"/>
       <c r="B215" s="10"/>
       <c r="C215" s="7"/>
@@ -6477,7 +6512,7 @@
       <c r="K215" s="10"/>
       <c r="L215" s="10"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:12" ht="15.75" customHeight="1">
       <c r="A216" s="10"/>
       <c r="B216" s="10"/>
       <c r="C216" s="7"/>
@@ -6491,7 +6526,7 @@
       <c r="K216" s="10"/>
       <c r="L216" s="10"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:12" ht="15.75" customHeight="1">
       <c r="A217" s="10"/>
       <c r="B217" s="10"/>
       <c r="C217" s="7"/>
@@ -6505,7 +6540,7 @@
       <c r="K217" s="10"/>
       <c r="L217" s="10"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:12" ht="15.75" customHeight="1">
       <c r="A218" s="10"/>
       <c r="B218" s="10"/>
       <c r="C218" s="7"/>
@@ -6519,7 +6554,7 @@
       <c r="K218" s="10"/>
       <c r="L218" s="10"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:12" ht="15.75" customHeight="1">
       <c r="A219" s="10"/>
       <c r="B219" s="10"/>
       <c r="C219" s="7"/>
@@ -6533,7 +6568,7 @@
       <c r="K219" s="10"/>
       <c r="L219" s="10"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:12" ht="15.75" customHeight="1">
       <c r="A220" s="10"/>
       <c r="B220" s="10"/>
       <c r="C220" s="7"/>
@@ -6547,7 +6582,7 @@
       <c r="K220" s="10"/>
       <c r="L220" s="10"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="1:12" ht="15.75" customHeight="1">
       <c r="A221" s="10"/>
       <c r="B221" s="10"/>
       <c r="C221" s="7"/>
@@ -6561,7 +6596,7 @@
       <c r="K221" s="10"/>
       <c r="L221" s="10"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="1:12" ht="15.75" customHeight="1">
       <c r="A222" s="10"/>
       <c r="B222" s="10"/>
       <c r="C222" s="7"/>
@@ -6575,7 +6610,7 @@
       <c r="K222" s="10"/>
       <c r="L222" s="10"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="1:12" ht="15.75" customHeight="1">
       <c r="A223" s="10"/>
       <c r="B223" s="10"/>
       <c r="C223" s="7"/>
@@ -6589,7 +6624,7 @@
       <c r="K223" s="10"/>
       <c r="L223" s="10"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="1:12" ht="15.75" customHeight="1">
       <c r="A224" s="10"/>
       <c r="B224" s="10"/>
       <c r="C224" s="7"/>
@@ -6603,7 +6638,7 @@
       <c r="K224" s="10"/>
       <c r="L224" s="10"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="1:12" ht="15.75" customHeight="1">
       <c r="A225" s="10"/>
       <c r="B225" s="10"/>
       <c r="C225" s="7"/>
@@ -6617,7 +6652,7 @@
       <c r="K225" s="10"/>
       <c r="L225" s="10"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="1:12" ht="15.75" customHeight="1">
       <c r="A226" s="10"/>
       <c r="B226" s="10"/>
       <c r="C226" s="7"/>
@@ -6631,7 +6666,7 @@
       <c r="K226" s="10"/>
       <c r="L226" s="10"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="1:12" ht="15.75" customHeight="1">
       <c r="A227" s="10"/>
       <c r="B227" s="10"/>
       <c r="C227" s="7"/>
@@ -6645,7 +6680,7 @@
       <c r="K227" s="10"/>
       <c r="L227" s="10"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="1:12" ht="15.75" customHeight="1">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="7"/>
@@ -6659,7 +6694,7 @@
       <c r="K228" s="10"/>
       <c r="L228" s="10"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="1:12" ht="15.75" customHeight="1">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="7"/>
@@ -6673,7 +6708,7 @@
       <c r="K229" s="10"/>
       <c r="L229" s="10"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="1:12" ht="15.75" customHeight="1">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="7"/>
@@ -6687,7 +6722,7 @@
       <c r="K230" s="10"/>
       <c r="L230" s="10"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="1:12" ht="15.75" customHeight="1">
       <c r="A231" s="10"/>
       <c r="B231" s="10"/>
       <c r="C231" s="7"/>
@@ -6701,7 +6736,7 @@
       <c r="K231" s="10"/>
       <c r="L231" s="10"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="1:12" ht="15.75" customHeight="1">
       <c r="A232" s="10"/>
       <c r="B232" s="10"/>
       <c r="C232" s="7"/>
@@ -6715,7 +6750,7 @@
       <c r="K232" s="10"/>
       <c r="L232" s="10"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="1:12" ht="15.75" customHeight="1">
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="7"/>
@@ -6729,7 +6764,7 @@
       <c r="K233" s="10"/>
       <c r="L233" s="10"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="1:12" ht="15.75" customHeight="1">
       <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="7"/>
@@ -6743,7 +6778,7 @@
       <c r="K234" s="10"/>
       <c r="L234" s="10"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="1:12" ht="15.75" customHeight="1">
       <c r="A235" s="10"/>
       <c r="B235" s="10"/>
       <c r="C235" s="7"/>
@@ -6757,7 +6792,7 @@
       <c r="K235" s="10"/>
       <c r="L235" s="10"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="1:12" ht="15.75" customHeight="1">
       <c r="A236" s="10"/>
       <c r="B236" s="10"/>
       <c r="C236" s="7"/>
@@ -6771,7 +6806,7 @@
       <c r="K236" s="10"/>
       <c r="L236" s="10"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="1:12" ht="15.75" customHeight="1">
       <c r="A237" s="10"/>
       <c r="B237" s="10"/>
       <c r="C237" s="7"/>
@@ -6785,7 +6820,7 @@
       <c r="K237" s="10"/>
       <c r="L237" s="10"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="1:12" ht="15.75" customHeight="1">
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="7"/>
@@ -6799,7 +6834,7 @@
       <c r="K238" s="10"/>
       <c r="L238" s="10"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="1:12" ht="15.75" customHeight="1">
       <c r="A239" s="10"/>
       <c r="B239" s="10"/>
       <c r="C239" s="7"/>
@@ -6813,7 +6848,7 @@
       <c r="K239" s="10"/>
       <c r="L239" s="10"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="1:12" ht="15.75" customHeight="1">
       <c r="A240" s="10"/>
       <c r="B240" s="10"/>
       <c r="C240" s="7"/>
@@ -6827,7 +6862,7 @@
       <c r="K240" s="10"/>
       <c r="L240" s="10"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="1:12" ht="15.75" customHeight="1">
       <c r="A241" s="10"/>
       <c r="B241" s="10"/>
       <c r="C241" s="7"/>
@@ -6841,7 +6876,7 @@
       <c r="K241" s="10"/>
       <c r="L241" s="10"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="1:12" ht="15.75" customHeight="1">
       <c r="A242" s="10"/>
       <c r="B242" s="10"/>
       <c r="C242" s="7"/>
@@ -6855,7 +6890,7 @@
       <c r="K242" s="10"/>
       <c r="L242" s="10"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="1:12" ht="15.75" customHeight="1">
       <c r="A243" s="10"/>
       <c r="B243" s="10"/>
       <c r="C243" s="7"/>
@@ -6869,7 +6904,7 @@
       <c r="K243" s="10"/>
       <c r="L243" s="10"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="1:12" ht="15.75" customHeight="1">
       <c r="A244" s="10"/>
       <c r="B244" s="10"/>
       <c r="C244" s="7"/>
@@ -6883,7 +6918,7 @@
       <c r="K244" s="10"/>
       <c r="L244" s="10"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="1:12" ht="15.75" customHeight="1">
       <c r="A245" s="10"/>
       <c r="B245" s="10"/>
       <c r="C245" s="7"/>
@@ -6897,7 +6932,7 @@
       <c r="K245" s="10"/>
       <c r="L245" s="10"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="1:12" ht="15.75" customHeight="1">
       <c r="A246" s="10"/>
       <c r="B246" s="10"/>
       <c r="C246" s="7"/>
@@ -6911,7 +6946,7 @@
       <c r="K246" s="10"/>
       <c r="L246" s="10"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="1:12" ht="15.75" customHeight="1">
       <c r="A247" s="10"/>
       <c r="B247" s="10"/>
       <c r="C247" s="7"/>
@@ -6925,7 +6960,7 @@
       <c r="K247" s="10"/>
       <c r="L247" s="10"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="1:12" ht="15.75" customHeight="1">
       <c r="A248" s="10"/>
       <c r="B248" s="10"/>
       <c r="C248" s="7"/>
@@ -6939,7 +6974,7 @@
       <c r="K248" s="10"/>
       <c r="L248" s="10"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="1:12" ht="15.75" customHeight="1">
       <c r="A249" s="10"/>
       <c r="B249" s="10"/>
       <c r="C249" s="7"/>
@@ -6953,7 +6988,7 @@
       <c r="K249" s="10"/>
       <c r="L249" s="10"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="1:12" ht="15.75" customHeight="1">
       <c r="A250" s="10"/>
       <c r="B250" s="10"/>
       <c r="C250" s="7"/>
@@ -6967,7 +7002,7 @@
       <c r="K250" s="10"/>
       <c r="L250" s="10"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" spans="1:12" ht="15.75" customHeight="1">
       <c r="A251" s="10"/>
       <c r="B251" s="10"/>
       <c r="C251" s="7"/>
@@ -6981,7 +7016,7 @@
       <c r="K251" s="10"/>
       <c r="L251" s="10"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" spans="1:12" ht="15.75" customHeight="1">
       <c r="A252" s="10"/>
       <c r="B252" s="10"/>
       <c r="C252" s="7"/>
@@ -6995,7 +7030,7 @@
       <c r="K252" s="10"/>
       <c r="L252" s="10"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" spans="1:12" ht="15.75" customHeight="1">
       <c r="A253" s="10"/>
       <c r="B253" s="10"/>
       <c r="C253" s="7"/>
@@ -7009,7 +7044,7 @@
       <c r="K253" s="10"/>
       <c r="L253" s="10"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" spans="1:12" ht="15.75" customHeight="1">
       <c r="A254" s="10"/>
       <c r="B254" s="10"/>
       <c r="C254" s="7"/>
@@ -7023,7 +7058,7 @@
       <c r="K254" s="10"/>
       <c r="L254" s="10"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" spans="1:12" ht="15.75" customHeight="1">
       <c r="A255" s="10"/>
       <c r="B255" s="10"/>
       <c r="C255" s="7"/>
@@ -7037,7 +7072,7 @@
       <c r="K255" s="10"/>
       <c r="L255" s="10"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" spans="1:12" ht="15.75" customHeight="1">
       <c r="A256" s="10"/>
       <c r="B256" s="10"/>
       <c r="C256" s="7"/>
@@ -7051,7 +7086,7 @@
       <c r="K256" s="10"/>
       <c r="L256" s="10"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" spans="1:12" ht="15.75" customHeight="1">
       <c r="A257" s="10"/>
       <c r="B257" s="10"/>
       <c r="C257" s="7"/>
@@ -7065,7 +7100,7 @@
       <c r="K257" s="10"/>
       <c r="L257" s="10"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" spans="1:12" ht="15.75" customHeight="1">
       <c r="A258" s="10"/>
       <c r="B258" s="10"/>
       <c r="C258" s="7"/>
@@ -7079,7 +7114,7 @@
       <c r="K258" s="10"/>
       <c r="L258" s="10"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" spans="1:12" ht="15.75" customHeight="1">
       <c r="A259" s="10"/>
       <c r="B259" s="10"/>
       <c r="C259" s="7"/>
@@ -7093,7 +7128,7 @@
       <c r="K259" s="10"/>
       <c r="L259" s="10"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" spans="1:12" ht="15.75" customHeight="1">
       <c r="A260" s="10"/>
       <c r="B260" s="10"/>
       <c r="C260" s="7"/>
@@ -7107,7 +7142,7 @@
       <c r="K260" s="10"/>
       <c r="L260" s="10"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" spans="1:12" ht="15.75" customHeight="1">
       <c r="A261" s="10"/>
       <c r="B261" s="10"/>
       <c r="C261" s="7"/>
@@ -7121,7 +7156,7 @@
       <c r="K261" s="10"/>
       <c r="L261" s="10"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" spans="1:12" ht="15.75" customHeight="1">
       <c r="A262" s="10"/>
       <c r="B262" s="10"/>
       <c r="C262" s="7"/>
@@ -7135,7 +7170,7 @@
       <c r="K262" s="10"/>
       <c r="L262" s="10"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" spans="1:12" ht="15.75" customHeight="1">
       <c r="A263" s="10"/>
       <c r="B263" s="10"/>
       <c r="C263" s="7"/>
@@ -7149,7 +7184,7 @@
       <c r="K263" s="10"/>
       <c r="L263" s="10"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" spans="1:12" ht="15.75" customHeight="1">
       <c r="A264" s="10"/>
       <c r="B264" s="10"/>
       <c r="C264" s="7"/>
@@ -7163,7 +7198,7 @@
       <c r="K264" s="10"/>
       <c r="L264" s="10"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" spans="1:12" ht="15.75" customHeight="1">
       <c r="A265" s="10"/>
       <c r="B265" s="10"/>
       <c r="C265" s="7"/>
@@ -7177,7 +7212,7 @@
       <c r="K265" s="10"/>
       <c r="L265" s="10"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" spans="1:12" ht="15.75" customHeight="1">
       <c r="A266" s="10"/>
       <c r="B266" s="10"/>
       <c r="C266" s="7"/>
@@ -7191,7 +7226,7 @@
       <c r="K266" s="10"/>
       <c r="L266" s="10"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" spans="1:12" ht="15.75" customHeight="1">
       <c r="A267" s="10"/>
       <c r="B267" s="10"/>
       <c r="C267" s="7"/>
@@ -7205,7 +7240,7 @@
       <c r="K267" s="10"/>
       <c r="L267" s="10"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" spans="1:12" ht="15.75" customHeight="1">
       <c r="A268" s="10"/>
       <c r="B268" s="10"/>
       <c r="C268" s="7"/>
@@ -7219,7 +7254,7 @@
       <c r="K268" s="10"/>
       <c r="L268" s="10"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" spans="1:12" ht="15.75" customHeight="1">
       <c r="A269" s="10"/>
       <c r="B269" s="10"/>
       <c r="C269" s="7"/>
@@ -7233,7 +7268,7 @@
       <c r="K269" s="10"/>
       <c r="L269" s="10"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" spans="1:12" ht="15.75" customHeight="1">
       <c r="A270" s="10"/>
       <c r="B270" s="10"/>
       <c r="C270" s="7"/>
@@ -7247,7 +7282,7 @@
       <c r="K270" s="10"/>
       <c r="L270" s="10"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" spans="1:12" ht="15.75" customHeight="1">
       <c r="A271" s="10"/>
       <c r="B271" s="10"/>
       <c r="C271" s="7"/>
@@ -7261,7 +7296,7 @@
       <c r="K271" s="10"/>
       <c r="L271" s="10"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" spans="1:12" ht="15.75" customHeight="1">
       <c r="A272" s="10"/>
       <c r="B272" s="10"/>
       <c r="C272" s="7"/>
@@ -7275,7 +7310,7 @@
       <c r="K272" s="10"/>
       <c r="L272" s="10"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" spans="1:12" ht="15.75" customHeight="1">
       <c r="A273" s="10"/>
       <c r="B273" s="10"/>
       <c r="C273" s="7"/>
@@ -7289,7 +7324,7 @@
       <c r="K273" s="10"/>
       <c r="L273" s="10"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" spans="1:12" ht="15.75" customHeight="1">
       <c r="A274" s="10"/>
       <c r="B274" s="10"/>
       <c r="C274" s="7"/>
@@ -7303,7 +7338,7 @@
       <c r="K274" s="10"/>
       <c r="L274" s="10"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" spans="1:12" ht="15.75" customHeight="1">
       <c r="A275" s="10"/>
       <c r="B275" s="10"/>
       <c r="C275" s="7"/>
@@ -7317,7 +7352,7 @@
       <c r="K275" s="10"/>
       <c r="L275" s="10"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" spans="1:12" ht="15.75" customHeight="1">
       <c r="A276" s="10"/>
       <c r="B276" s="10"/>
       <c r="C276" s="7"/>
@@ -7331,7 +7366,7 @@
       <c r="K276" s="10"/>
       <c r="L276" s="10"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" spans="1:12" ht="15.75" customHeight="1">
       <c r="A277" s="10"/>
       <c r="B277" s="10"/>
       <c r="C277" s="7"/>
@@ -7345,7 +7380,7 @@
       <c r="K277" s="10"/>
       <c r="L277" s="10"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" spans="1:12" ht="15.75" customHeight="1">
       <c r="A278" s="10"/>
       <c r="B278" s="10"/>
       <c r="C278" s="7"/>
@@ -7359,7 +7394,7 @@
       <c r="K278" s="10"/>
       <c r="L278" s="10"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" spans="1:12" ht="15.75" customHeight="1">
       <c r="A279" s="10"/>
       <c r="B279" s="10"/>
       <c r="C279" s="7"/>
@@ -7373,7 +7408,7 @@
       <c r="K279" s="10"/>
       <c r="L279" s="10"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" spans="1:12" ht="15.75" customHeight="1">
       <c r="A280" s="10"/>
       <c r="B280" s="10"/>
       <c r="C280" s="7"/>
@@ -7387,7 +7422,7 @@
       <c r="K280" s="10"/>
       <c r="L280" s="10"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" spans="1:12" ht="15.75" customHeight="1">
       <c r="A281" s="10"/>
       <c r="B281" s="10"/>
       <c r="C281" s="7"/>
@@ -7401,7 +7436,7 @@
       <c r="K281" s="10"/>
       <c r="L281" s="10"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" spans="1:12" ht="15.75" customHeight="1">
       <c r="A282" s="10"/>
       <c r="B282" s="10"/>
       <c r="C282" s="7"/>
@@ -7415,7 +7450,7 @@
       <c r="K282" s="10"/>
       <c r="L282" s="10"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" spans="1:12" ht="15.75" customHeight="1">
       <c r="A283" s="10"/>
       <c r="B283" s="10"/>
       <c r="C283" s="7"/>
@@ -7429,7 +7464,7 @@
       <c r="K283" s="10"/>
       <c r="L283" s="10"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" spans="1:12" ht="15.75" customHeight="1">
       <c r="A284" s="10"/>
       <c r="B284" s="10"/>
       <c r="C284" s="7"/>
@@ -7443,7 +7478,7 @@
       <c r="K284" s="10"/>
       <c r="L284" s="10"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" spans="1:12" ht="15.75" customHeight="1">
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="7"/>
@@ -7457,7 +7492,7 @@
       <c r="K285" s="10"/>
       <c r="L285" s="10"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" spans="1:12" ht="15.75" customHeight="1">
       <c r="A286" s="10"/>
       <c r="B286" s="10"/>
       <c r="C286" s="7"/>
@@ -7471,7 +7506,7 @@
       <c r="K286" s="10"/>
       <c r="L286" s="10"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" spans="1:12" ht="15.75" customHeight="1">
       <c r="A287" s="10"/>
       <c r="B287" s="10"/>
       <c r="C287" s="7"/>
@@ -7485,7 +7520,7 @@
       <c r="K287" s="10"/>
       <c r="L287" s="10"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" spans="1:12" ht="15.75" customHeight="1">
       <c r="A288" s="10"/>
       <c r="B288" s="10"/>
       <c r="C288" s="7"/>
@@ -7499,7 +7534,7 @@
       <c r="K288" s="10"/>
       <c r="L288" s="10"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" spans="1:12" ht="15.75" customHeight="1">
       <c r="A289" s="10"/>
       <c r="B289" s="10"/>
       <c r="C289" s="7"/>
@@ -7513,7 +7548,7 @@
       <c r="K289" s="10"/>
       <c r="L289" s="10"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" spans="1:12" ht="15.75" customHeight="1">
       <c r="A290" s="10"/>
       <c r="B290" s="10"/>
       <c r="C290" s="7"/>
@@ -7527,7 +7562,7 @@
       <c r="K290" s="10"/>
       <c r="L290" s="10"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" spans="1:12" ht="15.75" customHeight="1">
       <c r="A291" s="10"/>
       <c r="B291" s="10"/>
       <c r="C291" s="7"/>
@@ -7541,7 +7576,7 @@
       <c r="K291" s="10"/>
       <c r="L291" s="10"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" spans="1:12" ht="15.75" customHeight="1">
       <c r="A292" s="10"/>
       <c r="B292" s="10"/>
       <c r="C292" s="7"/>
@@ -7555,7 +7590,7 @@
       <c r="K292" s="10"/>
       <c r="L292" s="10"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" spans="1:12" ht="15.75" customHeight="1">
       <c r="A293" s="10"/>
       <c r="B293" s="10"/>
       <c r="C293" s="7"/>
@@ -7569,7 +7604,7 @@
       <c r="K293" s="10"/>
       <c r="L293" s="10"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row r="294" spans="1:12" ht="15.75" customHeight="1">
       <c r="A294" s="10"/>
       <c r="B294" s="10"/>
       <c r="C294" s="7"/>
@@ -7583,7 +7618,7 @@
       <c r="K294" s="10"/>
       <c r="L294" s="10"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row r="295" spans="1:12" ht="15.75" customHeight="1">
       <c r="A295" s="10"/>
       <c r="B295" s="10"/>
       <c r="C295" s="7"/>
@@ -7597,7 +7632,7 @@
       <c r="K295" s="10"/>
       <c r="L295" s="10"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row r="296" spans="1:12" ht="15.75" customHeight="1">
       <c r="A296" s="10"/>
       <c r="B296" s="10"/>
       <c r="C296" s="7"/>
@@ -7611,7 +7646,7 @@
       <c r="K296" s="10"/>
       <c r="L296" s="10"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row r="297" spans="1:12" ht="15.75" customHeight="1">
       <c r="A297" s="10"/>
       <c r="B297" s="10"/>
       <c r="C297" s="7"/>
@@ -7625,7 +7660,7 @@
       <c r="K297" s="10"/>
       <c r="L297" s="10"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row r="298" spans="1:12" ht="15.75" customHeight="1">
       <c r="A298" s="10"/>
       <c r="B298" s="10"/>
       <c r="C298" s="7"/>
@@ -7639,7 +7674,7 @@
       <c r="K298" s="10"/>
       <c r="L298" s="10"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row r="299" spans="1:12" ht="15.75" customHeight="1">
       <c r="A299" s="10"/>
       <c r="B299" s="10"/>
       <c r="C299" s="7"/>
@@ -7653,7 +7688,7 @@
       <c r="K299" s="10"/>
       <c r="L299" s="10"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row r="300" spans="1:12" ht="15.75" customHeight="1">
       <c r="A300" s="10"/>
       <c r="B300" s="10"/>
       <c r="C300" s="7"/>
@@ -7667,7 +7702,7 @@
       <c r="K300" s="10"/>
       <c r="L300" s="10"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row r="301" spans="1:12" ht="15.75" customHeight="1">
       <c r="A301" s="10"/>
       <c r="B301" s="10"/>
       <c r="C301" s="7"/>
@@ -7681,7 +7716,7 @@
       <c r="K301" s="10"/>
       <c r="L301" s="10"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row r="302" spans="1:12" ht="15.75" customHeight="1">
       <c r="A302" s="10"/>
       <c r="B302" s="10"/>
       <c r="C302" s="7"/>
@@ -7695,7 +7730,7 @@
       <c r="K302" s="10"/>
       <c r="L302" s="10"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row r="303" spans="1:12" ht="15.75" customHeight="1">
       <c r="A303" s="10"/>
       <c r="B303" s="10"/>
       <c r="C303" s="7"/>
@@ -7709,7 +7744,7 @@
       <c r="K303" s="10"/>
       <c r="L303" s="10"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row r="304" spans="1:12" ht="15.75" customHeight="1">
       <c r="A304" s="10"/>
       <c r="B304" s="10"/>
       <c r="C304" s="7"/>
@@ -7723,7 +7758,7 @@
       <c r="K304" s="10"/>
       <c r="L304" s="10"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row r="305" spans="1:12" ht="15.75" customHeight="1">
       <c r="A305" s="10"/>
       <c r="B305" s="10"/>
       <c r="C305" s="7"/>
@@ -7737,7 +7772,7 @@
       <c r="K305" s="10"/>
       <c r="L305" s="10"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row r="306" spans="1:12" ht="15.75" customHeight="1">
       <c r="A306" s="10"/>
       <c r="B306" s="10"/>
       <c r="C306" s="7"/>
@@ -7751,7 +7786,7 @@
       <c r="K306" s="10"/>
       <c r="L306" s="10"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row r="307" spans="1:12" ht="15.75" customHeight="1">
       <c r="A307" s="10"/>
       <c r="B307" s="10"/>
       <c r="C307" s="7"/>
@@ -7765,7 +7800,7 @@
       <c r="K307" s="10"/>
       <c r="L307" s="10"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row r="308" spans="1:12" ht="15.75" customHeight="1">
       <c r="A308" s="10"/>
       <c r="B308" s="10"/>
       <c r="C308" s="7"/>
@@ -7779,7 +7814,7 @@
       <c r="K308" s="10"/>
       <c r="L308" s="10"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row r="309" spans="1:12" ht="15.75" customHeight="1">
       <c r="A309" s="10"/>
       <c r="B309" s="10"/>
       <c r="C309" s="7"/>
@@ -7793,7 +7828,7 @@
       <c r="K309" s="10"/>
       <c r="L309" s="10"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row r="310" spans="1:12" ht="15.75" customHeight="1">
       <c r="A310" s="10"/>
       <c r="B310" s="10"/>
       <c r="C310" s="7"/>
@@ -7807,7 +7842,7 @@
       <c r="K310" s="10"/>
       <c r="L310" s="10"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row r="311" spans="1:12" ht="15.75" customHeight="1">
       <c r="A311" s="10"/>
       <c r="B311" s="10"/>
       <c r="C311" s="7"/>
@@ -7821,7 +7856,7 @@
       <c r="K311" s="10"/>
       <c r="L311" s="10"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row r="312" spans="1:12" ht="15.75" customHeight="1">
       <c r="A312" s="10"/>
       <c r="B312" s="10"/>
       <c r="C312" s="7"/>
@@ -7835,7 +7870,7 @@
       <c r="K312" s="10"/>
       <c r="L312" s="10"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row r="313" spans="1:12" ht="15.75" customHeight="1">
       <c r="A313" s="10"/>
       <c r="B313" s="10"/>
       <c r="C313" s="7"/>
@@ -7849,7 +7884,7 @@
       <c r="K313" s="10"/>
       <c r="L313" s="10"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row r="314" spans="1:12" ht="15.75" customHeight="1">
       <c r="A314" s="10"/>
       <c r="B314" s="10"/>
       <c r="C314" s="7"/>
@@ -7863,7 +7898,7 @@
       <c r="K314" s="10"/>
       <c r="L314" s="10"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row r="315" spans="1:12" ht="15.75" customHeight="1">
       <c r="A315" s="10"/>
       <c r="B315" s="10"/>
       <c r="C315" s="7"/>
@@ -7877,7 +7912,7 @@
       <c r="K315" s="10"/>
       <c r="L315" s="10"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" spans="1:12" ht="15.75" customHeight="1">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="7"/>
@@ -7891,7 +7926,7 @@
       <c r="K316" s="10"/>
       <c r="L316" s="10"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row r="317" spans="1:12" ht="15.75" customHeight="1">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="7"/>
@@ -7905,7 +7940,7 @@
       <c r="K317" s="10"/>
       <c r="L317" s="10"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row r="318" spans="1:12" ht="15.75" customHeight="1">
       <c r="A318" s="10"/>
       <c r="B318" s="10"/>
       <c r="C318" s="7"/>
@@ -7919,7 +7954,7 @@
       <c r="K318" s="10"/>
       <c r="L318" s="10"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row r="319" spans="1:12" ht="15.75" customHeight="1">
       <c r="A319" s="10"/>
       <c r="B319" s="10"/>
       <c r="C319" s="7"/>
@@ -7933,7 +7968,7 @@
       <c r="K319" s="10"/>
       <c r="L319" s="10"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row r="320" spans="1:12" ht="15.75" customHeight="1">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="7"/>
@@ -7947,7 +7982,7 @@
       <c r="K320" s="10"/>
       <c r="L320" s="10"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row r="321" spans="1:12" ht="15.75" customHeight="1">
       <c r="A321" s="10"/>
       <c r="B321" s="10"/>
       <c r="C321" s="7"/>
@@ -7961,7 +7996,7 @@
       <c r="K321" s="10"/>
       <c r="L321" s="10"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row r="322" spans="1:12" ht="15.75" customHeight="1">
       <c r="A322" s="10"/>
       <c r="B322" s="10"/>
       <c r="C322" s="7"/>
@@ -7975,7 +8010,7 @@
       <c r="K322" s="10"/>
       <c r="L322" s="10"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row r="323" spans="1:12" ht="15.75" customHeight="1">
       <c r="A323" s="10"/>
       <c r="B323" s="10"/>
       <c r="C323" s="7"/>
@@ -7989,7 +8024,7 @@
       <c r="K323" s="10"/>
       <c r="L323" s="10"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row r="324" spans="1:12" ht="15.75" customHeight="1">
       <c r="A324" s="10"/>
       <c r="B324" s="10"/>
       <c r="C324" s="7"/>
@@ -8003,7 +8038,7 @@
       <c r="K324" s="10"/>
       <c r="L324" s="10"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row r="325" spans="1:12" ht="15.75" customHeight="1">
       <c r="A325" s="10"/>
       <c r="B325" s="10"/>
       <c r="C325" s="7"/>
@@ -8017,7 +8052,7 @@
       <c r="K325" s="10"/>
       <c r="L325" s="10"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row r="326" spans="1:12" ht="15.75" customHeight="1">
       <c r="A326" s="10"/>
       <c r="B326" s="10"/>
       <c r="C326" s="7"/>
@@ -8031,7 +8066,7 @@
       <c r="K326" s="10"/>
       <c r="L326" s="10"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row r="327" spans="1:12" ht="15.75" customHeight="1">
       <c r="A327" s="10"/>
       <c r="B327" s="10"/>
       <c r="C327" s="7"/>
@@ -8045,7 +8080,7 @@
       <c r="K327" s="10"/>
       <c r="L327" s="10"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row r="328" spans="1:12" ht="15.75" customHeight="1">
       <c r="A328" s="10"/>
       <c r="B328" s="10"/>
       <c r="C328" s="7"/>
@@ -8059,7 +8094,7 @@
       <c r="K328" s="10"/>
       <c r="L328" s="10"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row r="329" spans="1:12" ht="15.75" customHeight="1">
       <c r="A329" s="10"/>
       <c r="B329" s="10"/>
       <c r="C329" s="7"/>
@@ -8073,7 +8108,7 @@
       <c r="K329" s="10"/>
       <c r="L329" s="10"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row r="330" spans="1:12" ht="15.75" customHeight="1">
       <c r="A330" s="10"/>
       <c r="B330" s="10"/>
       <c r="C330" s="7"/>
@@ -8087,7 +8122,7 @@
       <c r="K330" s="10"/>
       <c r="L330" s="10"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row r="331" spans="1:12" ht="15.75" customHeight="1">
       <c r="A331" s="10"/>
       <c r="B331" s="10"/>
       <c r="C331" s="7"/>
@@ -8101,7 +8136,7 @@
       <c r="K331" s="10"/>
       <c r="L331" s="10"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row r="332" spans="1:12" ht="15.75" customHeight="1">
       <c r="A332" s="10"/>
       <c r="B332" s="10"/>
       <c r="C332" s="7"/>
@@ -8115,7 +8150,7 @@
       <c r="K332" s="10"/>
       <c r="L332" s="10"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row r="333" spans="1:12" ht="15.75" customHeight="1">
       <c r="A333" s="10"/>
       <c r="B333" s="10"/>
       <c r="C333" s="7"/>
@@ -8129,7 +8164,7 @@
       <c r="K333" s="10"/>
       <c r="L333" s="10"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row r="334" spans="1:12" ht="15.75" customHeight="1">
       <c r="A334" s="10"/>
       <c r="B334" s="10"/>
       <c r="C334" s="7"/>
@@ -8143,7 +8178,7 @@
       <c r="K334" s="10"/>
       <c r="L334" s="10"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row r="335" spans="1:12" ht="15.75" customHeight="1">
       <c r="A335" s="10"/>
       <c r="B335" s="10"/>
       <c r="C335" s="7"/>
@@ -8157,7 +8192,7 @@
       <c r="K335" s="10"/>
       <c r="L335" s="10"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row r="336" spans="1:12" ht="15.75" customHeight="1">
       <c r="A336" s="10"/>
       <c r="B336" s="10"/>
       <c r="C336" s="7"/>
@@ -8171,7 +8206,7 @@
       <c r="K336" s="10"/>
       <c r="L336" s="10"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row r="337" spans="1:12" ht="15.75" customHeight="1">
       <c r="A337" s="10"/>
       <c r="B337" s="10"/>
       <c r="C337" s="7"/>
@@ -8185,7 +8220,7 @@
       <c r="K337" s="10"/>
       <c r="L337" s="10"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row r="338" spans="1:12" ht="15.75" customHeight="1">
       <c r="A338" s="10"/>
       <c r="B338" s="10"/>
       <c r="C338" s="7"/>
@@ -8199,7 +8234,7 @@
       <c r="K338" s="10"/>
       <c r="L338" s="10"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row r="339" spans="1:12" ht="15.75" customHeight="1">
       <c r="A339" s="10"/>
       <c r="B339" s="10"/>
       <c r="C339" s="7"/>
@@ -8213,7 +8248,7 @@
       <c r="K339" s="10"/>
       <c r="L339" s="10"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row r="340" spans="1:12" ht="15.75" customHeight="1">
       <c r="A340" s="10"/>
       <c r="B340" s="10"/>
       <c r="C340" s="7"/>
@@ -8227,7 +8262,7 @@
       <c r="K340" s="10"/>
       <c r="L340" s="10"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row r="341" spans="1:12" ht="15.75" customHeight="1">
       <c r="A341" s="10"/>
       <c r="B341" s="10"/>
       <c r="C341" s="7"/>
@@ -8241,7 +8276,7 @@
       <c r="K341" s="10"/>
       <c r="L341" s="10"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row r="342" spans="1:12" ht="15.75" customHeight="1">
       <c r="A342" s="10"/>
       <c r="B342" s="10"/>
       <c r="C342" s="7"/>
@@ -8255,7 +8290,7 @@
       <c r="K342" s="10"/>
       <c r="L342" s="10"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row r="343" spans="1:12" ht="15.75" customHeight="1">
       <c r="A343" s="10"/>
       <c r="B343" s="10"/>
       <c r="C343" s="7"/>
@@ -8269,7 +8304,7 @@
       <c r="K343" s="10"/>
       <c r="L343" s="10"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row r="344" spans="1:12" ht="15.75" customHeight="1">
       <c r="A344" s="10"/>
       <c r="B344" s="10"/>
       <c r="C344" s="7"/>
@@ -8283,7 +8318,7 @@
       <c r="K344" s="10"/>
       <c r="L344" s="10"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row r="345" spans="1:12" ht="15.75" customHeight="1">
       <c r="A345" s="10"/>
       <c r="B345" s="10"/>
       <c r="C345" s="7"/>
@@ -8297,7 +8332,7 @@
       <c r="K345" s="10"/>
       <c r="L345" s="10"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row r="346" spans="1:12" ht="15.75" customHeight="1">
       <c r="A346" s="10"/>
       <c r="B346" s="10"/>
       <c r="C346" s="7"/>
@@ -8311,7 +8346,7 @@
       <c r="K346" s="10"/>
       <c r="L346" s="10"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row r="347" spans="1:12" ht="15.75" customHeight="1">
       <c r="A347" s="10"/>
       <c r="B347" s="10"/>
       <c r="C347" s="7"/>
@@ -8325,7 +8360,7 @@
       <c r="K347" s="10"/>
       <c r="L347" s="10"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row r="348" spans="1:12" ht="15.75" customHeight="1">
       <c r="A348" s="10"/>
       <c r="B348" s="10"/>
       <c r="C348" s="7"/>
@@ -8339,7 +8374,7 @@
       <c r="K348" s="10"/>
       <c r="L348" s="10"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row r="349" spans="1:12" ht="15.75" customHeight="1">
       <c r="A349" s="10"/>
       <c r="B349" s="10"/>
       <c r="C349" s="7"/>
@@ -8353,7 +8388,7 @@
       <c r="K349" s="10"/>
       <c r="L349" s="10"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row r="350" spans="1:12" ht="15.75" customHeight="1">
       <c r="A350" s="10"/>
       <c r="B350" s="10"/>
       <c r="C350" s="7"/>
@@ -8367,7 +8402,7 @@
       <c r="K350" s="10"/>
       <c r="L350" s="10"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row r="351" spans="1:12" ht="15.75" customHeight="1">
       <c r="A351" s="10"/>
       <c r="B351" s="10"/>
       <c r="C351" s="7"/>
@@ -8381,7 +8416,7 @@
       <c r="K351" s="10"/>
       <c r="L351" s="10"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row r="352" spans="1:12" ht="15.75" customHeight="1">
       <c r="A352" s="10"/>
       <c r="B352" s="10"/>
       <c r="C352" s="7"/>
@@ -8395,7 +8430,7 @@
       <c r="K352" s="10"/>
       <c r="L352" s="10"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row r="353" spans="1:12" ht="15.75" customHeight="1">
       <c r="A353" s="10"/>
       <c r="B353" s="10"/>
       <c r="C353" s="7"/>
@@ -8409,7 +8444,7 @@
       <c r="K353" s="10"/>
       <c r="L353" s="10"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row r="354" spans="1:12" ht="15.75" customHeight="1">
       <c r="A354" s="10"/>
       <c r="B354" s="10"/>
       <c r="C354" s="7"/>
@@ -8423,7 +8458,7 @@
       <c r="K354" s="10"/>
       <c r="L354" s="10"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row r="355" spans="1:12" ht="15.75" customHeight="1">
       <c r="A355" s="10"/>
       <c r="B355" s="10"/>
       <c r="C355" s="7"/>
@@ -8437,7 +8472,7 @@
       <c r="K355" s="10"/>
       <c r="L355" s="10"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row r="356" spans="1:12" ht="15.75" customHeight="1">
       <c r="A356" s="10"/>
       <c r="B356" s="10"/>
       <c r="C356" s="7"/>
@@ -8451,7 +8486,7 @@
       <c r="K356" s="10"/>
       <c r="L356" s="10"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row r="357" spans="1:12" ht="15.75" customHeight="1">
       <c r="A357" s="10"/>
       <c r="B357" s="10"/>
       <c r="C357" s="7"/>
@@ -8465,7 +8500,7 @@
       <c r="K357" s="10"/>
       <c r="L357" s="10"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row r="358" spans="1:12" ht="15.75" customHeight="1">
       <c r="A358" s="10"/>
       <c r="B358" s="10"/>
       <c r="C358" s="7"/>
@@ -8479,7 +8514,7 @@
       <c r="K358" s="10"/>
       <c r="L358" s="10"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row r="359" spans="1:12" ht="15.75" customHeight="1">
       <c r="A359" s="10"/>
       <c r="B359" s="10"/>
       <c r="C359" s="7"/>
@@ -8493,7 +8528,7 @@
       <c r="K359" s="10"/>
       <c r="L359" s="10"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row r="360" spans="1:12" ht="15.75" customHeight="1">
       <c r="A360" s="10"/>
       <c r="B360" s="10"/>
       <c r="C360" s="7"/>
@@ -8507,7 +8542,7 @@
       <c r="K360" s="10"/>
       <c r="L360" s="10"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row r="361" spans="1:12" ht="15.75" customHeight="1">
       <c r="A361" s="10"/>
       <c r="B361" s="10"/>
       <c r="C361" s="7"/>
@@ -8521,7 +8556,7 @@
       <c r="K361" s="10"/>
       <c r="L361" s="10"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row r="362" spans="1:12" ht="15.75" customHeight="1">
       <c r="A362" s="10"/>
       <c r="B362" s="10"/>
       <c r="C362" s="7"/>
@@ -8535,7 +8570,7 @@
       <c r="K362" s="10"/>
       <c r="L362" s="10"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row r="363" spans="1:12" ht="15.75" customHeight="1">
       <c r="A363" s="10"/>
       <c r="B363" s="10"/>
       <c r="C363" s="7"/>
@@ -8549,7 +8584,7 @@
       <c r="K363" s="10"/>
       <c r="L363" s="10"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row r="364" spans="1:12" ht="15.75" customHeight="1">
       <c r="A364" s="10"/>
       <c r="B364" s="10"/>
       <c r="C364" s="7"/>
@@ -8563,7 +8598,7 @@
       <c r="K364" s="10"/>
       <c r="L364" s="10"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row r="365" spans="1:12" ht="15.75" customHeight="1">
       <c r="A365" s="10"/>
       <c r="B365" s="10"/>
       <c r="C365" s="7"/>
@@ -8577,7 +8612,7 @@
       <c r="K365" s="10"/>
       <c r="L365" s="10"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row r="366" spans="1:12" ht="15.75" customHeight="1">
       <c r="A366" s="10"/>
       <c r="B366" s="10"/>
       <c r="C366" s="7"/>
@@ -8591,7 +8626,7 @@
       <c r="K366" s="10"/>
       <c r="L366" s="10"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row r="367" spans="1:12" ht="15.75" customHeight="1">
       <c r="A367" s="10"/>
       <c r="B367" s="10"/>
       <c r="C367" s="7"/>
@@ -8605,7 +8640,7 @@
       <c r="K367" s="10"/>
       <c r="L367" s="10"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row r="368" spans="1:12" ht="15.75" customHeight="1">
       <c r="A368" s="10"/>
       <c r="B368" s="10"/>
       <c r="C368" s="7"/>
@@ -8619,7 +8654,7 @@
       <c r="K368" s="10"/>
       <c r="L368" s="10"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row r="369" spans="1:12" ht="15.75" customHeight="1">
       <c r="A369" s="10"/>
       <c r="B369" s="10"/>
       <c r="C369" s="7"/>
@@ -8633,7 +8668,7 @@
       <c r="K369" s="10"/>
       <c r="L369" s="10"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row r="370" spans="1:12" ht="15.75" customHeight="1">
       <c r="A370" s="10"/>
       <c r="B370" s="10"/>
       <c r="C370" s="7"/>
@@ -8647,7 +8682,7 @@
       <c r="K370" s="10"/>
       <c r="L370" s="10"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row r="371" spans="1:12" ht="15.75" customHeight="1">
       <c r="A371" s="10"/>
       <c r="B371" s="10"/>
       <c r="C371" s="7"/>
@@ -8661,7 +8696,7 @@
       <c r="K371" s="10"/>
       <c r="L371" s="10"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row r="372" spans="1:12" ht="15.75" customHeight="1">
       <c r="A372" s="10"/>
       <c r="B372" s="10"/>
       <c r="C372" s="7"/>
@@ -8675,7 +8710,7 @@
       <c r="K372" s="10"/>
       <c r="L372" s="10"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row r="373" spans="1:12" ht="15.75" customHeight="1">
       <c r="A373" s="10"/>
       <c r="B373" s="10"/>
       <c r="C373" s="7"/>
@@ -8689,7 +8724,7 @@
       <c r="K373" s="10"/>
       <c r="L373" s="10"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row r="374" spans="1:12" ht="15.75" customHeight="1">
       <c r="A374" s="10"/>
       <c r="B374" s="10"/>
       <c r="C374" s="7"/>
@@ -8703,7 +8738,7 @@
       <c r="K374" s="10"/>
       <c r="L374" s="10"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row r="375" spans="1:12" ht="15.75" customHeight="1">
       <c r="A375" s="10"/>
       <c r="B375" s="10"/>
       <c r="C375" s="7"/>
@@ -8717,7 +8752,7 @@
       <c r="K375" s="10"/>
       <c r="L375" s="10"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row r="376" spans="1:12" ht="15.75" customHeight="1">
       <c r="A376" s="10"/>
       <c r="B376" s="10"/>
       <c r="C376" s="7"/>
@@ -8731,7 +8766,7 @@
       <c r="K376" s="10"/>
       <c r="L376" s="10"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row r="377" spans="1:12" ht="15.75" customHeight="1">
       <c r="A377" s="10"/>
       <c r="B377" s="10"/>
       <c r="C377" s="7"/>
@@ -8745,7 +8780,7 @@
       <c r="K377" s="10"/>
       <c r="L377" s="10"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row r="378" spans="1:12" ht="15.75" customHeight="1">
       <c r="A378" s="10"/>
       <c r="B378" s="10"/>
       <c r="C378" s="7"/>
@@ -8759,7 +8794,7 @@
       <c r="K378" s="10"/>
       <c r="L378" s="10"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row r="379" spans="1:12" ht="15.75" customHeight="1">
       <c r="A379" s="10"/>
       <c r="B379" s="10"/>
       <c r="C379" s="7"/>
@@ -8773,7 +8808,7 @@
       <c r="K379" s="10"/>
       <c r="L379" s="10"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row r="380" spans="1:12" ht="15.75" customHeight="1">
       <c r="A380" s="10"/>
       <c r="B380" s="10"/>
       <c r="C380" s="7"/>
@@ -8787,7 +8822,7 @@
       <c r="K380" s="10"/>
       <c r="L380" s="10"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row r="381" spans="1:12" ht="15.75" customHeight="1">
       <c r="A381" s="10"/>
       <c r="B381" s="10"/>
       <c r="C381" s="7"/>
@@ -8801,7 +8836,7 @@
       <c r="K381" s="10"/>
       <c r="L381" s="10"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row r="382" spans="1:12" ht="15.75" customHeight="1">
       <c r="A382" s="10"/>
       <c r="B382" s="10"/>
       <c r="C382" s="7"/>
@@ -8815,7 +8850,7 @@
       <c r="K382" s="10"/>
       <c r="L382" s="10"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row r="383" spans="1:12" ht="15.75" customHeight="1">
       <c r="A383" s="10"/>
       <c r="B383" s="10"/>
       <c r="C383" s="7"/>
@@ -8829,7 +8864,7 @@
       <c r="K383" s="10"/>
       <c r="L383" s="10"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row r="384" spans="1:12" ht="15.75" customHeight="1">
       <c r="A384" s="10"/>
       <c r="B384" s="10"/>
       <c r="C384" s="7"/>
@@ -8843,7 +8878,7 @@
       <c r="K384" s="10"/>
       <c r="L384" s="10"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row r="385" spans="1:12" ht="15.75" customHeight="1">
       <c r="A385" s="10"/>
       <c r="B385" s="10"/>
       <c r="C385" s="7"/>
@@ -8857,7 +8892,7 @@
       <c r="K385" s="10"/>
       <c r="L385" s="10"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row r="386" spans="1:12" ht="15.75" customHeight="1">
       <c r="A386" s="10"/>
       <c r="B386" s="10"/>
       <c r="C386" s="7"/>
@@ -8871,7 +8906,7 @@
       <c r="K386" s="10"/>
       <c r="L386" s="10"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row r="387" spans="1:12" ht="15.75" customHeight="1">
       <c r="A387" s="10"/>
       <c r="B387" s="10"/>
       <c r="C387" s="7"/>
@@ -8885,7 +8920,7 @@
       <c r="K387" s="10"/>
       <c r="L387" s="10"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row r="388" spans="1:12" ht="15.75" customHeight="1">
       <c r="A388" s="10"/>
       <c r="B388" s="10"/>
       <c r="C388" s="7"/>
@@ -8899,7 +8934,7 @@
       <c r="K388" s="10"/>
       <c r="L388" s="10"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row r="389" spans="1:12" ht="15.75" customHeight="1">
       <c r="A389" s="10"/>
       <c r="B389" s="10"/>
       <c r="C389" s="7"/>
@@ -8913,7 +8948,7 @@
       <c r="K389" s="10"/>
       <c r="L389" s="10"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row r="390" spans="1:12" ht="15.75" customHeight="1">
       <c r="A390" s="10"/>
       <c r="B390" s="10"/>
       <c r="C390" s="7"/>
@@ -8927,7 +8962,7 @@
       <c r="K390" s="10"/>
       <c r="L390" s="10"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row r="391" spans="1:12" ht="15.75" customHeight="1">
       <c r="A391" s="10"/>
       <c r="B391" s="10"/>
       <c r="C391" s="7"/>
@@ -8941,7 +8976,7 @@
       <c r="K391" s="10"/>
       <c r="L391" s="10"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row r="392" spans="1:12" ht="15.75" customHeight="1">
       <c r="A392" s="10"/>
       <c r="B392" s="10"/>
       <c r="C392" s="7"/>
@@ -8955,7 +8990,7 @@
       <c r="K392" s="10"/>
       <c r="L392" s="10"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row r="393" spans="1:12" ht="15.75" customHeight="1">
       <c r="A393" s="10"/>
       <c r="B393" s="10"/>
       <c r="C393" s="7"/>
@@ -8969,7 +9004,7 @@
       <c r="K393" s="10"/>
       <c r="L393" s="10"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row r="394" spans="1:12" ht="15.75" customHeight="1">
       <c r="A394" s="10"/>
       <c r="B394" s="10"/>
       <c r="C394" s="7"/>
@@ -8983,7 +9018,7 @@
       <c r="K394" s="10"/>
       <c r="L394" s="10"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row r="395" spans="1:12" ht="15.75" customHeight="1">
       <c r="A395" s="10"/>
       <c r="B395" s="10"/>
       <c r="C395" s="7"/>
@@ -8997,7 +9032,7 @@
       <c r="K395" s="10"/>
       <c r="L395" s="10"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row r="396" spans="1:12" ht="15.75" customHeight="1">
       <c r="A396" s="10"/>
       <c r="B396" s="10"/>
       <c r="C396" s="7"/>
@@ -9011,7 +9046,7 @@
       <c r="K396" s="10"/>
       <c r="L396" s="10"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row r="397" spans="1:12" ht="15.75" customHeight="1">
       <c r="A397" s="10"/>
       <c r="B397" s="10"/>
       <c r="C397" s="7"/>
@@ -9025,7 +9060,7 @@
       <c r="K397" s="10"/>
       <c r="L397" s="10"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row r="398" spans="1:12" ht="15.75" customHeight="1">
       <c r="A398" s="10"/>
       <c r="B398" s="10"/>
       <c r="C398" s="7"/>
@@ -9039,7 +9074,7 @@
       <c r="K398" s="10"/>
       <c r="L398" s="10"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row r="399" spans="1:12" ht="15.75" customHeight="1">
       <c r="A399" s="10"/>
       <c r="B399" s="10"/>
       <c r="C399" s="7"/>
@@ -9053,7 +9088,7 @@
       <c r="K399" s="10"/>
       <c r="L399" s="10"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row r="400" spans="1:12" ht="15.75" customHeight="1">
       <c r="A400" s="10"/>
       <c r="B400" s="10"/>
       <c r="C400" s="7"/>
@@ -9067,7 +9102,7 @@
       <c r="K400" s="10"/>
       <c r="L400" s="10"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row r="401" spans="1:12" ht="15.75" customHeight="1">
       <c r="A401" s="10"/>
       <c r="B401" s="10"/>
       <c r="C401" s="7"/>
@@ -9081,7 +9116,7 @@
       <c r="K401" s="10"/>
       <c r="L401" s="10"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row r="402" spans="1:12" ht="15.75" customHeight="1">
       <c r="A402" s="10"/>
       <c r="B402" s="10"/>
       <c r="C402" s="7"/>
@@ -9095,7 +9130,7 @@
       <c r="K402" s="10"/>
       <c r="L402" s="10"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row r="403" spans="1:12" ht="15.75" customHeight="1">
       <c r="A403" s="10"/>
       <c r="B403" s="10"/>
       <c r="C403" s="7"/>
@@ -9109,7 +9144,7 @@
       <c r="K403" s="10"/>
       <c r="L403" s="10"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row r="404" spans="1:12" ht="15.75" customHeight="1">
       <c r="A404" s="10"/>
       <c r="B404" s="10"/>
       <c r="C404" s="7"/>
@@ -9123,7 +9158,7 @@
       <c r="K404" s="10"/>
       <c r="L404" s="10"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row r="405" spans="1:12" ht="15.75" customHeight="1">
       <c r="A405" s="10"/>
       <c r="B405" s="10"/>
       <c r="C405" s="7"/>
@@ -9137,7 +9172,7 @@
       <c r="K405" s="10"/>
       <c r="L405" s="10"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row r="406" spans="1:12" ht="15.75" customHeight="1">
       <c r="A406" s="10"/>
       <c r="B406" s="10"/>
       <c r="C406" s="7"/>
@@ -9151,7 +9186,7 @@
       <c r="K406" s="10"/>
       <c r="L406" s="10"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row r="407" spans="1:12" ht="15.75" customHeight="1">
       <c r="A407" s="10"/>
       <c r="B407" s="10"/>
       <c r="C407" s="7"/>
@@ -9165,7 +9200,7 @@
       <c r="K407" s="10"/>
       <c r="L407" s="10"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row r="408" spans="1:12" ht="15.75" customHeight="1">
       <c r="A408" s="10"/>
       <c r="B408" s="10"/>
       <c r="C408" s="7"/>
@@ -9179,7 +9214,7 @@
       <c r="K408" s="10"/>
       <c r="L408" s="10"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row r="409" spans="1:12" ht="15.75" customHeight="1">
       <c r="A409" s="10"/>
       <c r="B409" s="10"/>
       <c r="C409" s="7"/>
@@ -9193,7 +9228,7 @@
       <c r="K409" s="10"/>
       <c r="L409" s="10"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row r="410" spans="1:12" ht="15.75" customHeight="1">
       <c r="A410" s="10"/>
       <c r="B410" s="10"/>
       <c r="C410" s="7"/>
@@ -9207,7 +9242,7 @@
       <c r="K410" s="10"/>
       <c r="L410" s="10"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row r="411" spans="1:12" ht="15.75" customHeight="1">
       <c r="A411" s="10"/>
       <c r="B411" s="10"/>
       <c r="C411" s="7"/>
@@ -9221,7 +9256,7 @@
       <c r="K411" s="10"/>
       <c r="L411" s="10"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row r="412" spans="1:12" ht="15.75" customHeight="1">
       <c r="A412" s="10"/>
       <c r="B412" s="10"/>
       <c r="C412" s="7"/>
@@ -9235,7 +9270,7 @@
       <c r="K412" s="10"/>
       <c r="L412" s="10"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row r="413" spans="1:12" ht="15.75" customHeight="1">
       <c r="A413" s="10"/>
       <c r="B413" s="10"/>
       <c r="C413" s="7"/>
@@ -9249,7 +9284,7 @@
       <c r="K413" s="10"/>
       <c r="L413" s="10"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row r="414" spans="1:12" ht="15.75" customHeight="1">
       <c r="A414" s="10"/>
       <c r="B414" s="10"/>
       <c r="C414" s="7"/>
@@ -9263,7 +9298,7 @@
       <c r="K414" s="10"/>
       <c r="L414" s="10"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row r="415" spans="1:12" ht="15.75" customHeight="1">
       <c r="A415" s="10"/>
       <c r="B415" s="10"/>
       <c r="C415" s="7"/>
@@ -9277,7 +9312,7 @@
       <c r="K415" s="10"/>
       <c r="L415" s="10"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row r="416" spans="1:12" ht="15.75" customHeight="1">
       <c r="A416" s="10"/>
       <c r="B416" s="10"/>
       <c r="C416" s="7"/>
@@ -9291,7 +9326,7 @@
       <c r="K416" s="10"/>
       <c r="L416" s="10"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row r="417" spans="1:12" ht="15.75" customHeight="1">
       <c r="A417" s="10"/>
       <c r="B417" s="10"/>
       <c r="C417" s="7"/>
@@ -9305,7 +9340,7 @@
       <c r="K417" s="10"/>
       <c r="L417" s="10"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row r="418" spans="1:12" ht="15.75" customHeight="1">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="7"/>
@@ -9319,7 +9354,7 @@
       <c r="K418" s="10"/>
       <c r="L418" s="10"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row r="419" spans="1:12" ht="15.75" customHeight="1">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="7"/>
@@ -9333,7 +9368,7 @@
       <c r="K419" s="10"/>
       <c r="L419" s="10"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row r="420" spans="1:12" ht="15.75" customHeight="1">
       <c r="A420" s="10"/>
       <c r="B420" s="10"/>
       <c r="C420" s="7"/>
@@ -9347,7 +9382,7 @@
       <c r="K420" s="10"/>
       <c r="L420" s="10"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row r="421" spans="1:12" ht="15.75" customHeight="1">
       <c r="A421" s="10"/>
       <c r="B421" s="10"/>
       <c r="C421" s="7"/>
@@ -9361,7 +9396,7 @@
       <c r="K421" s="10"/>
       <c r="L421" s="10"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row r="422" spans="1:12" ht="15.75" customHeight="1">
       <c r="A422" s="10"/>
       <c r="B422" s="10"/>
       <c r="C422" s="7"/>
@@ -9375,7 +9410,7 @@
       <c r="K422" s="10"/>
       <c r="L422" s="10"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row r="423" spans="1:12" ht="15.75" customHeight="1">
       <c r="A423" s="10"/>
       <c r="B423" s="10"/>
       <c r="C423" s="7"/>
@@ -9389,7 +9424,7 @@
       <c r="K423" s="10"/>
       <c r="L423" s="10"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row r="424" spans="1:12" ht="15.75" customHeight="1">
       <c r="A424" s="10"/>
       <c r="B424" s="10"/>
       <c r="C424" s="7"/>
@@ -9403,7 +9438,7 @@
       <c r="K424" s="10"/>
       <c r="L424" s="10"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row r="425" spans="1:12" ht="15.75" customHeight="1">
       <c r="A425" s="10"/>
       <c r="B425" s="10"/>
       <c r="C425" s="7"/>
@@ -9417,7 +9452,7 @@
       <c r="K425" s="10"/>
       <c r="L425" s="10"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" spans="1:12" ht="15.75" customHeight="1">
       <c r="A426" s="10"/>
       <c r="B426" s="10"/>
       <c r="C426" s="7"/>
@@ -9431,7 +9466,7 @@
       <c r="K426" s="10"/>
       <c r="L426" s="10"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row r="427" spans="1:12" ht="15.75" customHeight="1">
       <c r="A427" s="10"/>
       <c r="B427" s="10"/>
       <c r="C427" s="7"/>
@@ -9445,7 +9480,7 @@
       <c r="K427" s="10"/>
       <c r="L427" s="10"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" spans="1:12" ht="15.75" customHeight="1">
       <c r="A428" s="10"/>
       <c r="B428" s="10"/>
       <c r="C428" s="7"/>
@@ -9459,7 +9494,7 @@
       <c r="K428" s="10"/>
       <c r="L428" s="10"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row r="429" spans="1:12" ht="15.75" customHeight="1">
       <c r="A429" s="10"/>
       <c r="B429" s="10"/>
       <c r="C429" s="7"/>
@@ -9473,7 +9508,7 @@
       <c r="K429" s="10"/>
       <c r="L429" s="10"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row r="430" spans="1:12" ht="15.75" customHeight="1">
       <c r="A430" s="10"/>
       <c r="B430" s="10"/>
       <c r="C430" s="7"/>
@@ -9487,7 +9522,7 @@
       <c r="K430" s="10"/>
       <c r="L430" s="10"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row r="431" spans="1:12" ht="15.75" customHeight="1">
       <c r="A431" s="10"/>
       <c r="B431" s="10"/>
       <c r="C431" s="7"/>
@@ -9501,7 +9536,7 @@
       <c r="K431" s="10"/>
       <c r="L431" s="10"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row r="432" spans="1:12" ht="15.75" customHeight="1">
       <c r="A432" s="10"/>
       <c r="B432" s="10"/>
       <c r="C432" s="7"/>
@@ -9515,7 +9550,7 @@
       <c r="K432" s="10"/>
       <c r="L432" s="10"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row r="433" spans="1:12" ht="15.75" customHeight="1">
       <c r="A433" s="10"/>
       <c r="B433" s="10"/>
       <c r="C433" s="7"/>
@@ -9529,7 +9564,7 @@
       <c r="K433" s="10"/>
       <c r="L433" s="10"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row r="434" spans="1:12" ht="15.75" customHeight="1">
       <c r="A434" s="10"/>
       <c r="B434" s="10"/>
       <c r="C434" s="7"/>
@@ -9543,7 +9578,7 @@
       <c r="K434" s="10"/>
       <c r="L434" s="10"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row r="435" spans="1:12" ht="15.75" customHeight="1">
       <c r="A435" s="10"/>
       <c r="B435" s="10"/>
       <c r="C435" s="7"/>
@@ -9557,7 +9592,7 @@
       <c r="K435" s="10"/>
       <c r="L435" s="10"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row r="436" spans="1:12" ht="15.75" customHeight="1">
       <c r="A436" s="10"/>
       <c r="B436" s="10"/>
       <c r="C436" s="7"/>
@@ -9571,7 +9606,7 @@
       <c r="K436" s="10"/>
       <c r="L436" s="10"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row r="437" spans="1:12" ht="15.75" customHeight="1">
       <c r="A437" s="10"/>
       <c r="B437" s="10"/>
       <c r="C437" s="7"/>
@@ -9585,7 +9620,7 @@
       <c r="K437" s="10"/>
       <c r="L437" s="10"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" spans="1:12" ht="15.75" customHeight="1">
       <c r="A438" s="10"/>
       <c r="B438" s="10"/>
       <c r="C438" s="7"/>
@@ -9599,7 +9634,7 @@
       <c r="K438" s="10"/>
       <c r="L438" s="10"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row r="439" spans="1:12" ht="15.75" customHeight="1">
       <c r="A439" s="10"/>
       <c r="B439" s="10"/>
       <c r="C439" s="7"/>
@@ -9613,7 +9648,7 @@
       <c r="K439" s="10"/>
       <c r="L439" s="10"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row r="440" spans="1:12" ht="15.75" customHeight="1">
       <c r="A440" s="10"/>
       <c r="B440" s="10"/>
       <c r="C440" s="7"/>
@@ -9627,7 +9662,7 @@
       <c r="K440" s="10"/>
       <c r="L440" s="10"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row r="441" spans="1:12" ht="15.75" customHeight="1">
       <c r="A441" s="10"/>
       <c r="B441" s="10"/>
       <c r="C441" s="7"/>
@@ -9641,7 +9676,7 @@
       <c r="K441" s="10"/>
       <c r="L441" s="10"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row r="442" spans="1:12" ht="15.75" customHeight="1">
       <c r="A442" s="10"/>
       <c r="B442" s="10"/>
       <c r="C442" s="7"/>
@@ -9655,7 +9690,7 @@
       <c r="K442" s="10"/>
       <c r="L442" s="10"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row r="443" spans="1:12" ht="15.75" customHeight="1">
       <c r="A443" s="10"/>
       <c r="B443" s="10"/>
       <c r="C443" s="7"/>
@@ -9669,7 +9704,7 @@
       <c r="K443" s="10"/>
       <c r="L443" s="10"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row r="444" spans="1:12" ht="15.75" customHeight="1">
       <c r="A444" s="10"/>
       <c r="B444" s="10"/>
       <c r="C444" s="7"/>
@@ -9683,7 +9718,7 @@
       <c r="K444" s="10"/>
       <c r="L444" s="10"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row r="445" spans="1:12" ht="15.75" customHeight="1">
       <c r="A445" s="10"/>
       <c r="B445" s="10"/>
       <c r="C445" s="7"/>
@@ -9697,7 +9732,7 @@
       <c r="K445" s="10"/>
       <c r="L445" s="10"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row r="446" spans="1:12" ht="15.75" customHeight="1">
       <c r="A446" s="10"/>
       <c r="B446" s="10"/>
       <c r="C446" s="7"/>
@@ -9711,7 +9746,7 @@
       <c r="K446" s="10"/>
       <c r="L446" s="10"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row r="447" spans="1:12" ht="15.75" customHeight="1">
       <c r="A447" s="10"/>
       <c r="B447" s="10"/>
       <c r="C447" s="7"/>
@@ -9725,7 +9760,7 @@
       <c r="K447" s="10"/>
       <c r="L447" s="10"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row r="448" spans="1:12" ht="15.75" customHeight="1">
       <c r="A448" s="10"/>
       <c r="B448" s="10"/>
       <c r="C448" s="7"/>
@@ -9739,7 +9774,7 @@
       <c r="K448" s="10"/>
       <c r="L448" s="10"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row r="449" spans="1:12" ht="15.75" customHeight="1">
       <c r="A449" s="10"/>
       <c r="B449" s="10"/>
       <c r="C449" s="7"/>
@@ -9753,7 +9788,7 @@
       <c r="K449" s="10"/>
       <c r="L449" s="10"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row r="450" spans="1:12" ht="15.75" customHeight="1">
       <c r="A450" s="10"/>
       <c r="B450" s="10"/>
       <c r="C450" s="7"/>
@@ -9767,7 +9802,7 @@
       <c r="K450" s="10"/>
       <c r="L450" s="10"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row r="451" spans="1:12" ht="15.75" customHeight="1">
       <c r="A451" s="10"/>
       <c r="B451" s="10"/>
       <c r="C451" s="7"/>
@@ -9781,7 +9816,7 @@
       <c r="K451" s="10"/>
       <c r="L451" s="10"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row r="452" spans="1:12" ht="15.75" customHeight="1">
       <c r="A452" s="10"/>
       <c r="B452" s="10"/>
       <c r="C452" s="7"/>
@@ -9795,7 +9830,7 @@
       <c r="K452" s="10"/>
       <c r="L452" s="10"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row r="453" spans="1:12" ht="15.75" customHeight="1">
       <c r="A453" s="10"/>
       <c r="B453" s="10"/>
       <c r="C453" s="7"/>
@@ -9809,7 +9844,7 @@
       <c r="K453" s="10"/>
       <c r="L453" s="10"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row r="454" spans="1:12" ht="15.75" customHeight="1">
       <c r="A454" s="10"/>
       <c r="B454" s="10"/>
       <c r="C454" s="7"/>
@@ -9823,7 +9858,7 @@
       <c r="K454" s="10"/>
       <c r="L454" s="10"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row r="455" spans="1:12" ht="15.75" customHeight="1">
       <c r="A455" s="10"/>
       <c r="B455" s="10"/>
       <c r="C455" s="7"/>
@@ -9837,7 +9872,7 @@
       <c r="K455" s="10"/>
       <c r="L455" s="10"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row r="456" spans="1:12" ht="15.75" customHeight="1">
       <c r="A456" s="10"/>
       <c r="B456" s="10"/>
       <c r="C456" s="7"/>
@@ -9851,7 +9886,7 @@
       <c r="K456" s="10"/>
       <c r="L456" s="10"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row r="457" spans="1:12" ht="15.75" customHeight="1">
       <c r="A457" s="10"/>
       <c r="B457" s="10"/>
       <c r="C457" s="7"/>
@@ -9865,7 +9900,7 @@
       <c r="K457" s="10"/>
       <c r="L457" s="10"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row r="458" spans="1:12" ht="15.75" customHeight="1">
       <c r="A458" s="10"/>
       <c r="B458" s="10"/>
       <c r="C458" s="7"/>
@@ -9879,7 +9914,7 @@
       <c r="K458" s="10"/>
       <c r="L458" s="10"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row r="459" spans="1:12" ht="15.75" customHeight="1">
       <c r="A459" s="10"/>
       <c r="B459" s="10"/>
       <c r="C459" s="7"/>
@@ -9893,7 +9928,7 @@
       <c r="K459" s="10"/>
       <c r="L459" s="10"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row r="460" spans="1:12" ht="15.75" customHeight="1">
       <c r="A460" s="10"/>
       <c r="B460" s="10"/>
       <c r="C460" s="7"/>
@@ -9907,7 +9942,7 @@
       <c r="K460" s="10"/>
       <c r="L460" s="10"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row r="461" spans="1:12" ht="15.75" customHeight="1">
       <c r="A461" s="10"/>
       <c r="B461" s="10"/>
       <c r="C461" s="7"/>
@@ -9921,7 +9956,7 @@
       <c r="K461" s="10"/>
       <c r="L461" s="10"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row r="462" spans="1:12" ht="15.75" customHeight="1">
       <c r="A462" s="10"/>
       <c r="B462" s="10"/>
       <c r="C462" s="7"/>
@@ -9935,7 +9970,7 @@
       <c r="K462" s="10"/>
       <c r="L462" s="10"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row r="463" spans="1:12" ht="15.75" customHeight="1">
       <c r="A463" s="10"/>
       <c r="B463" s="10"/>
       <c r="C463" s="7"/>
@@ -9949,7 +9984,7 @@
       <c r="K463" s="10"/>
       <c r="L463" s="10"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row r="464" spans="1:12" ht="15.75" customHeight="1">
       <c r="A464" s="10"/>
       <c r="B464" s="10"/>
       <c r="C464" s="7"/>
@@ -9963,7 +9998,7 @@
       <c r="K464" s="10"/>
       <c r="L464" s="10"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row r="465" spans="1:12" ht="15.75" customHeight="1">
       <c r="A465" s="10"/>
       <c r="B465" s="10"/>
       <c r="C465" s="7"/>
@@ -9977,7 +10012,7 @@
       <c r="K465" s="10"/>
       <c r="L465" s="10"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row r="466" spans="1:12" ht="15.75" customHeight="1">
       <c r="A466" s="10"/>
       <c r="B466" s="10"/>
       <c r="C466" s="7"/>
@@ -9991,7 +10026,7 @@
       <c r="K466" s="10"/>
       <c r="L466" s="10"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row r="467" spans="1:12" ht="15.75" customHeight="1">
       <c r="A467" s="10"/>
       <c r="B467" s="10"/>
       <c r="C467" s="7"/>
@@ -10005,7 +10040,7 @@
       <c r="K467" s="10"/>
       <c r="L467" s="10"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row r="468" spans="1:12" ht="15.75" customHeight="1">
       <c r="A468" s="10"/>
       <c r="B468" s="10"/>
       <c r="C468" s="7"/>
@@ -10019,7 +10054,7 @@
       <c r="K468" s="10"/>
       <c r="L468" s="10"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row r="469" spans="1:12" ht="15.75" customHeight="1">
       <c r="A469" s="10"/>
       <c r="B469" s="10"/>
       <c r="C469" s="7"/>
@@ -10033,7 +10068,7 @@
       <c r="K469" s="10"/>
       <c r="L469" s="10"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row r="470" spans="1:12" ht="15.75" customHeight="1">
       <c r="A470" s="10"/>
       <c r="B470" s="10"/>
       <c r="C470" s="7"/>
@@ -10047,7 +10082,7 @@
       <c r="K470" s="10"/>
       <c r="L470" s="10"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row r="471" spans="1:12" ht="15.75" customHeight="1">
       <c r="A471" s="10"/>
       <c r="B471" s="10"/>
       <c r="C471" s="7"/>
@@ -10061,7 +10096,7 @@
       <c r="K471" s="10"/>
       <c r="L471" s="10"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row r="472" spans="1:12" ht="15.75" customHeight="1">
       <c r="A472" s="10"/>
       <c r="B472" s="10"/>
       <c r="C472" s="7"/>
@@ -10075,7 +10110,7 @@
       <c r="K472" s="10"/>
       <c r="L472" s="10"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row r="473" spans="1:12" ht="15.75" customHeight="1">
       <c r="A473" s="10"/>
       <c r="B473" s="10"/>
       <c r="C473" s="7"/>
@@ -10089,7 +10124,7 @@
       <c r="K473" s="10"/>
       <c r="L473" s="10"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row r="474" spans="1:12" ht="15.75" customHeight="1">
       <c r="A474" s="10"/>
       <c r="B474" s="10"/>
       <c r="C474" s="7"/>
@@ -10103,7 +10138,7 @@
       <c r="K474" s="10"/>
       <c r="L474" s="10"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row r="475" spans="1:12" ht="15.75" customHeight="1">
       <c r="A475" s="10"/>
       <c r="B475" s="10"/>
       <c r="C475" s="7"/>
@@ -10117,7 +10152,7 @@
       <c r="K475" s="10"/>
       <c r="L475" s="10"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row r="476" spans="1:12" ht="15.75" customHeight="1">
       <c r="A476" s="10"/>
       <c r="B476" s="10"/>
       <c r="C476" s="7"/>
@@ -10131,7 +10166,7 @@
       <c r="K476" s="10"/>
       <c r="L476" s="10"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row r="477" spans="1:12" ht="15.75" customHeight="1">
       <c r="A477" s="10"/>
       <c r="B477" s="10"/>
       <c r="C477" s="7"/>
@@ -10145,7 +10180,7 @@
       <c r="K477" s="10"/>
       <c r="L477" s="10"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row r="478" spans="1:12" ht="15.75" customHeight="1">
       <c r="A478" s="10"/>
       <c r="B478" s="10"/>
       <c r="C478" s="7"/>
@@ -10159,7 +10194,7 @@
       <c r="K478" s="10"/>
       <c r="L478" s="10"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row r="479" spans="1:12" ht="15.75" customHeight="1">
       <c r="A479" s="10"/>
       <c r="B479" s="10"/>
       <c r="C479" s="7"/>
@@ -10173,7 +10208,7 @@
       <c r="K479" s="10"/>
       <c r="L479" s="10"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row r="480" spans="1:12" ht="15.75" customHeight="1">
       <c r="A480" s="10"/>
       <c r="B480" s="10"/>
       <c r="C480" s="7"/>
@@ -10187,7 +10222,7 @@
       <c r="K480" s="10"/>
       <c r="L480" s="10"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row r="481" spans="1:12" ht="15.75" customHeight="1">
       <c r="A481" s="10"/>
       <c r="B481" s="10"/>
       <c r="C481" s="7"/>
@@ -10201,7 +10236,7 @@
       <c r="K481" s="10"/>
       <c r="L481" s="10"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row r="482" spans="1:12" ht="15.75" customHeight="1">
       <c r="A482" s="10"/>
       <c r="B482" s="10"/>
       <c r="C482" s="7"/>
@@ -10215,7 +10250,7 @@
       <c r="K482" s="10"/>
       <c r="L482" s="10"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row r="483" spans="1:12" ht="15.75" customHeight="1">
       <c r="A483" s="10"/>
       <c r="B483" s="10"/>
       <c r="C483" s="7"/>
@@ -10229,7 +10264,7 @@
       <c r="K483" s="10"/>
       <c r="L483" s="10"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row r="484" spans="1:12" ht="15.75" customHeight="1">
       <c r="A484" s="10"/>
       <c r="B484" s="10"/>
       <c r="C484" s="7"/>
@@ -10243,7 +10278,7 @@
       <c r="K484" s="10"/>
       <c r="L484" s="10"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row r="485" spans="1:12" ht="15.75" customHeight="1">
       <c r="A485" s="10"/>
       <c r="B485" s="10"/>
       <c r="C485" s="7"/>
@@ -10257,7 +10292,7 @@
       <c r="K485" s="10"/>
       <c r="L485" s="10"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row r="486" spans="1:12" ht="15.75" customHeight="1">
       <c r="A486" s="10"/>
       <c r="B486" s="10"/>
       <c r="C486" s="7"/>
@@ -10271,7 +10306,7 @@
       <c r="K486" s="10"/>
       <c r="L486" s="10"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row r="487" spans="1:12" ht="15.75" customHeight="1">
       <c r="A487" s="10"/>
       <c r="B487" s="10"/>
       <c r="C487" s="7"/>
@@ -10285,7 +10320,7 @@
       <c r="K487" s="10"/>
       <c r="L487" s="10"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row r="488" spans="1:12" ht="15.75" customHeight="1">
       <c r="A488" s="10"/>
       <c r="B488" s="10"/>
       <c r="C488" s="7"/>
@@ -10299,7 +10334,7 @@
       <c r="K488" s="10"/>
       <c r="L488" s="10"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row r="489" spans="1:12" ht="15.75" customHeight="1">
       <c r="A489" s="10"/>
       <c r="B489" s="10"/>
       <c r="C489" s="7"/>
@@ -10313,7 +10348,7 @@
       <c r="K489" s="10"/>
       <c r="L489" s="10"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row r="490" spans="1:12" ht="15.75" customHeight="1">
       <c r="A490" s="10"/>
       <c r="B490" s="10"/>
       <c r="C490" s="7"/>
@@ -10327,7 +10362,7 @@
       <c r="K490" s="10"/>
       <c r="L490" s="10"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row r="491" spans="1:12" ht="15.75" customHeight="1">
       <c r="A491" s="10"/>
       <c r="B491" s="10"/>
       <c r="C491" s="7"/>
@@ -10341,7 +10376,7 @@
       <c r="K491" s="10"/>
       <c r="L491" s="10"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row r="492" spans="1:12" ht="15.75" customHeight="1">
       <c r="A492" s="10"/>
       <c r="B492" s="10"/>
       <c r="C492" s="7"/>
@@ -10355,7 +10390,7 @@
       <c r="K492" s="10"/>
       <c r="L492" s="10"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row r="493" spans="1:12" ht="15.75" customHeight="1">
       <c r="A493" s="10"/>
       <c r="B493" s="10"/>
       <c r="C493" s="7"/>
@@ -10369,7 +10404,7 @@
       <c r="K493" s="10"/>
       <c r="L493" s="10"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row r="494" spans="1:12" ht="15.75" customHeight="1">
       <c r="A494" s="10"/>
       <c r="B494" s="10"/>
       <c r="C494" s="7"/>
@@ -10383,7 +10418,7 @@
       <c r="K494" s="10"/>
       <c r="L494" s="10"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row r="495" spans="1:12" ht="15.75" customHeight="1">
       <c r="A495" s="10"/>
       <c r="B495" s="10"/>
       <c r="C495" s="7"/>
@@ -10397,7 +10432,7 @@
       <c r="K495" s="10"/>
       <c r="L495" s="10"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row r="496" spans="1:12" ht="15.75" customHeight="1">
       <c r="A496" s="10"/>
       <c r="B496" s="10"/>
       <c r="C496" s="7"/>
@@ -10411,7 +10446,7 @@
       <c r="K496" s="10"/>
       <c r="L496" s="10"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row r="497" spans="1:12" ht="15.75" customHeight="1">
       <c r="A497" s="10"/>
       <c r="B497" s="10"/>
       <c r="C497" s="7"/>
@@ -10425,7 +10460,7 @@
       <c r="K497" s="10"/>
       <c r="L497" s="10"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row r="498" spans="1:12" ht="15.75" customHeight="1">
       <c r="A498" s="10"/>
       <c r="B498" s="10"/>
       <c r="C498" s="7"/>
@@ -10439,7 +10474,7 @@
       <c r="K498" s="10"/>
       <c r="L498" s="10"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row r="499" spans="1:12" ht="15.75" customHeight="1">
       <c r="A499" s="10"/>
       <c r="B499" s="10"/>
       <c r="C499" s="7"/>
@@ -10453,7 +10488,7 @@
       <c r="K499" s="10"/>
       <c r="L499" s="10"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row r="500" spans="1:12" ht="15.75" customHeight="1">
       <c r="A500" s="10"/>
       <c r="B500" s="10"/>
       <c r="C500" s="7"/>
@@ -10467,7 +10502,7 @@
       <c r="K500" s="10"/>
       <c r="L500" s="10"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row r="501" spans="1:12" ht="15.75" customHeight="1">
       <c r="A501" s="10"/>
       <c r="B501" s="10"/>
       <c r="C501" s="7"/>
@@ -10481,7 +10516,7 @@
       <c r="K501" s="10"/>
       <c r="L501" s="10"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row r="502" spans="1:12" ht="15.75" customHeight="1">
       <c r="A502" s="10"/>
       <c r="B502" s="10"/>
       <c r="C502" s="7"/>
@@ -10495,7 +10530,7 @@
       <c r="K502" s="10"/>
       <c r="L502" s="10"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row r="503" spans="1:12" ht="15.75" customHeight="1">
       <c r="A503" s="10"/>
       <c r="B503" s="10"/>
       <c r="C503" s="7"/>
@@ -10509,7 +10544,7 @@
       <c r="K503" s="10"/>
       <c r="L503" s="10"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row r="504" spans="1:12" ht="15.75" customHeight="1">
       <c r="A504" s="10"/>
       <c r="B504" s="10"/>
       <c r="C504" s="7"/>
@@ -10523,7 +10558,7 @@
       <c r="K504" s="10"/>
       <c r="L504" s="10"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row r="505" spans="1:12" ht="15.75" customHeight="1">
       <c r="A505" s="10"/>
       <c r="B505" s="10"/>
       <c r="C505" s="7"/>
@@ -10537,7 +10572,7 @@
       <c r="K505" s="10"/>
       <c r="L505" s="10"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row r="506" spans="1:12" ht="15.75" customHeight="1">
       <c r="A506" s="10"/>
       <c r="B506" s="10"/>
       <c r="C506" s="7"/>
@@ -10551,7 +10586,7 @@
       <c r="K506" s="10"/>
       <c r="L506" s="10"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row r="507" spans="1:12" ht="15.75" customHeight="1">
       <c r="A507" s="10"/>
       <c r="B507" s="10"/>
       <c r="C507" s="7"/>
@@ -10565,7 +10600,7 @@
       <c r="K507" s="10"/>
       <c r="L507" s="10"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row r="508" spans="1:12" ht="15.75" customHeight="1">
       <c r="A508" s="10"/>
       <c r="B508" s="10"/>
       <c r="C508" s="7"/>
@@ -10579,7 +10614,7 @@
       <c r="K508" s="10"/>
       <c r="L508" s="10"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row r="509" spans="1:12" ht="15.75" customHeight="1">
       <c r="A509" s="10"/>
       <c r="B509" s="10"/>
       <c r="C509" s="7"/>
@@ -10593,7 +10628,7 @@
       <c r="K509" s="10"/>
       <c r="L509" s="10"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row r="510" spans="1:12" ht="15.75" customHeight="1">
       <c r="A510" s="10"/>
       <c r="B510" s="10"/>
       <c r="C510" s="7"/>
@@ -10607,7 +10642,7 @@
       <c r="K510" s="10"/>
       <c r="L510" s="10"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row r="511" spans="1:12" ht="15.75" customHeight="1">
       <c r="A511" s="10"/>
       <c r="B511" s="10"/>
       <c r="C511" s="7"/>
@@ -10621,7 +10656,7 @@
       <c r="K511" s="10"/>
       <c r="L511" s="10"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row r="512" spans="1:12" ht="15.75" customHeight="1">
       <c r="A512" s="10"/>
       <c r="B512" s="10"/>
       <c r="C512" s="7"/>
@@ -10635,7 +10670,7 @@
       <c r="K512" s="10"/>
       <c r="L512" s="10"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row r="513" spans="1:12" ht="15.75" customHeight="1">
       <c r="A513" s="10"/>
       <c r="B513" s="10"/>
       <c r="C513" s="7"/>
@@ -10649,7 +10684,7 @@
       <c r="K513" s="10"/>
       <c r="L513" s="10"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row r="514" spans="1:12" ht="15.75" customHeight="1">
       <c r="A514" s="10"/>
       <c r="B514" s="10"/>
       <c r="C514" s="7"/>
@@ -10663,7 +10698,7 @@
       <c r="K514" s="10"/>
       <c r="L514" s="10"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row r="515" spans="1:12" ht="15.75" customHeight="1">
       <c r="A515" s="10"/>
       <c r="B515" s="10"/>
       <c r="C515" s="7"/>
@@ -10677,7 +10712,7 @@
       <c r="K515" s="10"/>
       <c r="L515" s="10"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row r="516" spans="1:12" ht="15.75" customHeight="1">
       <c r="A516" s="10"/>
       <c r="B516" s="10"/>
       <c r="C516" s="7"/>
@@ -10691,7 +10726,7 @@
       <c r="K516" s="10"/>
       <c r="L516" s="10"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row r="517" spans="1:12" ht="15.75" customHeight="1">
       <c r="A517" s="10"/>
       <c r="B517" s="10"/>
       <c r="C517" s="7"/>
@@ -10705,7 +10740,7 @@
       <c r="K517" s="10"/>
       <c r="L517" s="10"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row r="518" spans="1:12" ht="15.75" customHeight="1">
       <c r="A518" s="10"/>
       <c r="B518" s="10"/>
       <c r="C518" s="7"/>
@@ -10719,7 +10754,7 @@
       <c r="K518" s="10"/>
       <c r="L518" s="10"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row r="519" spans="1:12" ht="15.75" customHeight="1">
       <c r="A519" s="10"/>
       <c r="B519" s="10"/>
       <c r="C519" s="7"/>
@@ -10733,7 +10768,7 @@
       <c r="K519" s="10"/>
       <c r="L519" s="10"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row r="520" spans="1:12" ht="15.75" customHeight="1">
       <c r="A520" s="10"/>
       <c r="B520" s="10"/>
       <c r="C520" s="7"/>
@@ -10747,7 +10782,7 @@
       <c r="K520" s="10"/>
       <c r="L520" s="10"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row r="521" spans="1:12" ht="15.75" customHeight="1">
       <c r="A521" s="10"/>
       <c r="B521" s="10"/>
       <c r="C521" s="7"/>
@@ -10761,7 +10796,7 @@
       <c r="K521" s="10"/>
       <c r="L521" s="10"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row r="522" spans="1:12" ht="15.75" customHeight="1">
       <c r="A522" s="10"/>
       <c r="B522" s="10"/>
       <c r="C522" s="7"/>
@@ -10775,7 +10810,7 @@
       <c r="K522" s="10"/>
       <c r="L522" s="10"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row r="523" spans="1:12" ht="15.75" customHeight="1">
       <c r="A523" s="10"/>
       <c r="B523" s="10"/>
       <c r="C523" s="7"/>
@@ -10789,7 +10824,7 @@
       <c r="K523" s="10"/>
       <c r="L523" s="10"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row r="524" spans="1:12" ht="15.75" customHeight="1">
       <c r="A524" s="10"/>
       <c r="B524" s="10"/>
       <c r="C524" s="7"/>
@@ -10803,7 +10838,7 @@
       <c r="K524" s="10"/>
       <c r="L524" s="10"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row r="525" spans="1:12" ht="15.75" customHeight="1">
       <c r="A525" s="10"/>
       <c r="B525" s="10"/>
       <c r="C525" s="7"/>
@@ -10817,7 +10852,7 @@
       <c r="K525" s="10"/>
       <c r="L525" s="10"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row r="526" spans="1:12" ht="15.75" customHeight="1">
       <c r="A526" s="10"/>
       <c r="B526" s="10"/>
       <c r="C526" s="7"/>
@@ -10831,7 +10866,7 @@
       <c r="K526" s="10"/>
       <c r="L526" s="10"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row r="527" spans="1:12" ht="15.75" customHeight="1">
       <c r="A527" s="10"/>
       <c r="B527" s="10"/>
       <c r="C527" s="7"/>
@@ -10845,7 +10880,7 @@
       <c r="K527" s="10"/>
       <c r="L527" s="10"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row r="528" spans="1:12" ht="15.75" customHeight="1">
       <c r="A528" s="10"/>
       <c r="B528" s="10"/>
       <c r="C528" s="7"/>
@@ -10859,7 +10894,7 @@
       <c r="K528" s="10"/>
       <c r="L528" s="10"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row r="529" spans="1:12" ht="15.75" customHeight="1">
       <c r="A529" s="10"/>
       <c r="B529" s="10"/>
       <c r="C529" s="7"/>
@@ -10873,7 +10908,7 @@
       <c r="K529" s="10"/>
       <c r="L529" s="10"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row r="530" spans="1:12" ht="15.75" customHeight="1">
       <c r="A530" s="10"/>
       <c r="B530" s="10"/>
       <c r="C530" s="7"/>
@@ -10887,7 +10922,7 @@
       <c r="K530" s="10"/>
       <c r="L530" s="10"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row r="531" spans="1:12" ht="15.75" customHeight="1">
       <c r="A531" s="10"/>
       <c r="B531" s="10"/>
       <c r="C531" s="7"/>
@@ -10901,7 +10936,7 @@
       <c r="K531" s="10"/>
       <c r="L531" s="10"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row r="532" spans="1:12" ht="15.75" customHeight="1">
       <c r="A532" s="10"/>
       <c r="B532" s="10"/>
       <c r="C532" s="7"/>
@@ -10915,7 +10950,7 @@
       <c r="K532" s="10"/>
       <c r="L532" s="10"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row r="533" spans="1:12" ht="15.75" customHeight="1">
       <c r="A533" s="10"/>
       <c r="B533" s="10"/>
       <c r="C533" s="7"/>
@@ -10929,7 +10964,7 @@
       <c r="K533" s="10"/>
       <c r="L533" s="10"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row r="534" spans="1:12" ht="15.75" customHeight="1">
       <c r="A534" s="10"/>
       <c r="B534" s="10"/>
       <c r="C534" s="7"/>
@@ -10943,7 +10978,7 @@
       <c r="K534" s="10"/>
       <c r="L534" s="10"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row r="535" spans="1:12" ht="15.75" customHeight="1">
       <c r="A535" s="10"/>
       <c r="B535" s="10"/>
       <c r="C535" s="7"/>
@@ -10957,7 +10992,7 @@
       <c r="K535" s="10"/>
       <c r="L535" s="10"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row r="536" spans="1:12" ht="15.75" customHeight="1">
       <c r="A536" s="10"/>
       <c r="B536" s="10"/>
       <c r="C536" s="7"/>
@@ -10971,7 +11006,7 @@
       <c r="K536" s="10"/>
       <c r="L536" s="10"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row r="537" spans="1:12" ht="15.75" customHeight="1">
       <c r="A537" s="10"/>
       <c r="B537" s="10"/>
       <c r="C537" s="7"/>
@@ -10985,7 +11020,7 @@
       <c r="K537" s="10"/>
       <c r="L537" s="10"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row r="538" spans="1:12" ht="15.75" customHeight="1">
       <c r="A538" s="10"/>
       <c r="B538" s="10"/>
       <c r="C538" s="7"/>
@@ -10999,7 +11034,7 @@
       <c r="K538" s="10"/>
       <c r="L538" s="10"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row r="539" spans="1:12" ht="15.75" customHeight="1">
       <c r="A539" s="10"/>
       <c r="B539" s="10"/>
       <c r="C539" s="7"/>
@@ -11013,7 +11048,7 @@
       <c r="K539" s="10"/>
       <c r="L539" s="10"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row r="540" spans="1:12" ht="15.75" customHeight="1">
       <c r="A540" s="10"/>
       <c r="B540" s="10"/>
       <c r="C540" s="7"/>
@@ -11027,7 +11062,7 @@
       <c r="K540" s="10"/>
       <c r="L540" s="10"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row r="541" spans="1:12" ht="15.75" customHeight="1">
       <c r="A541" s="10"/>
       <c r="B541" s="10"/>
       <c r="C541" s="7"/>
@@ -11041,7 +11076,7 @@
       <c r="K541" s="10"/>
       <c r="L541" s="10"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row r="542" spans="1:12" ht="15.75" customHeight="1">
       <c r="A542" s="10"/>
       <c r="B542" s="10"/>
       <c r="C542" s="7"/>
@@ -11055,7 +11090,7 @@
       <c r="K542" s="10"/>
       <c r="L542" s="10"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row r="543" spans="1:12" ht="15.75" customHeight="1">
       <c r="A543" s="10"/>
       <c r="B543" s="10"/>
       <c r="C543" s="7"/>
@@ -11069,7 +11104,7 @@
       <c r="K543" s="10"/>
       <c r="L543" s="10"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row r="544" spans="1:12" ht="15.75" customHeight="1">
       <c r="A544" s="10"/>
       <c r="B544" s="10"/>
       <c r="C544" s="7"/>
@@ -11083,7 +11118,7 @@
       <c r="K544" s="10"/>
       <c r="L544" s="10"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row r="545" spans="1:12" ht="15.75" customHeight="1">
       <c r="A545" s="10"/>
       <c r="B545" s="10"/>
       <c r="C545" s="7"/>
@@ -11097,7 +11132,7 @@
       <c r="K545" s="10"/>
       <c r="L545" s="10"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row r="546" spans="1:12" ht="15.75" customHeight="1">
       <c r="A546" s="10"/>
       <c r="B546" s="10"/>
       <c r="C546" s="7"/>
@@ -11111,7 +11146,7 @@
       <c r="K546" s="10"/>
       <c r="L546" s="10"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row r="547" spans="1:12" ht="15.75" customHeight="1">
       <c r="A547" s="10"/>
       <c r="B547" s="10"/>
       <c r="C547" s="7"/>
@@ -11125,7 +11160,7 @@
       <c r="K547" s="10"/>
       <c r="L547" s="10"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row r="548" spans="1:12" ht="15.75" customHeight="1">
       <c r="A548" s="10"/>
       <c r="B548" s="10"/>
       <c r="C548" s="7"/>
@@ -11139,7 +11174,7 @@
       <c r="K548" s="10"/>
       <c r="L548" s="10"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row r="549" spans="1:12" ht="15.75" customHeight="1">
       <c r="A549" s="10"/>
       <c r="B549" s="10"/>
       <c r="C549" s="7"/>
@@ -11153,7 +11188,7 @@
       <c r="K549" s="10"/>
       <c r="L549" s="10"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row r="550" spans="1:12" ht="15.75" customHeight="1">
       <c r="A550" s="10"/>
       <c r="B550" s="10"/>
       <c r="C550" s="7"/>
@@ -11167,7 +11202,7 @@
       <c r="K550" s="10"/>
       <c r="L550" s="10"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row r="551" spans="1:12" ht="15.75" customHeight="1">
       <c r="A551" s="10"/>
       <c r="B551" s="10"/>
       <c r="C551" s="7"/>
@@ -11181,7 +11216,7 @@
       <c r="K551" s="10"/>
       <c r="L551" s="10"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row r="552" spans="1:12" ht="15.75" customHeight="1">
       <c r="A552" s="10"/>
       <c r="B552" s="10"/>
       <c r="C552" s="7"/>
@@ -11195,7 +11230,7 @@
       <c r="K552" s="10"/>
       <c r="L552" s="10"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row r="553" spans="1:12" ht="15.75" customHeight="1">
       <c r="A553" s="10"/>
       <c r="B553" s="10"/>
       <c r="C553" s="7"/>
@@ -11209,7 +11244,7 @@
       <c r="K553" s="10"/>
       <c r="L553" s="10"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row r="554" spans="1:12" ht="15.75" customHeight="1">
       <c r="A554" s="10"/>
       <c r="B554" s="10"/>
       <c r="C554" s="7"/>
@@ -11223,7 +11258,7 @@
       <c r="K554" s="10"/>
       <c r="L554" s="10"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row r="555" spans="1:12" ht="15.75" customHeight="1">
       <c r="A555" s="10"/>
       <c r="B555" s="10"/>
       <c r="C555" s="7"/>
@@ -11237,7 +11272,7 @@
       <c r="K555" s="10"/>
       <c r="L555" s="10"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row r="556" spans="1:12" ht="15.75" customHeight="1">
       <c r="A556" s="10"/>
       <c r="B556" s="10"/>
       <c r="C556" s="7"/>
@@ -11251,7 +11286,7 @@
       <c r="K556" s="10"/>
       <c r="L556" s="10"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row r="557" spans="1:12" ht="15.75" customHeight="1">
       <c r="A557" s="10"/>
       <c r="B557" s="10"/>
       <c r="C557" s="7"/>
@@ -11265,7 +11300,7 @@
       <c r="K557" s="10"/>
       <c r="L557" s="10"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row r="558" spans="1:12" ht="15.75" customHeight="1">
       <c r="A558" s="10"/>
       <c r="B558" s="10"/>
       <c r="C558" s="7"/>
@@ -11279,7 +11314,7 @@
       <c r="K558" s="10"/>
       <c r="L558" s="10"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row r="559" spans="1:12" ht="15.75" customHeight="1">
       <c r="A559" s="10"/>
       <c r="B559" s="10"/>
       <c r="C559" s="7"/>
@@ -11293,7 +11328,7 @@
       <c r="K559" s="10"/>
       <c r="L559" s="10"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row r="560" spans="1:12" ht="15.75" customHeight="1">
       <c r="A560" s="10"/>
       <c r="B560" s="10"/>
       <c r="C560" s="7"/>
@@ -11307,7 +11342,7 @@
       <c r="K560" s="10"/>
       <c r="L560" s="10"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row r="561" spans="1:12" ht="15.75" customHeight="1">
       <c r="A561" s="10"/>
       <c r="B561" s="10"/>
       <c r="C561" s="7"/>
@@ -11321,7 +11356,7 @@
       <c r="K561" s="10"/>
       <c r="L561" s="10"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row r="562" spans="1:12" ht="15.75" customHeight="1">
       <c r="A562" s="10"/>
       <c r="B562" s="10"/>
       <c r="C562" s="7"/>
@@ -11335,7 +11370,7 @@
       <c r="K562" s="10"/>
       <c r="L562" s="10"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row r="563" spans="1:12" ht="15.75" customHeight="1">
       <c r="A563" s="10"/>
       <c r="B563" s="10"/>
       <c r="C563" s="7"/>
@@ -11349,7 +11384,7 @@
       <c r="K563" s="10"/>
       <c r="L563" s="10"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row r="564" spans="1:12" ht="15.75" customHeight="1">
       <c r="A564" s="10"/>
       <c r="B564" s="10"/>
       <c r="C564" s="7"/>
@@ -11363,7 +11398,7 @@
       <c r="K564" s="10"/>
       <c r="L564" s="10"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row r="565" spans="1:12" ht="15.75" customHeight="1">
       <c r="A565" s="10"/>
       <c r="B565" s="10"/>
       <c r="C565" s="7"/>
@@ -11377,7 +11412,7 @@
       <c r="K565" s="10"/>
       <c r="L565" s="10"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row r="566" spans="1:12" ht="15.75" customHeight="1">
       <c r="A566" s="10"/>
       <c r="B566" s="10"/>
       <c r="C566" s="7"/>
@@ -11391,7 +11426,7 @@
       <c r="K566" s="10"/>
       <c r="L566" s="10"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row r="567" spans="1:12" ht="15.75" customHeight="1">
       <c r="A567" s="10"/>
       <c r="B567" s="10"/>
       <c r="C567" s="7"/>
@@ -11405,7 +11440,7 @@
       <c r="K567" s="10"/>
       <c r="L567" s="10"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row r="568" spans="1:12" ht="15.75" customHeight="1">
       <c r="A568" s="10"/>
       <c r="B568" s="10"/>
       <c r="C568" s="7"/>
@@ -11419,7 +11454,7 @@
       <c r="K568" s="10"/>
       <c r="L568" s="10"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row r="569" spans="1:12" ht="15.75" customHeight="1">
       <c r="A569" s="10"/>
       <c r="B569" s="10"/>
       <c r="C569" s="7"/>
@@ -11433,7 +11468,7 @@
       <c r="K569" s="10"/>
       <c r="L569" s="10"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row r="570" spans="1:12" ht="15.75" customHeight="1">
       <c r="A570" s="10"/>
       <c r="B570" s="10"/>
       <c r="C570" s="7"/>
@@ -11447,7 +11482,7 @@
       <c r="K570" s="10"/>
       <c r="L570" s="10"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row r="571" spans="1:12" ht="15.75" customHeight="1">
       <c r="A571" s="10"/>
       <c r="B571" s="10"/>
       <c r="C571" s="7"/>
@@ -11461,7 +11496,7 @@
       <c r="K571" s="10"/>
       <c r="L571" s="10"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row r="572" spans="1:12" ht="15.75" customHeight="1">
       <c r="A572" s="10"/>
       <c r="B572" s="10"/>
       <c r="C572" s="7"/>
@@ -11475,7 +11510,7 @@
       <c r="K572" s="10"/>
       <c r="L572" s="10"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row r="573" spans="1:12" ht="15.75" customHeight="1">
       <c r="A573" s="10"/>
       <c r="B573" s="10"/>
       <c r="C573" s="7"/>
@@ -11489,7 +11524,7 @@
       <c r="K573" s="10"/>
       <c r="L573" s="10"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row r="574" spans="1:12" ht="15.75" customHeight="1">
       <c r="A574" s="10"/>
       <c r="B574" s="10"/>
       <c r="C574" s="7"/>
@@ -11503,7 +11538,7 @@
       <c r="K574" s="10"/>
       <c r="L574" s="10"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row r="575" spans="1:12" ht="15.75" customHeight="1">
       <c r="A575" s="10"/>
       <c r="B575" s="10"/>
       <c r="C575" s="7"/>
@@ -11517,7 +11552,7 @@
       <c r="K575" s="10"/>
       <c r="L575" s="10"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row r="576" spans="1:12" ht="15.75" customHeight="1">
       <c r="A576" s="10"/>
       <c r="B576" s="10"/>
       <c r="C576" s="7"/>
@@ -11531,7 +11566,7 @@
       <c r="K576" s="10"/>
       <c r="L576" s="10"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row r="577" spans="1:12" ht="15.75" customHeight="1">
       <c r="A577" s="10"/>
       <c r="B577" s="10"/>
       <c r="C577" s="7"/>
@@ -11545,7 +11580,7 @@
       <c r="K577" s="10"/>
       <c r="L577" s="10"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row r="578" spans="1:12" ht="15.75" customHeight="1">
       <c r="A578" s="10"/>
       <c r="B578" s="10"/>
       <c r="C578" s="7"/>
@@ -11559,7 +11594,7 @@
       <c r="K578" s="10"/>
       <c r="L578" s="10"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row r="579" spans="1:12" ht="15.75" customHeight="1">
       <c r="A579" s="10"/>
       <c r="B579" s="10"/>
       <c r="C579" s="7"/>
@@ -11573,7 +11608,7 @@
       <c r="K579" s="10"/>
       <c r="L579" s="10"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row r="580" spans="1:12" ht="15.75" customHeight="1">
       <c r="A580" s="10"/>
       <c r="B580" s="10"/>
       <c r="C580" s="7"/>
@@ -11587,7 +11622,7 @@
       <c r="K580" s="10"/>
       <c r="L580" s="10"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row r="581" spans="1:12" ht="15.75" customHeight="1">
       <c r="A581" s="10"/>
       <c r="B581" s="10"/>
       <c r="C581" s="7"/>
@@ -11601,7 +11636,7 @@
       <c r="K581" s="10"/>
       <c r="L581" s="10"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row r="582" spans="1:12" ht="15.75" customHeight="1">
       <c r="A582" s="10"/>
       <c r="B582" s="10"/>
       <c r="C582" s="7"/>
@@ -11615,7 +11650,7 @@
       <c r="K582" s="10"/>
       <c r="L582" s="10"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row r="583" spans="1:12" ht="15.75" customHeight="1">
       <c r="A583" s="10"/>
       <c r="B583" s="10"/>
       <c r="C583" s="7"/>
@@ -11629,7 +11664,7 @@
       <c r="K583" s="10"/>
       <c r="L583" s="10"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row r="584" spans="1:12" ht="15.75" customHeight="1">
       <c r="A584" s="10"/>
       <c r="B584" s="10"/>
       <c r="C584" s="7"/>
@@ -11643,7 +11678,7 @@
       <c r="K584" s="10"/>
       <c r="L584" s="10"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row r="585" spans="1:12" ht="15.75" customHeight="1">
       <c r="A585" s="10"/>
       <c r="B585" s="10"/>
       <c r="C585" s="7"/>
@@ -11657,7 +11692,7 @@
       <c r="K585" s="10"/>
       <c r="L585" s="10"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row r="586" spans="1:12" ht="15.75" customHeight="1">
       <c r="A586" s="10"/>
       <c r="B586" s="10"/>
       <c r="C586" s="7"/>
@@ -11671,7 +11706,7 @@
       <c r="K586" s="10"/>
       <c r="L586" s="10"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row r="587" spans="1:12" ht="15.75" customHeight="1">
       <c r="A587" s="10"/>
       <c r="B587" s="10"/>
       <c r="C587" s="7"/>
@@ -11685,7 +11720,7 @@
       <c r="K587" s="10"/>
       <c r="L587" s="10"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row r="588" spans="1:12" ht="15.75" customHeight="1">
       <c r="A588" s="10"/>
       <c r="B588" s="10"/>
       <c r="C588" s="7"/>
@@ -11699,7 +11734,7 @@
       <c r="K588" s="10"/>
       <c r="L588" s="10"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row r="589" spans="1:12" ht="15.75" customHeight="1">
       <c r="A589" s="10"/>
       <c r="B589" s="10"/>
       <c r="C589" s="7"/>
@@ -11713,7 +11748,7 @@
       <c r="K589" s="10"/>
       <c r="L589" s="10"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row r="590" spans="1:12" ht="15.75" customHeight="1">
       <c r="A590" s="10"/>
       <c r="B590" s="10"/>
       <c r="C590" s="7"/>
@@ -11727,7 +11762,7 @@
       <c r="K590" s="10"/>
       <c r="L590" s="10"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row r="591" spans="1:12" ht="15.75" customHeight="1">
       <c r="A591" s="10"/>
       <c r="B591" s="10"/>
       <c r="C591" s="7"/>
@@ -11741,7 +11776,7 @@
       <c r="K591" s="10"/>
       <c r="L591" s="10"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row r="592" spans="1:12" ht="15.75" customHeight="1">
       <c r="A592" s="10"/>
       <c r="B592" s="10"/>
       <c r="C592" s="7"/>
@@ -11755,7 +11790,7 @@
       <c r="K592" s="10"/>
       <c r="L592" s="10"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row r="593" spans="1:12" ht="15.75" customHeight="1">
       <c r="A593" s="10"/>
       <c r="B593" s="10"/>
       <c r="C593" s="7"/>
@@ -11769,7 +11804,7 @@
       <c r="K593" s="10"/>
       <c r="L593" s="10"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row r="594" spans="1:12" ht="15.75" customHeight="1">
       <c r="A594" s="10"/>
       <c r="B594" s="10"/>
       <c r="C594" s="7"/>
@@ -11783,7 +11818,7 @@
       <c r="K594" s="10"/>
       <c r="L594" s="10"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row r="595" spans="1:12" ht="15.75" customHeight="1">
       <c r="A595" s="10"/>
       <c r="B595" s="10"/>
       <c r="C595" s="7"/>
@@ -11797,7 +11832,7 @@
       <c r="K595" s="10"/>
       <c r="L595" s="10"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row r="596" spans="1:12" ht="15.75" customHeight="1">
       <c r="A596" s="10"/>
       <c r="B596" s="10"/>
       <c r="C596" s="7"/>
@@ -11811,7 +11846,7 @@
       <c r="K596" s="10"/>
       <c r="L596" s="10"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row r="597" spans="1:12" ht="15.75" customHeight="1">
       <c r="A597" s="10"/>
       <c r="B597" s="10"/>
       <c r="C597" s="7"/>
@@ -11825,7 +11860,7 @@
       <c r="K597" s="10"/>
       <c r="L597" s="10"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row r="598" spans="1:12" ht="15.75" customHeight="1">
       <c r="A598" s="10"/>
       <c r="B598" s="10"/>
       <c r="C598" s="7"/>
@@ -11839,7 +11874,7 @@
       <c r="K598" s="10"/>
       <c r="L598" s="10"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row r="599" spans="1:12" ht="15.75" customHeight="1">
       <c r="A599" s="10"/>
       <c r="B599" s="10"/>
       <c r="C599" s="7"/>
@@ -11853,7 +11888,7 @@
       <c r="K599" s="10"/>
       <c r="L599" s="10"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row r="600" spans="1:12" ht="15.75" customHeight="1">
       <c r="A600" s="10"/>
       <c r="B600" s="10"/>
       <c r="C600" s="7"/>
@@ -11867,7 +11902,7 @@
       <c r="K600" s="10"/>
       <c r="L600" s="10"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row r="601" spans="1:12" ht="15.75" customHeight="1">
       <c r="A601" s="10"/>
       <c r="B601" s="10"/>
       <c r="C601" s="7"/>
@@ -11881,7 +11916,7 @@
       <c r="K601" s="10"/>
       <c r="L601" s="10"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row r="602" spans="1:12" ht="15.75" customHeight="1">
       <c r="A602" s="10"/>
       <c r="B602" s="10"/>
       <c r="C602" s="7"/>
@@ -11895,7 +11930,7 @@
       <c r="K602" s="10"/>
       <c r="L602" s="10"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row r="603" spans="1:12" ht="15.75" customHeight="1">
       <c r="A603" s="10"/>
       <c r="B603" s="10"/>
       <c r="C603" s="7"/>
@@ -11909,7 +11944,7 @@
       <c r="K603" s="10"/>
       <c r="L603" s="10"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row r="604" spans="1:12" ht="15.75" customHeight="1">
       <c r="A604" s="10"/>
       <c r="B604" s="10"/>
       <c r="C604" s="7"/>
@@ -11923,7 +11958,7 @@
       <c r="K604" s="10"/>
       <c r="L604" s="10"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row r="605" spans="1:12" ht="15.75" customHeight="1">
       <c r="A605" s="10"/>
       <c r="B605" s="10"/>
       <c r="C605" s="7"/>
@@ -11937,7 +11972,7 @@
       <c r="K605" s="10"/>
       <c r="L605" s="10"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row r="606" spans="1:12" ht="15.75" customHeight="1">
       <c r="A606" s="10"/>
       <c r="B606" s="10"/>
       <c r="C606" s="7"/>
@@ -11951,7 +11986,7 @@
       <c r="K606" s="10"/>
       <c r="L606" s="10"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row r="607" spans="1:12" ht="15.75" customHeight="1">
       <c r="A607" s="10"/>
       <c r="B607" s="10"/>
       <c r="C607" s="7"/>
@@ -11965,7 +12000,7 @@
       <c r="K607" s="10"/>
       <c r="L607" s="10"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row r="608" spans="1:12" ht="15.75" customHeight="1">
       <c r="A608" s="10"/>
       <c r="B608" s="10"/>
       <c r="C608" s="7"/>
@@ -11979,7 +12014,7 @@
       <c r="K608" s="10"/>
       <c r="L608" s="10"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row r="609" spans="1:12" ht="15.75" customHeight="1">
       <c r="A609" s="10"/>
       <c r="B609" s="10"/>
       <c r="C609" s="7"/>
@@ -11993,7 +12028,7 @@
       <c r="K609" s="10"/>
       <c r="L609" s="10"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row r="610" spans="1:12" ht="15.75" customHeight="1">
       <c r="A610" s="10"/>
       <c r="B610" s="10"/>
       <c r="C610" s="7"/>
@@ -12007,7 +12042,7 @@
       <c r="K610" s="10"/>
       <c r="L610" s="10"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row r="611" spans="1:12" ht="15.75" customHeight="1">
       <c r="A611" s="10"/>
       <c r="B611" s="10"/>
       <c r="C611" s="7"/>
@@ -12021,7 +12056,7 @@
       <c r="K611" s="10"/>
       <c r="L611" s="10"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row r="612" spans="1:12" ht="15.75" customHeight="1">
       <c r="A612" s="10"/>
       <c r="B612" s="10"/>
       <c r="C612" s="7"/>
@@ -12035,7 +12070,7 @@
       <c r="K612" s="10"/>
       <c r="L612" s="10"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row r="613" spans="1:12" ht="15.75" customHeight="1">
       <c r="A613" s="10"/>
       <c r="B613" s="10"/>
       <c r="C613" s="7"/>
@@ -12049,7 +12084,7 @@
       <c r="K613" s="10"/>
       <c r="L613" s="10"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row r="614" spans="1:12" ht="15.75" customHeight="1">
       <c r="A614" s="10"/>
       <c r="B614" s="10"/>
       <c r="C614" s="7"/>
@@ -12063,7 +12098,7 @@
       <c r="K614" s="10"/>
       <c r="L614" s="10"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row r="615" spans="1:12" ht="15.75" customHeight="1">
       <c r="A615" s="10"/>
       <c r="B615" s="10"/>
       <c r="C615" s="7"/>
@@ -12077,7 +12112,7 @@
       <c r="K615" s="10"/>
       <c r="L615" s="10"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row r="616" spans="1:12" ht="15.75" customHeight="1">
       <c r="A616" s="10"/>
       <c r="B616" s="10"/>
       <c r="C616" s="7"/>
@@ -12091,7 +12126,7 @@
       <c r="K616" s="10"/>
       <c r="L616" s="10"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row r="617" spans="1:12" ht="15.75" customHeight="1">
       <c r="A617" s="10"/>
       <c r="B617" s="10"/>
       <c r="C617" s="7"/>
@@ -12105,7 +12140,7 @@
       <c r="K617" s="10"/>
       <c r="L617" s="10"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row r="618" spans="1:12" ht="15.75" customHeight="1">
       <c r="A618" s="10"/>
       <c r="B618" s="10"/>
       <c r="C618" s="7"/>
@@ -12119,7 +12154,7 @@
       <c r="K618" s="10"/>
       <c r="L618" s="10"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row r="619" spans="1:12" ht="15.75" customHeight="1">
       <c r="A619" s="10"/>
       <c r="B619" s="10"/>
       <c r="C619" s="7"/>
@@ -12133,7 +12168,7 @@
       <c r="K619" s="10"/>
       <c r="L619" s="10"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row r="620" spans="1:12" ht="15.75" customHeight="1">
       <c r="A620" s="10"/>
       <c r="B620" s="10"/>
       <c r="C620" s="7"/>
@@ -12147,7 +12182,7 @@
       <c r="K620" s="10"/>
       <c r="L620" s="10"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row r="621" spans="1:12" ht="15.75" customHeight="1">
       <c r="A621" s="10"/>
       <c r="B621" s="10"/>
       <c r="C621" s="7"/>
@@ -12161,7 +12196,7 @@
       <c r="K621" s="10"/>
       <c r="L621" s="10"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row r="622" spans="1:12" ht="15.75" customHeight="1">
       <c r="A622" s="10"/>
       <c r="B622" s="10"/>
       <c r="C622" s="7"/>
@@ -12175,7 +12210,7 @@
       <c r="K622" s="10"/>
       <c r="L622" s="10"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row r="623" spans="1:12" ht="15.75" customHeight="1">
       <c r="A623" s="10"/>
       <c r="B623" s="10"/>
       <c r="C623" s="7"/>
@@ -12189,7 +12224,7 @@
       <c r="K623" s="10"/>
       <c r="L623" s="10"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row r="624" spans="1:12" ht="15.75" customHeight="1">
       <c r="A624" s="10"/>
       <c r="B624" s="10"/>
       <c r="C624" s="7"/>
@@ -12203,7 +12238,7 @@
       <c r="K624" s="10"/>
       <c r="L624" s="10"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row r="625" spans="1:12" ht="15.75" customHeight="1">
       <c r="A625" s="10"/>
       <c r="B625" s="10"/>
       <c r="C625" s="7"/>
@@ -12217,7 +12252,7 @@
       <c r="K625" s="10"/>
       <c r="L625" s="10"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row r="626" spans="1:12" ht="15.75" customHeight="1">
       <c r="A626" s="10"/>
       <c r="B626" s="10"/>
       <c r="C626" s="7"/>
@@ -12231,7 +12266,7 @@
       <c r="K626" s="10"/>
       <c r="L626" s="10"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row r="627" spans="1:12" ht="15.75" customHeight="1">
       <c r="A627" s="10"/>
       <c r="B627" s="10"/>
       <c r="C627" s="7"/>
@@ -12245,7 +12280,7 @@
       <c r="K627" s="10"/>
       <c r="L627" s="10"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row r="628" spans="1:12" ht="15.75" customHeight="1">
       <c r="A628" s="10"/>
       <c r="B628" s="10"/>
       <c r="C628" s="7"/>
@@ -12259,7 +12294,7 @@
       <c r="K628" s="10"/>
       <c r="L628" s="10"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row r="629" spans="1:12" ht="15.75" customHeight="1">
       <c r="A629" s="10"/>
       <c r="B629" s="10"/>
       <c r="C629" s="7"/>
@@ -12273,7 +12308,7 @@
       <c r="K629" s="10"/>
       <c r="L629" s="10"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row r="630" spans="1:12" ht="15.75" customHeight="1">
       <c r="A630" s="10"/>
       <c r="B630" s="10"/>
       <c r="C630" s="7"/>
@@ -12287,7 +12322,7 @@
       <c r="K630" s="10"/>
       <c r="L630" s="10"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row r="631" spans="1:12" ht="15.75" customHeight="1">
       <c r="A631" s="10"/>
       <c r="B631" s="10"/>
       <c r="C631" s="7"/>
@@ -12301,7 +12336,7 @@
       <c r="K631" s="10"/>
       <c r="L631" s="10"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row r="632" spans="1:12" ht="15.75" customHeight="1">
       <c r="A632" s="10"/>
       <c r="B632" s="10"/>
       <c r="C632" s="7"/>
@@ -12315,7 +12350,7 @@
       <c r="K632" s="10"/>
       <c r="L632" s="10"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row r="633" spans="1:12" ht="15.75" customHeight="1">
       <c r="A633" s="10"/>
       <c r="B633" s="10"/>
       <c r="C633" s="7"/>
@@ -12329,7 +12364,7 @@
       <c r="K633" s="10"/>
       <c r="L633" s="10"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row r="634" spans="1:12" ht="15.75" customHeight="1">
       <c r="A634" s="10"/>
       <c r="B634" s="10"/>
       <c r="C634" s="7"/>
@@ -12343,7 +12378,7 @@
       <c r="K634" s="10"/>
       <c r="L634" s="10"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row r="635" spans="1:12" ht="15.75" customHeight="1">
       <c r="A635" s="10"/>
       <c r="B635" s="10"/>
       <c r="C635" s="7"/>
@@ -12357,7 +12392,7 @@
       <c r="K635" s="10"/>
       <c r="L635" s="10"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row r="636" spans="1:12" ht="15.75" customHeight="1">
       <c r="A636" s="10"/>
       <c r="B636" s="10"/>
       <c r="C636" s="7"/>
@@ -12371,7 +12406,7 @@
       <c r="K636" s="10"/>
       <c r="L636" s="10"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row r="637" spans="1:12" ht="15.75" customHeight="1">
       <c r="A637" s="10"/>
       <c r="B637" s="10"/>
       <c r="C637" s="7"/>
@@ -12385,7 +12420,7 @@
       <c r="K637" s="10"/>
       <c r="L637" s="10"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row r="638" spans="1:12" ht="15.75" customHeight="1">
       <c r="A638" s="10"/>
       <c r="B638" s="10"/>
       <c r="C638" s="7"/>
@@ -12399,7 +12434,7 @@
       <c r="K638" s="10"/>
       <c r="L638" s="10"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row r="639" spans="1:12" ht="15.75" customHeight="1">
       <c r="A639" s="10"/>
       <c r="B639" s="10"/>
       <c r="C639" s="7"/>
@@ -12413,7 +12448,7 @@
       <c r="K639" s="10"/>
       <c r="L639" s="10"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row r="640" spans="1:12" ht="15.75" customHeight="1">
       <c r="A640" s="10"/>
       <c r="B640" s="10"/>
       <c r="C640" s="7"/>
@@ -12427,7 +12462,7 @@
       <c r="K640" s="10"/>
       <c r="L640" s="10"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row r="641" spans="1:12" ht="15.75" customHeight="1">
       <c r="A641" s="10"/>
       <c r="B641" s="10"/>
       <c r="C641" s="7"/>
@@ -12441,7 +12476,7 @@
       <c r="K641" s="10"/>
       <c r="L641" s="10"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row r="642" spans="1:12" ht="15.75" customHeight="1">
       <c r="A642" s="10"/>
       <c r="B642" s="10"/>
       <c r="C642" s="7"/>
@@ -12455,7 +12490,7 @@
       <c r="K642" s="10"/>
       <c r="L642" s="10"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row r="643" spans="1:12" ht="15.75" customHeight="1">
       <c r="A643" s="10"/>
       <c r="B643" s="10"/>
       <c r="C643" s="7"/>
@@ -12469,7 +12504,7 @@
       <c r="K643" s="10"/>
       <c r="L643" s="10"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row r="644" spans="1:12" ht="15.75" customHeight="1">
       <c r="A644" s="10"/>
       <c r="B644" s="10"/>
       <c r="C644" s="7"/>
@@ -12483,7 +12518,7 @@
       <c r="K644" s="10"/>
       <c r="L644" s="10"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row r="645" spans="1:12" ht="15.75" customHeight="1">
       <c r="A645" s="10"/>
       <c r="B645" s="10"/>
       <c r="C645" s="7"/>
@@ -12497,7 +12532,7 @@
       <c r="K645" s="10"/>
       <c r="L645" s="10"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row r="646" spans="1:12" ht="15.75" customHeight="1">
       <c r="A646" s="10"/>
       <c r="B646" s="10"/>
       <c r="C646" s="7"/>
@@ -12511,7 +12546,7 @@
       <c r="K646" s="10"/>
       <c r="L646" s="10"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row r="647" spans="1:12" ht="15.75" customHeight="1">
       <c r="A647" s="10"/>
       <c r="B647" s="10"/>
       <c r="C647" s="7"/>
@@ -12525,7 +12560,7 @@
       <c r="K647" s="10"/>
       <c r="L647" s="10"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row r="648" spans="1:12" ht="15.75" customHeight="1">
       <c r="A648" s="10"/>
       <c r="B648" s="10"/>
       <c r="C648" s="7"/>
@@ -12539,7 +12574,7 @@
       <c r="K648" s="10"/>
       <c r="L648" s="10"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row r="649" spans="1:12" ht="15.75" customHeight="1">
       <c r="A649" s="10"/>
       <c r="B649" s="10"/>
       <c r="C649" s="7"/>
@@ -12553,7 +12588,7 @@
       <c r="K649" s="10"/>
       <c r="L649" s="10"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row r="650" spans="1:12" ht="15.75" customHeight="1">
       <c r="A650" s="10"/>
       <c r="B650" s="10"/>
       <c r="C650" s="7"/>
@@ -12567,7 +12602,7 @@
       <c r="K650" s="10"/>
       <c r="L650" s="10"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row r="651" spans="1:12" ht="15.75" customHeight="1">
       <c r="A651" s="10"/>
       <c r="B651" s="10"/>
       <c r="C651" s="7"/>
@@ -12581,7 +12616,7 @@
       <c r="K651" s="10"/>
       <c r="L651" s="10"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row r="652" spans="1:12" ht="15.75" customHeight="1">
       <c r="A652" s="10"/>
       <c r="B652" s="10"/>
       <c r="C652" s="7"/>
@@ -12595,7 +12630,7 @@
       <c r="K652" s="10"/>
       <c r="L652" s="10"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row r="653" spans="1:12" ht="15.75" customHeight="1">
       <c r="A653" s="10"/>
       <c r="B653" s="10"/>
       <c r="C653" s="7"/>
@@ -12609,7 +12644,7 @@
       <c r="K653" s="10"/>
       <c r="L653" s="10"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row r="654" spans="1:12" ht="15.75" customHeight="1">
       <c r="A654" s="10"/>
       <c r="B654" s="10"/>
       <c r="C654" s="7"/>
@@ -12623,7 +12658,7 @@
       <c r="K654" s="10"/>
       <c r="L654" s="10"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row r="655" spans="1:12" ht="15.75" customHeight="1">
       <c r="A655" s="10"/>
       <c r="B655" s="10"/>
       <c r="C655" s="7"/>
@@ -12637,7 +12672,7 @@
       <c r="K655" s="10"/>
       <c r="L655" s="10"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row r="656" spans="1:12" ht="15.75" customHeight="1">
       <c r="A656" s="10"/>
       <c r="B656" s="10"/>
       <c r="C656" s="7"/>
@@ -12651,7 +12686,7 @@
       <c r="K656" s="10"/>
       <c r="L656" s="10"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row r="657" spans="1:12" ht="15.75" customHeight="1">
       <c r="A657" s="10"/>
       <c r="B657" s="10"/>
       <c r="C657" s="7"/>
@@ -12665,7 +12700,7 @@
       <c r="K657" s="10"/>
       <c r="L657" s="10"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row r="658" spans="1:12" ht="15.75" customHeight="1">
       <c r="A658" s="10"/>
       <c r="B658" s="10"/>
       <c r="C658" s="7"/>
@@ -12679,7 +12714,7 @@
       <c r="K658" s="10"/>
       <c r="L658" s="10"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row r="659" spans="1:12" ht="15.75" customHeight="1">
       <c r="A659" s="10"/>
       <c r="B659" s="10"/>
       <c r="C659" s="7"/>
@@ -12693,7 +12728,7 @@
       <c r="K659" s="10"/>
       <c r="L659" s="10"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row r="660" spans="1:12" ht="15.75" customHeight="1">
       <c r="A660" s="10"/>
       <c r="B660" s="10"/>
       <c r="C660" s="7"/>
@@ -12707,7 +12742,7 @@
       <c r="K660" s="10"/>
       <c r="L660" s="10"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row r="661" spans="1:12" ht="15.75" customHeight="1">
       <c r="A661" s="10"/>
       <c r="B661" s="10"/>
       <c r="C661" s="7"/>
@@ -12721,7 +12756,7 @@
       <c r="K661" s="10"/>
       <c r="L661" s="10"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row r="662" spans="1:12" ht="15.75" customHeight="1">
       <c r="A662" s="10"/>
       <c r="B662" s="10"/>
       <c r="C662" s="7"/>
@@ -12735,7 +12770,7 @@
       <c r="K662" s="10"/>
       <c r="L662" s="10"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row r="663" spans="1:12" ht="15.75" customHeight="1">
       <c r="A663" s="10"/>
       <c r="B663" s="10"/>
       <c r="C663" s="7"/>
@@ -12749,7 +12784,7 @@
       <c r="K663" s="10"/>
       <c r="L663" s="10"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row r="664" spans="1:12" ht="15.75" customHeight="1">
       <c r="A664" s="10"/>
       <c r="B664" s="10"/>
       <c r="C664" s="7"/>
@@ -12763,7 +12798,7 @@
       <c r="K664" s="10"/>
       <c r="L664" s="10"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row r="665" spans="1:12" ht="15.75" customHeight="1">
       <c r="A665" s="10"/>
       <c r="B665" s="10"/>
       <c r="C665" s="7"/>
@@ -12777,7 +12812,7 @@
       <c r="K665" s="10"/>
       <c r="L665" s="10"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row r="666" spans="1:12" ht="15.75" customHeight="1">
       <c r="A666" s="10"/>
       <c r="B666" s="10"/>
       <c r="C666" s="7"/>
@@ -12791,7 +12826,7 @@
       <c r="K666" s="10"/>
       <c r="L666" s="10"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row r="667" spans="1:12" ht="15.75" customHeight="1">
       <c r="A667" s="10"/>
       <c r="B667" s="10"/>
       <c r="C667" s="7"/>
@@ -12805,7 +12840,7 @@
       <c r="K667" s="10"/>
       <c r="L667" s="10"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row r="668" spans="1:12" ht="15.75" customHeight="1">
       <c r="A668" s="10"/>
       <c r="B668" s="10"/>
       <c r="C668" s="7"/>
@@ -12819,7 +12854,7 @@
       <c r="K668" s="10"/>
       <c r="L668" s="10"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row r="669" spans="1:12" ht="15.75" customHeight="1">
       <c r="A669" s="10"/>
       <c r="B669" s="10"/>
       <c r="C669" s="7"/>
@@ -12833,7 +12868,7 @@
       <c r="K669" s="10"/>
       <c r="L669" s="10"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row r="670" spans="1:12" ht="15.75" customHeight="1">
       <c r="A670" s="10"/>
       <c r="B670" s="10"/>
       <c r="C670" s="7"/>
@@ -12847,7 +12882,7 @@
       <c r="K670" s="10"/>
       <c r="L670" s="10"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row r="671" spans="1:12" ht="15.75" customHeight="1">
       <c r="A671" s="10"/>
       <c r="B671" s="10"/>
       <c r="C671" s="7"/>
@@ -12861,7 +12896,7 @@
       <c r="K671" s="10"/>
       <c r="L671" s="10"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row r="672" spans="1:12" ht="15.75" customHeight="1">
       <c r="A672" s="10"/>
       <c r="B672" s="10"/>
       <c r="C672" s="7"/>
@@ -12875,7 +12910,7 @@
       <c r="K672" s="10"/>
       <c r="L672" s="10"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row r="673" spans="1:12" ht="15.75" customHeight="1">
       <c r="A673" s="10"/>
       <c r="B673" s="10"/>
       <c r="C673" s="7"/>
@@ -12889,7 +12924,7 @@
       <c r="K673" s="10"/>
       <c r="L673" s="10"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row r="674" spans="1:12" ht="15.75" customHeight="1">
       <c r="A674" s="10"/>
       <c r="B674" s="10"/>
       <c r="C674" s="7"/>
@@ -12903,7 +12938,7 @@
       <c r="K674" s="10"/>
       <c r="L674" s="10"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row r="675" spans="1:12" ht="15.75" customHeight="1">
       <c r="A675" s="10"/>
       <c r="B675" s="10"/>
       <c r="C675" s="7"/>
@@ -12917,7 +12952,7 @@
       <c r="K675" s="10"/>
       <c r="L675" s="10"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row r="676" spans="1:12" ht="15.75" customHeight="1">
       <c r="A676" s="10"/>
       <c r="B676" s="10"/>
       <c r="C676" s="7"/>
@@ -12931,7 +12966,7 @@
       <c r="K676" s="10"/>
       <c r="L676" s="10"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row r="677" spans="1:12" ht="15.75" customHeight="1">
       <c r="A677" s="10"/>
       <c r="B677" s="10"/>
       <c r="C677" s="7"/>
@@ -12945,7 +12980,7 @@
       <c r="K677" s="10"/>
       <c r="L677" s="10"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row r="678" spans="1:12" ht="15.75" customHeight="1">
       <c r="A678" s="10"/>
       <c r="B678" s="10"/>
       <c r="C678" s="7"/>
@@ -12959,7 +12994,7 @@
       <c r="K678" s="10"/>
       <c r="L678" s="10"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row r="679" spans="1:12" ht="15.75" customHeight="1">
       <c r="A679" s="10"/>
       <c r="B679" s="10"/>
       <c r="C679" s="7"/>
@@ -12973,7 +13008,7 @@
       <c r="K679" s="10"/>
       <c r="L679" s="10"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row r="680" spans="1:12" ht="15.75" customHeight="1">
       <c r="A680" s="10"/>
       <c r="B680" s="10"/>
       <c r="C680" s="7"/>
@@ -12987,7 +13022,7 @@
       <c r="K680" s="10"/>
       <c r="L680" s="10"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row r="681" spans="1:12" ht="15.75" customHeight="1">
       <c r="A681" s="10"/>
       <c r="B681" s="10"/>
       <c r="C681" s="7"/>
@@ -13001,7 +13036,7 @@
       <c r="K681" s="10"/>
       <c r="L681" s="10"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row r="682" spans="1:12" ht="15.75" customHeight="1">
       <c r="A682" s="10"/>
       <c r="B682" s="10"/>
       <c r="C682" s="7"/>
@@ -13015,7 +13050,7 @@
       <c r="K682" s="10"/>
       <c r="L682" s="10"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row r="683" spans="1:12" ht="15.75" customHeight="1">
       <c r="A683" s="10"/>
       <c r="B683" s="10"/>
       <c r="C683" s="7"/>
@@ -13029,7 +13064,7 @@
       <c r="K683" s="10"/>
       <c r="L683" s="10"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row r="684" spans="1:12" ht="15.75" customHeight="1">
       <c r="A684" s="10"/>
       <c r="B684" s="10"/>
       <c r="C684" s="7"/>
@@ -13043,7 +13078,7 @@
       <c r="K684" s="10"/>
       <c r="L684" s="10"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row r="685" spans="1:12" ht="15.75" customHeight="1">
       <c r="A685" s="10"/>
       <c r="B685" s="10"/>
       <c r="C685" s="7"/>
@@ -13057,7 +13092,7 @@
       <c r="K685" s="10"/>
       <c r="L685" s="10"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row r="686" spans="1:12" ht="15.75" customHeight="1">
       <c r="A686" s="10"/>
       <c r="B686" s="10"/>
       <c r="C686" s="7"/>
@@ -13071,7 +13106,7 @@
       <c r="K686" s="10"/>
       <c r="L686" s="10"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row r="687" spans="1:12" ht="15.75" customHeight="1">
       <c r="A687" s="10"/>
       <c r="B687" s="10"/>
       <c r="C687" s="7"/>
@@ -13085,7 +13120,7 @@
       <c r="K687" s="10"/>
       <c r="L687" s="10"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row r="688" spans="1:12" ht="15.75" customHeight="1">
       <c r="A688" s="10"/>
       <c r="B688" s="10"/>
       <c r="C688" s="7"/>
@@ -13099,7 +13134,7 @@
       <c r="K688" s="10"/>
       <c r="L688" s="10"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row r="689" spans="1:12" ht="15.75" customHeight="1">
       <c r="A689" s="10"/>
       <c r="B689" s="10"/>
       <c r="C689" s="7"/>
@@ -13113,7 +13148,7 @@
       <c r="K689" s="10"/>
       <c r="L689" s="10"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row r="690" spans="1:12" ht="15.75" customHeight="1">
       <c r="A690" s="10"/>
       <c r="B690" s="10"/>
       <c r="C690" s="7"/>
@@ -13127,7 +13162,7 @@
       <c r="K690" s="10"/>
       <c r="L690" s="10"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row r="691" spans="1:12" ht="15.75" customHeight="1">
       <c r="A691" s="10"/>
       <c r="B691" s="10"/>
       <c r="C691" s="7"/>
@@ -13141,7 +13176,7 @@
       <c r="K691" s="10"/>
       <c r="L691" s="10"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row r="692" spans="1:12" ht="15.75" customHeight="1">
       <c r="A692" s="10"/>
       <c r="B692" s="10"/>
       <c r="C692" s="7"/>
@@ -13155,7 +13190,7 @@
       <c r="K692" s="10"/>
       <c r="L692" s="10"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row r="693" spans="1:12" ht="15.75" customHeight="1">
       <c r="A693" s="10"/>
       <c r="B693" s="10"/>
       <c r="C693" s="7"/>
@@ -13169,7 +13204,7 @@
       <c r="K693" s="10"/>
       <c r="L693" s="10"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row r="694" spans="1:12" ht="15.75" customHeight="1">
       <c r="A694" s="10"/>
       <c r="B694" s="10"/>
       <c r="C694" s="7"/>
@@ -13183,7 +13218,7 @@
       <c r="K694" s="10"/>
       <c r="L694" s="10"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row r="695" spans="1:12" ht="15.75" customHeight="1">
       <c r="A695" s="10"/>
       <c r="B695" s="10"/>
       <c r="C695" s="7"/>
@@ -13197,7 +13232,7 @@
       <c r="K695" s="10"/>
       <c r="L695" s="10"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row r="696" spans="1:12" ht="15.75" customHeight="1">
       <c r="A696" s="10"/>
       <c r="B696" s="10"/>
       <c r="C696" s="7"/>
@@ -13211,7 +13246,7 @@
       <c r="K696" s="10"/>
       <c r="L696" s="10"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row r="697" spans="1:12" ht="15.75" customHeight="1">
       <c r="A697" s="10"/>
       <c r="B697" s="10"/>
       <c r="C697" s="7"/>
@@ -13225,7 +13260,7 @@
       <c r="K697" s="10"/>
       <c r="L697" s="10"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row r="698" spans="1:12" ht="15.75" customHeight="1">
       <c r="A698" s="10"/>
       <c r="B698" s="10"/>
       <c r="C698" s="7"/>
@@ -13239,7 +13274,7 @@
       <c r="K698" s="10"/>
       <c r="L698" s="10"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row r="699" spans="1:12" ht="15.75" customHeight="1">
       <c r="A699" s="10"/>
       <c r="B699" s="10"/>
       <c r="C699" s="7"/>
@@ -13253,7 +13288,7 @@
       <c r="K699" s="10"/>
       <c r="L699" s="10"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row r="700" spans="1:12" ht="15.75" customHeight="1">
       <c r="A700" s="10"/>
       <c r="B700" s="10"/>
       <c r="C700" s="7"/>
@@ -13267,7 +13302,7 @@
       <c r="K700" s="10"/>
       <c r="L700" s="10"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row r="701" spans="1:12" ht="15.75" customHeight="1">
       <c r="A701" s="10"/>
       <c r="B701" s="10"/>
       <c r="C701" s="7"/>
@@ -13281,7 +13316,7 @@
       <c r="K701" s="10"/>
       <c r="L701" s="10"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row r="702" spans="1:12" ht="15.75" customHeight="1">
       <c r="A702" s="10"/>
       <c r="B702" s="10"/>
       <c r="C702" s="7"/>
@@ -13295,7 +13330,7 @@
       <c r="K702" s="10"/>
       <c r="L702" s="10"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row r="703" spans="1:12" ht="15.75" customHeight="1">
       <c r="A703" s="10"/>
       <c r="B703" s="10"/>
       <c r="C703" s="7"/>
@@ -13309,7 +13344,7 @@
       <c r="K703" s="10"/>
       <c r="L703" s="10"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row r="704" spans="1:12" ht="15.75" customHeight="1">
       <c r="A704" s="10"/>
       <c r="B704" s="10"/>
       <c r="C704" s="7"/>
@@ -13323,7 +13358,7 @@
       <c r="K704" s="10"/>
       <c r="L704" s="10"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row r="705" spans="1:12" ht="15.75" customHeight="1">
       <c r="A705" s="10"/>
       <c r="B705" s="10"/>
       <c r="C705" s="7"/>
@@ -13337,7 +13372,7 @@
       <c r="K705" s="10"/>
       <c r="L705" s="10"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row r="706" spans="1:12" ht="15.75" customHeight="1">
       <c r="A706" s="10"/>
       <c r="B706" s="10"/>
       <c r="C706" s="7"/>
@@ -13351,7 +13386,7 @@
       <c r="K706" s="10"/>
       <c r="L706" s="10"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row r="707" spans="1:12" ht="15.75" customHeight="1">
       <c r="A707" s="10"/>
       <c r="B707" s="10"/>
       <c r="C707" s="7"/>
@@ -13365,7 +13400,7 @@
       <c r="K707" s="10"/>
       <c r="L707" s="10"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row r="708" spans="1:12" ht="15.75" customHeight="1">
       <c r="A708" s="10"/>
       <c r="B708" s="10"/>
       <c r="C708" s="7"/>
@@ -13379,7 +13414,7 @@
       <c r="K708" s="10"/>
       <c r="L708" s="10"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row r="709" spans="1:12" ht="15.75" customHeight="1">
       <c r="A709" s="10"/>
       <c r="B709" s="10"/>
       <c r="C709" s="7"/>
@@ -13393,7 +13428,7 @@
       <c r="K709" s="10"/>
       <c r="L709" s="10"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row r="710" spans="1:12" ht="15.75" customHeight="1">
       <c r="A710" s="10"/>
       <c r="B710" s="10"/>
       <c r="C710" s="7"/>
@@ -13407,7 +13442,7 @@
       <c r="K710" s="10"/>
       <c r="L710" s="10"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row r="711" spans="1:12" ht="15.75" customHeight="1">
       <c r="A711" s="10"/>
       <c r="B711" s="10"/>
       <c r="C711" s="7"/>
@@ -13421,7 +13456,7 @@
       <c r="K711" s="10"/>
       <c r="L711" s="10"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row r="712" spans="1:12" ht="15.75" customHeight="1">
       <c r="A712" s="10"/>
       <c r="B712" s="10"/>
       <c r="C712" s="7"/>
@@ -13435,7 +13470,7 @@
       <c r="K712" s="10"/>
       <c r="L712" s="10"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row r="713" spans="1:12" ht="15.75" customHeight="1">
       <c r="A713" s="10"/>
       <c r="B713" s="10"/>
       <c r="C713" s="7"/>
@@ -13449,7 +13484,7 @@
       <c r="K713" s="10"/>
       <c r="L713" s="10"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row r="714" spans="1:12" ht="15.75" customHeight="1">
       <c r="A714" s="10"/>
       <c r="B714" s="10"/>
       <c r="C714" s="7"/>
@@ -13463,7 +13498,7 @@
       <c r="K714" s="10"/>
       <c r="L714" s="10"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row r="715" spans="1:12" ht="15.75" customHeight="1">
       <c r="A715" s="10"/>
       <c r="B715" s="10"/>
       <c r="C715" s="7"/>
@@ -13477,7 +13512,7 @@
       <c r="K715" s="10"/>
       <c r="L715" s="10"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row r="716" spans="1:12" ht="15.75" customHeight="1">
       <c r="A716" s="10"/>
       <c r="B716" s="10"/>
       <c r="C716" s="7"/>
@@ -13491,7 +13526,7 @@
       <c r="K716" s="10"/>
       <c r="L716" s="10"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row r="717" spans="1:12" ht="15.75" customHeight="1">
       <c r="A717" s="10"/>
       <c r="B717" s="10"/>
       <c r="C717" s="7"/>
@@ -13505,7 +13540,7 @@
       <c r="K717" s="10"/>
       <c r="L717" s="10"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row r="718" spans="1:12" ht="15.75" customHeight="1">
       <c r="A718" s="10"/>
       <c r="B718" s="10"/>
       <c r="C718" s="7"/>
@@ -13519,7 +13554,7 @@
       <c r="K718" s="10"/>
       <c r="L718" s="10"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row r="719" spans="1:12" ht="15.75" customHeight="1">
       <c r="A719" s="10"/>
       <c r="B719" s="10"/>
       <c r="C719" s="7"/>
@@ -13533,7 +13568,7 @@
       <c r="K719" s="10"/>
       <c r="L719" s="10"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row r="720" spans="1:12" ht="15.75" customHeight="1">
       <c r="A720" s="10"/>
       <c r="B720" s="10"/>
       <c r="C720" s="7"/>
@@ -13547,7 +13582,7 @@
       <c r="K720" s="10"/>
       <c r="L720" s="10"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row r="721" spans="1:12" ht="15.75" customHeight="1">
       <c r="A721" s="10"/>
       <c r="B721" s="10"/>
       <c r="C721" s="7"/>
@@ -13561,7 +13596,7 @@
       <c r="K721" s="10"/>
       <c r="L721" s="10"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row r="722" spans="1:12" ht="15.75" customHeight="1">
       <c r="A722" s="10"/>
       <c r="B722" s="10"/>
       <c r="C722" s="7"/>
@@ -13575,7 +13610,7 @@
       <c r="K722" s="10"/>
       <c r="L722" s="10"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row r="723" spans="1:12" ht="15.75" customHeight="1">
       <c r="A723" s="10"/>
       <c r="B723" s="10"/>
       <c r="C723" s="7"/>
@@ -13589,7 +13624,7 @@
       <c r="K723" s="10"/>
       <c r="L723" s="10"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row r="724" spans="1:12" ht="15.75" customHeight="1">
       <c r="A724" s="10"/>
       <c r="B724" s="10"/>
       <c r="C724" s="7"/>
@@ -13603,7 +13638,7 @@
       <c r="K724" s="10"/>
       <c r="L724" s="10"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row r="725" spans="1:12" ht="15.75" customHeight="1">
       <c r="A725" s="10"/>
       <c r="B725" s="10"/>
       <c r="C725" s="7"/>
@@ -13617,7 +13652,7 @@
       <c r="K725" s="10"/>
       <c r="L725" s="10"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row r="726" spans="1:12" ht="15.75" customHeight="1">
       <c r="A726" s="10"/>
       <c r="B726" s="10"/>
       <c r="C726" s="7"/>
@@ -13631,7 +13666,7 @@
       <c r="K726" s="10"/>
       <c r="L726" s="10"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row r="727" spans="1:12" ht="15.75" customHeight="1">
       <c r="A727" s="10"/>
       <c r="B727" s="10"/>
       <c r="C727" s="7"/>
@@ -13645,7 +13680,7 @@
       <c r="K727" s="10"/>
       <c r="L727" s="10"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row r="728" spans="1:12" ht="15.75" customHeight="1">
       <c r="A728" s="10"/>
       <c r="B728" s="10"/>
       <c r="C728" s="7"/>
@@ -13659,7 +13694,7 @@
       <c r="K728" s="10"/>
       <c r="L728" s="10"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row r="729" spans="1:12" ht="15.75" customHeight="1">
       <c r="A729" s="10"/>
       <c r="B729" s="10"/>
       <c r="C729" s="7"/>
@@ -13673,7 +13708,7 @@
       <c r="K729" s="10"/>
       <c r="L729" s="10"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row r="730" spans="1:12" ht="15.75" customHeight="1">
       <c r="A730" s="10"/>
       <c r="B730" s="10"/>
       <c r="C730" s="7"/>
@@ -13687,7 +13722,7 @@
       <c r="K730" s="10"/>
       <c r="L730" s="10"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row r="731" spans="1:12" ht="15.75" customHeight="1">
       <c r="A731" s="10"/>
       <c r="B731" s="10"/>
       <c r="C731" s="7"/>
@@ -13701,7 +13736,7 @@
       <c r="K731" s="10"/>
       <c r="L731" s="10"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row r="732" spans="1:12" ht="15.75" customHeight="1">
       <c r="A732" s="10"/>
       <c r="B732" s="10"/>
       <c r="C732" s="7"/>
@@ -13715,7 +13750,7 @@
       <c r="K732" s="10"/>
       <c r="L732" s="10"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row r="733" spans="1:12" ht="15.75" customHeight="1">
       <c r="A733" s="10"/>
       <c r="B733" s="10"/>
       <c r="C733" s="7"/>
@@ -13729,7 +13764,7 @@
       <c r="K733" s="10"/>
       <c r="L733" s="10"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row r="734" spans="1:12" ht="15.75" customHeight="1">
       <c r="A734" s="10"/>
       <c r="B734" s="10"/>
       <c r="C734" s="7"/>
@@ -13743,7 +13778,7 @@
       <c r="K734" s="10"/>
       <c r="L734" s="10"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row r="735" spans="1:12" ht="15.75" customHeight="1">
       <c r="A735" s="10"/>
       <c r="B735" s="10"/>
       <c r="C735" s="7"/>
@@ -13757,7 +13792,7 @@
       <c r="K735" s="10"/>
       <c r="L735" s="10"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row r="736" spans="1:12" ht="15.75" customHeight="1">
       <c r="A736" s="10"/>
       <c r="B736" s="10"/>
       <c r="C736" s="7"/>
@@ -13771,7 +13806,7 @@
       <c r="K736" s="10"/>
       <c r="L736" s="10"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row r="737" spans="1:12" ht="15.75" customHeight="1">
       <c r="A737" s="10"/>
       <c r="B737" s="10"/>
       <c r="C737" s="7"/>
@@ -13785,7 +13820,7 @@
       <c r="K737" s="10"/>
       <c r="L737" s="10"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row r="738" spans="1:12" ht="15.75" customHeight="1">
       <c r="A738" s="10"/>
       <c r="B738" s="10"/>
       <c r="C738" s="7"/>
@@ -13799,7 +13834,7 @@
       <c r="K738" s="10"/>
       <c r="L738" s="10"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row r="739" spans="1:12" ht="15.75" customHeight="1">
       <c r="A739" s="10"/>
       <c r="B739" s="10"/>
       <c r="C739" s="7"/>
@@ -13813,7 +13848,7 @@
       <c r="K739" s="10"/>
       <c r="L739" s="10"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row r="740" spans="1:12" ht="15.75" customHeight="1">
       <c r="A740" s="10"/>
       <c r="B740" s="10"/>
       <c r="C740" s="7"/>
@@ -13827,7 +13862,7 @@
       <c r="K740" s="10"/>
       <c r="L740" s="10"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row r="741" spans="1:12" ht="15.75" customHeight="1">
       <c r="A741" s="10"/>
       <c r="B741" s="10"/>
       <c r="C741" s="7"/>
@@ -13841,7 +13876,7 @@
       <c r="K741" s="10"/>
       <c r="L741" s="10"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row r="742" spans="1:12" ht="15.75" customHeight="1">
       <c r="A742" s="10"/>
       <c r="B742" s="10"/>
       <c r="C742" s="7"/>
@@ -13855,7 +13890,7 @@
       <c r="K742" s="10"/>
       <c r="L742" s="10"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row r="743" spans="1:12" ht="15.75" customHeight="1">
       <c r="A743" s="10"/>
       <c r="B743" s="10"/>
       <c r="C743" s="7"/>
@@ -13869,7 +13904,7 @@
       <c r="K743" s="10"/>
       <c r="L743" s="10"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row r="744" spans="1:12" ht="15.75" customHeight="1">
       <c r="A744" s="10"/>
       <c r="B744" s="10"/>
       <c r="C744" s="7"/>
@@ -13883,7 +13918,7 @@
       <c r="K744" s="10"/>
       <c r="L744" s="10"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row r="745" spans="1:12" ht="15.75" customHeight="1">
       <c r="A745" s="10"/>
       <c r="B745" s="10"/>
       <c r="C745" s="7"/>
@@ -13897,7 +13932,7 @@
       <c r="K745" s="10"/>
       <c r="L745" s="10"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row r="746" spans="1:12" ht="15.75" customHeight="1">
       <c r="A746" s="10"/>
       <c r="B746" s="10"/>
       <c r="C746" s="7"/>
@@ -13911,7 +13946,7 @@
       <c r="K746" s="10"/>
       <c r="L746" s="10"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row r="747" spans="1:12" ht="15.75" customHeight="1">
       <c r="A747" s="10"/>
       <c r="B747" s="10"/>
       <c r="C747" s="7"/>
@@ -13925,7 +13960,7 @@
       <c r="K747" s="10"/>
       <c r="L747" s="10"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row r="748" spans="1:12" ht="15.75" customHeight="1">
       <c r="A748" s="10"/>
       <c r="B748" s="10"/>
       <c r="C748" s="7"/>
@@ -13939,7 +13974,7 @@
       <c r="K748" s="10"/>
       <c r="L748" s="10"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row r="749" spans="1:12" ht="15.75" customHeight="1">
       <c r="A749" s="10"/>
       <c r="B749" s="10"/>
       <c r="C749" s="7"/>
@@ -13953,7 +13988,7 @@
       <c r="K749" s="10"/>
       <c r="L749" s="10"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row r="750" spans="1:12" ht="15.75" customHeight="1">
       <c r="A750" s="10"/>
       <c r="B750" s="10"/>
       <c r="C750" s="7"/>
@@ -13967,7 +14002,7 @@
       <c r="K750" s="10"/>
       <c r="L750" s="10"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row r="751" spans="1:12" ht="15.75" customHeight="1">
       <c r="A751" s="10"/>
       <c r="B751" s="10"/>
       <c r="C751" s="7"/>
@@ -13981,7 +14016,7 @@
       <c r="K751" s="10"/>
       <c r="L751" s="10"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row r="752" spans="1:12" ht="15.75" customHeight="1">
       <c r="A752" s="10"/>
       <c r="B752" s="10"/>
       <c r="C752" s="7"/>
@@ -13995,7 +14030,7 @@
       <c r="K752" s="10"/>
       <c r="L752" s="10"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row r="753" spans="1:12" ht="15.75" customHeight="1">
       <c r="A753" s="10"/>
       <c r="B753" s="10"/>
       <c r="C753" s="7"/>
@@ -14009,7 +14044,7 @@
       <c r="K753" s="10"/>
       <c r="L753" s="10"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row r="754" spans="1:12" ht="15.75" customHeight="1">
       <c r="A754" s="10"/>
       <c r="B754" s="10"/>
       <c r="C754" s="7"/>
@@ -14023,7 +14058,7 @@
       <c r="K754" s="10"/>
       <c r="L754" s="10"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row r="755" spans="1:12" ht="15.75" customHeight="1">
       <c r="A755" s="10"/>
       <c r="B755" s="10"/>
       <c r="C755" s="7"/>
@@ -14037,7 +14072,7 @@
       <c r="K755" s="10"/>
       <c r="L755" s="10"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row r="756" spans="1:12" ht="15.75" customHeight="1">
       <c r="A756" s="10"/>
       <c r="B756" s="10"/>
       <c r="C756" s="7"/>
@@ -14051,7 +14086,7 @@
       <c r="K756" s="10"/>
       <c r="L756" s="10"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row r="757" spans="1:12" ht="15.75" customHeight="1">
       <c r="A757" s="10"/>
       <c r="B757" s="10"/>
       <c r="C757" s="7"/>
@@ -14065,7 +14100,7 @@
       <c r="K757" s="10"/>
       <c r="L757" s="10"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row r="758" spans="1:12" ht="15.75" customHeight="1">
       <c r="A758" s="10"/>
       <c r="B758" s="10"/>
       <c r="C758" s="7"/>
@@ -14079,7 +14114,7 @@
       <c r="K758" s="10"/>
       <c r="L758" s="10"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row r="759" spans="1:12" ht="15.75" customHeight="1">
       <c r="A759" s="10"/>
       <c r="B759" s="10"/>
       <c r="C759" s="7"/>
@@ -14093,7 +14128,7 @@
       <c r="K759" s="10"/>
       <c r="L759" s="10"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row r="760" spans="1:12" ht="15.75" customHeight="1">
       <c r="A760" s="10"/>
       <c r="B760" s="10"/>
       <c r="C760" s="7"/>
@@ -14107,7 +14142,7 @@
       <c r="K760" s="10"/>
       <c r="L760" s="10"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row r="761" spans="1:12" ht="15.75" customHeight="1">
       <c r="A761" s="10"/>
       <c r="B761" s="10"/>
       <c r="C761" s="7"/>
@@ -14121,7 +14156,7 @@
       <c r="K761" s="10"/>
       <c r="L761" s="10"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row r="762" spans="1:12" ht="15.75" customHeight="1">
       <c r="A762" s="10"/>
       <c r="B762" s="10"/>
       <c r="C762" s="7"/>
@@ -14135,7 +14170,7 @@
       <c r="K762" s="10"/>
       <c r="L762" s="10"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row r="763" spans="1:12" ht="15.75" customHeight="1">
       <c r="A763" s="10"/>
       <c r="B763" s="10"/>
       <c r="C763" s="7"/>
@@ -14149,7 +14184,7 @@
       <c r="K763" s="10"/>
       <c r="L763" s="10"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row r="764" spans="1:12" ht="15.75" customHeight="1">
       <c r="A764" s="10"/>
       <c r="B764" s="10"/>
       <c r="C764" s="7"/>
@@ -14163,7 +14198,7 @@
       <c r="K764" s="10"/>
       <c r="L764" s="10"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row r="765" spans="1:12" ht="15.75" customHeight="1">
       <c r="A765" s="10"/>
       <c r="B765" s="10"/>
       <c r="C765" s="7"/>
@@ -14177,7 +14212,7 @@
       <c r="K765" s="10"/>
       <c r="L765" s="10"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row r="766" spans="1:12" ht="15.75" customHeight="1">
       <c r="A766" s="10"/>
       <c r="B766" s="10"/>
       <c r="C766" s="7"/>
@@ -14191,7 +14226,7 @@
       <c r="K766" s="10"/>
       <c r="L766" s="10"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row r="767" spans="1:12" ht="15.75" customHeight="1">
       <c r="A767" s="10"/>
       <c r="B767" s="10"/>
       <c r="C767" s="7"/>
@@ -14205,7 +14240,7 @@
       <c r="K767" s="10"/>
       <c r="L767" s="10"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row r="768" spans="1:12" ht="15.75" customHeight="1">
       <c r="A768" s="10"/>
       <c r="B768" s="10"/>
       <c r="C768" s="7"/>
@@ -14219,7 +14254,7 @@
       <c r="K768" s="10"/>
       <c r="L768" s="10"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row r="769" spans="1:12" ht="15.75" customHeight="1">
       <c r="A769" s="10"/>
       <c r="B769" s="10"/>
       <c r="C769" s="7"/>
@@ -14233,7 +14268,7 @@
       <c r="K769" s="10"/>
       <c r="L769" s="10"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row r="770" spans="1:12" ht="15.75" customHeight="1">
       <c r="A770" s="10"/>
       <c r="B770" s="10"/>
       <c r="C770" s="7"/>
@@ -14247,7 +14282,7 @@
       <c r="K770" s="10"/>
       <c r="L770" s="10"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row r="771" spans="1:12" ht="15.75" customHeight="1">
       <c r="A771" s="10"/>
       <c r="B771" s="10"/>
       <c r="C771" s="7"/>
@@ -14261,7 +14296,7 @@
       <c r="K771" s="10"/>
       <c r="L771" s="10"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row r="772" spans="1:12" ht="15.75" customHeight="1">
       <c r="A772" s="10"/>
       <c r="B772" s="10"/>
       <c r="C772" s="7"/>
@@ -14275,7 +14310,7 @@
       <c r="K772" s="10"/>
       <c r="L772" s="10"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row r="773" spans="1:12" ht="15.75" customHeight="1">
       <c r="A773" s="10"/>
       <c r="B773" s="10"/>
       <c r="C773" s="7"/>
@@ -14289,7 +14324,7 @@
       <c r="K773" s="10"/>
       <c r="L773" s="10"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row r="774" spans="1:12" ht="15.75" customHeight="1">
       <c r="A774" s="10"/>
       <c r="B774" s="10"/>
       <c r="C774" s="7"/>
@@ -14303,7 +14338,7 @@
       <c r="K774" s="10"/>
       <c r="L774" s="10"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row r="775" spans="1:12" ht="15.75" customHeight="1">
       <c r="A775" s="10"/>
       <c r="B775" s="10"/>
       <c r="C775" s="7"/>
@@ -14317,7 +14352,7 @@
       <c r="K775" s="10"/>
       <c r="L775" s="10"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row r="776" spans="1:12" ht="15.75" customHeight="1">
       <c r="A776" s="10"/>
       <c r="B776" s="10"/>
       <c r="C776" s="7"/>
@@ -14331,7 +14366,7 @@
       <c r="K776" s="10"/>
       <c r="L776" s="10"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row r="777" spans="1:12" ht="15.75" customHeight="1">
       <c r="A777" s="10"/>
       <c r="B777" s="10"/>
       <c r="C777" s="7"/>
@@ -14345,7 +14380,7 @@
       <c r="K777" s="10"/>
       <c r="L777" s="10"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row r="778" spans="1:12" ht="15.75" customHeight="1">
       <c r="A778" s="10"/>
       <c r="B778" s="10"/>
       <c r="C778" s="7"/>
@@ -14359,7 +14394,7 @@
       <c r="K778" s="10"/>
       <c r="L778" s="10"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row r="779" spans="1:12" ht="15.75" customHeight="1">
       <c r="A779" s="10"/>
       <c r="B779" s="10"/>
       <c r="C779" s="7"/>
@@ -14373,7 +14408,7 @@
       <c r="K779" s="10"/>
       <c r="L779" s="10"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row r="780" spans="1:12" ht="15.75" customHeight="1">
       <c r="A780" s="10"/>
       <c r="B780" s="10"/>
       <c r="C780" s="7"/>
@@ -14387,7 +14422,7 @@
       <c r="K780" s="10"/>
       <c r="L780" s="10"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row r="781" spans="1:12" ht="15.75" customHeight="1">
       <c r="A781" s="10"/>
       <c r="B781" s="10"/>
       <c r="C781" s="7"/>
@@ -14401,7 +14436,7 @@
       <c r="K781" s="10"/>
       <c r="L781" s="10"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row r="782" spans="1:12" ht="15.75" customHeight="1">
       <c r="A782" s="10"/>
       <c r="B782" s="10"/>
       <c r="C782" s="7"/>
@@ -14415,7 +14450,7 @@
       <c r="K782" s="10"/>
       <c r="L782" s="10"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row r="783" spans="1:12" ht="15.75" customHeight="1">
       <c r="A783" s="10"/>
       <c r="B783" s="10"/>
       <c r="C783" s="7"/>
@@ -14429,7 +14464,7 @@
       <c r="K783" s="10"/>
       <c r="L783" s="10"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row r="784" spans="1:12" ht="15.75" customHeight="1">
       <c r="A784" s="10"/>
       <c r="B784" s="10"/>
       <c r="C784" s="7"/>
@@ -14443,7 +14478,7 @@
       <c r="K784" s="10"/>
       <c r="L784" s="10"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row r="785" spans="1:12" ht="15.75" customHeight="1">
       <c r="A785" s="10"/>
       <c r="B785" s="10"/>
       <c r="C785" s="7"/>
@@ -14457,7 +14492,7 @@
       <c r="K785" s="10"/>
       <c r="L785" s="10"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row r="786" spans="1:12" ht="15.75" customHeight="1">
       <c r="A786" s="10"/>
       <c r="B786" s="10"/>
       <c r="C786" s="7"/>
@@ -14471,7 +14506,7 @@
       <c r="K786" s="10"/>
       <c r="L786" s="10"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row r="787" spans="1:12" ht="15.75" customHeight="1">
       <c r="A787" s="10"/>
       <c r="B787" s="10"/>
       <c r="C787" s="7"/>
@@ -14485,7 +14520,7 @@
       <c r="K787" s="10"/>
       <c r="L787" s="10"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row r="788" spans="1:12" ht="15.75" customHeight="1">
       <c r="A788" s="10"/>
       <c r="B788" s="10"/>
       <c r="C788" s="7"/>
@@ -14499,7 +14534,7 @@
       <c r="K788" s="10"/>
       <c r="L788" s="10"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row r="789" spans="1:12" ht="15.75" customHeight="1">
       <c r="A789" s="10"/>
       <c r="B789" s="10"/>
       <c r="C789" s="7"/>
@@ -14513,7 +14548,7 @@
       <c r="K789" s="10"/>
       <c r="L789" s="10"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row r="790" spans="1:12" ht="15.75" customHeight="1">
       <c r="A790" s="10"/>
       <c r="B790" s="10"/>
       <c r="C790" s="7"/>
@@ -14527,7 +14562,7 @@
       <c r="K790" s="10"/>
       <c r="L790" s="10"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row r="791" spans="1:12" ht="15.75" customHeight="1">
       <c r="A791" s="10"/>
       <c r="B791" s="10"/>
       <c r="C791" s="7"/>
@@ -14541,7 +14576,7 @@
       <c r="K791" s="10"/>
       <c r="L791" s="10"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row r="792" spans="1:12" ht="15.75" customHeight="1">
       <c r="A792" s="10"/>
       <c r="B792" s="10"/>
       <c r="C792" s="7"/>
@@ -14555,7 +14590,7 @@
       <c r="K792" s="10"/>
       <c r="L792" s="10"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row r="793" spans="1:12" ht="15.75" customHeight="1">
       <c r="A793" s="10"/>
       <c r="B793" s="10"/>
       <c r="C793" s="7"/>
@@ -14569,7 +14604,7 @@
       <c r="K793" s="10"/>
       <c r="L793" s="10"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row r="794" spans="1:12" ht="15.75" customHeight="1">
       <c r="A794" s="10"/>
       <c r="B794" s="10"/>
       <c r="C794" s="7"/>
@@ -14583,7 +14618,7 @@
       <c r="K794" s="10"/>
       <c r="L794" s="10"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row r="795" spans="1:12" ht="15.75" customHeight="1">
       <c r="A795" s="10"/>
       <c r="B795" s="10"/>
       <c r="C795" s="7"/>
@@ -14597,7 +14632,7 @@
       <c r="K795" s="10"/>
       <c r="L795" s="10"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row r="796" spans="1:12" ht="15.75" customHeight="1">
       <c r="A796" s="10"/>
       <c r="B796" s="10"/>
       <c r="C796" s="7"/>
@@ -14611,7 +14646,7 @@
       <c r="K796" s="10"/>
       <c r="L796" s="10"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row r="797" spans="1:12" ht="15.75" customHeight="1">
       <c r="A797" s="10"/>
       <c r="B797" s="10"/>
       <c r="C797" s="7"/>
@@ -14625,7 +14660,7 @@
       <c r="K797" s="10"/>
       <c r="L797" s="10"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row r="798" spans="1:12" ht="15.75" customHeight="1">
       <c r="A798" s="10"/>
       <c r="B798" s="10"/>
       <c r="C798" s="7"/>
@@ -14639,7 +14674,7 @@
       <c r="K798" s="10"/>
       <c r="L798" s="10"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row r="799" spans="1:12" ht="15.75" customHeight="1">
       <c r="A799" s="10"/>
       <c r="B799" s="10"/>
       <c r="C799" s="7"/>
@@ -14653,7 +14688,7 @@
       <c r="K799" s="10"/>
       <c r="L799" s="10"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row r="800" spans="1:12" ht="15.75" customHeight="1">
       <c r="A800" s="10"/>
       <c r="B800" s="10"/>
       <c r="C800" s="7"/>
@@ -14667,7 +14702,7 @@
       <c r="K800" s="10"/>
       <c r="L800" s="10"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row r="801" spans="1:12" ht="15.75" customHeight="1">
       <c r="A801" s="10"/>
       <c r="B801" s="10"/>
       <c r="C801" s="7"/>
@@ -14681,7 +14716,7 @@
       <c r="K801" s="10"/>
       <c r="L801" s="10"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row r="802" spans="1:12" ht="15.75" customHeight="1">
       <c r="A802" s="10"/>
       <c r="B802" s="10"/>
       <c r="C802" s="7"/>
@@ -14695,7 +14730,7 @@
       <c r="K802" s="10"/>
       <c r="L802" s="10"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row r="803" spans="1:12" ht="15.75" customHeight="1">
       <c r="A803" s="10"/>
       <c r="B803" s="10"/>
       <c r="C803" s="7"/>
@@ -14709,7 +14744,7 @@
       <c r="K803" s="10"/>
       <c r="L803" s="10"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row r="804" spans="1:12" ht="15.75" customHeight="1">
       <c r="A804" s="10"/>
       <c r="B804" s="10"/>
       <c r="C804" s="7"/>
@@ -14723,7 +14758,7 @@
       <c r="K804" s="10"/>
       <c r="L804" s="10"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row r="805" spans="1:12" ht="15.75" customHeight="1">
       <c r="A805" s="10"/>
       <c r="B805" s="10"/>
       <c r="C805" s="7"/>
@@ -14737,7 +14772,7 @@
       <c r="K805" s="10"/>
       <c r="L805" s="10"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row r="806" spans="1:12" ht="15.75" customHeight="1">
       <c r="A806" s="10"/>
       <c r="B806" s="10"/>
       <c r="C806" s="7"/>
@@ -14751,7 +14786,7 @@
       <c r="K806" s="10"/>
       <c r="L806" s="10"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row r="807" spans="1:12" ht="15.75" customHeight="1">
       <c r="A807" s="10"/>
       <c r="B807" s="10"/>
       <c r="C807" s="7"/>
@@ -14765,7 +14800,7 @@
       <c r="K807" s="10"/>
       <c r="L807" s="10"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row r="808" spans="1:12" ht="15.75" customHeight="1">
       <c r="A808" s="10"/>
       <c r="B808" s="10"/>
       <c r="C808" s="7"/>
@@ -14779,7 +14814,7 @@
       <c r="K808" s="10"/>
       <c r="L808" s="10"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row r="809" spans="1:12" ht="15.75" customHeight="1">
       <c r="A809" s="10"/>
       <c r="B809" s="10"/>
       <c r="C809" s="7"/>
@@ -14793,7 +14828,7 @@
       <c r="K809" s="10"/>
       <c r="L809" s="10"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row r="810" spans="1:12" ht="15.75" customHeight="1">
       <c r="A810" s="10"/>
       <c r="B810" s="10"/>
       <c r="C810" s="7"/>
@@ -14807,7 +14842,7 @@
       <c r="K810" s="10"/>
       <c r="L810" s="10"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row r="811" spans="1:12" ht="15.75" customHeight="1">
       <c r="A811" s="10"/>
       <c r="B811" s="10"/>
       <c r="C811" s="7"/>
@@ -14821,7 +14856,7 @@
       <c r="K811" s="10"/>
       <c r="L811" s="10"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row r="812" spans="1:12" ht="15.75" customHeight="1">
       <c r="A812" s="10"/>
       <c r="B812" s="10"/>
       <c r="C812" s="7"/>
@@ -14835,7 +14870,7 @@
       <c r="K812" s="10"/>
       <c r="L812" s="10"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row r="813" spans="1:12" ht="15.75" customHeight="1">
       <c r="A813" s="10"/>
       <c r="B813" s="10"/>
       <c r="C813" s="7"/>
@@ -14849,7 +14884,7 @@
       <c r="K813" s="10"/>
       <c r="L813" s="10"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row r="814" spans="1:12" ht="15.75" customHeight="1">
       <c r="A814" s="10"/>
       <c r="B814" s="10"/>
       <c r="C814" s="7"/>
@@ -14863,7 +14898,7 @@
       <c r="K814" s="10"/>
       <c r="L814" s="10"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row r="815" spans="1:12" ht="15.75" customHeight="1">
       <c r="A815" s="10"/>
       <c r="B815" s="10"/>
       <c r="C815" s="7"/>
@@ -14877,7 +14912,7 @@
       <c r="K815" s="10"/>
       <c r="L815" s="10"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row r="816" spans="1:12" ht="15.75" customHeight="1">
       <c r="A816" s="10"/>
       <c r="B816" s="10"/>
       <c r="C816" s="7"/>
@@ -14891,7 +14926,7 @@
       <c r="K816" s="10"/>
       <c r="L816" s="10"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row r="817" spans="1:12" ht="15.75" customHeight="1">
       <c r="A817" s="10"/>
       <c r="B817" s="10"/>
       <c r="C817" s="7"/>
@@ -14905,7 +14940,7 @@
       <c r="K817" s="10"/>
       <c r="L817" s="10"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row r="818" spans="1:12" ht="15.75" customHeight="1">
       <c r="A818" s="10"/>
       <c r="B818" s="10"/>
       <c r="C818" s="7"/>
@@ -14919,7 +14954,7 @@
       <c r="K818" s="10"/>
       <c r="L818" s="10"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row r="819" spans="1:12" ht="15.75" customHeight="1">
       <c r="A819" s="10"/>
       <c r="B819" s="10"/>
       <c r="C819" s="7"/>
@@ -14933,7 +14968,7 @@
       <c r="K819" s="10"/>
       <c r="L819" s="10"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row r="820" spans="1:12" ht="15.75" customHeight="1">
       <c r="A820" s="10"/>
       <c r="B820" s="10"/>
       <c r="C820" s="7"/>
@@ -14947,7 +14982,7 @@
       <c r="K820" s="10"/>
       <c r="L820" s="10"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row r="821" spans="1:12" ht="15.75" customHeight="1">
       <c r="A821" s="10"/>
       <c r="B821" s="10"/>
       <c r="C821" s="7"/>
@@ -14961,7 +14996,7 @@
       <c r="K821" s="10"/>
       <c r="L821" s="10"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row r="822" spans="1:12" ht="15.75" customHeight="1">
       <c r="A822" s="10"/>
       <c r="B822" s="10"/>
       <c r="C822" s="7"/>
@@ -14975,7 +15010,7 @@
       <c r="K822" s="10"/>
       <c r="L822" s="10"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row r="823" spans="1:12" ht="15.75" customHeight="1">
       <c r="A823" s="10"/>
       <c r="B823" s="10"/>
       <c r="C823" s="7"/>
@@ -14989,7 +15024,7 @@
       <c r="K823" s="10"/>
       <c r="L823" s="10"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row r="824" spans="1:12" ht="15.75" customHeight="1">
       <c r="A824" s="10"/>
       <c r="B824" s="10"/>
       <c r="C824" s="7"/>
@@ -15003,7 +15038,7 @@
       <c r="K824" s="10"/>
       <c r="L824" s="10"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row r="825" spans="1:12" ht="15.75" customHeight="1">
       <c r="A825" s="10"/>
       <c r="B825" s="10"/>
       <c r="C825" s="7"/>
@@ -15017,7 +15052,7 @@
       <c r="K825" s="10"/>
       <c r="L825" s="10"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row r="826" spans="1:12" ht="15.75" customHeight="1">
       <c r="A826" s="10"/>
       <c r="B826" s="10"/>
       <c r="C826" s="7"/>
@@ -15031,7 +15066,7 @@
       <c r="K826" s="10"/>
       <c r="L826" s="10"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row r="827" spans="1:12" ht="15.75" customHeight="1">
       <c r="A827" s="10"/>
       <c r="B827" s="10"/>
       <c r="C827" s="7"/>
@@ -15045,7 +15080,7 @@
       <c r="K827" s="10"/>
       <c r="L827" s="10"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row r="828" spans="1:12" ht="15.75" customHeight="1">
       <c r="A828" s="10"/>
       <c r="B828" s="10"/>
       <c r="C828" s="7"/>
@@ -15059,7 +15094,7 @@
       <c r="K828" s="10"/>
       <c r="L828" s="10"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row r="829" spans="1:12" ht="15.75" customHeight="1">
       <c r="A829" s="10"/>
       <c r="B829" s="10"/>
       <c r="C829" s="7"/>
@@ -15073,7 +15108,7 @@
       <c r="K829" s="10"/>
       <c r="L829" s="10"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row r="830" spans="1:12" ht="15.75" customHeight="1">
       <c r="A830" s="10"/>
       <c r="B830" s="10"/>
       <c r="C830" s="7"/>
@@ -15087,7 +15122,7 @@
       <c r="K830" s="10"/>
       <c r="L830" s="10"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row r="831" spans="1:12" ht="15.75" customHeight="1">
       <c r="A831" s="10"/>
       <c r="B831" s="10"/>
       <c r="C831" s="7"/>
@@ -15101,7 +15136,7 @@
       <c r="K831" s="10"/>
       <c r="L831" s="10"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row r="832" spans="1:12" ht="15.75" customHeight="1">
       <c r="A832" s="10"/>
       <c r="B832" s="10"/>
       <c r="C832" s="7"/>
@@ -15115,7 +15150,7 @@
       <c r="K832" s="10"/>
       <c r="L832" s="10"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row r="833" spans="1:12" ht="15.75" customHeight="1">
       <c r="A833" s="10"/>
       <c r="B833" s="10"/>
       <c r="C833" s="7"/>
@@ -15129,7 +15164,7 @@
       <c r="K833" s="10"/>
       <c r="L833" s="10"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row r="834" spans="1:12" ht="15.75" customHeight="1">
       <c r="A834" s="10"/>
       <c r="B834" s="10"/>
       <c r="C834" s="7"/>
@@ -15143,7 +15178,7 @@
       <c r="K834" s="10"/>
       <c r="L834" s="10"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row r="835" spans="1:12" ht="15.75" customHeight="1">
       <c r="A835" s="10"/>
       <c r="B835" s="10"/>
       <c r="C835" s="7"/>
@@ -15157,7 +15192,7 @@
       <c r="K835" s="10"/>
       <c r="L835" s="10"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row r="836" spans="1:12" ht="15.75" customHeight="1">
       <c r="A836" s="10"/>
       <c r="B836" s="10"/>
       <c r="C836" s="7"/>
@@ -15171,7 +15206,7 @@
       <c r="K836" s="10"/>
       <c r="L836" s="10"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row r="837" spans="1:12" ht="15.75" customHeight="1">
       <c r="A837" s="10"/>
       <c r="B837" s="10"/>
       <c r="C837" s="7"/>
@@ -15185,7 +15220,7 @@
       <c r="K837" s="10"/>
       <c r="L837" s="10"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row r="838" spans="1:12" ht="15.75" customHeight="1">
       <c r="A838" s="10"/>
       <c r="B838" s="10"/>
       <c r="C838" s="7"/>
@@ -15199,7 +15234,7 @@
       <c r="K838" s="10"/>
       <c r="L838" s="10"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row r="839" spans="1:12" ht="15.75" customHeight="1">
       <c r="A839" s="10"/>
       <c r="B839" s="10"/>
       <c r="C839" s="7"/>
@@ -15213,7 +15248,7 @@
       <c r="K839" s="10"/>
       <c r="L839" s="10"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row r="840" spans="1:12" ht="15.75" customHeight="1">
       <c r="A840" s="10"/>
       <c r="B840" s="10"/>
       <c r="C840" s="7"/>
@@ -15227,7 +15262,7 @@
       <c r="K840" s="10"/>
       <c r="L840" s="10"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row r="841" spans="1:12" ht="15.75" customHeight="1">
       <c r="A841" s="10"/>
       <c r="B841" s="10"/>
       <c r="C841" s="7"/>
@@ -15241,7 +15276,7 @@
       <c r="K841" s="10"/>
       <c r="L841" s="10"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row r="842" spans="1:12" ht="15.75" customHeight="1">
       <c r="A842" s="10"/>
       <c r="B842" s="10"/>
       <c r="C842" s="7"/>
@@ -15255,7 +15290,7 @@
       <c r="K842" s="10"/>
       <c r="L842" s="10"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row r="843" spans="1:12" ht="15.75" customHeight="1">
       <c r="A843" s="10"/>
       <c r="B843" s="10"/>
       <c r="C843" s="7"/>
@@ -15269,7 +15304,7 @@
       <c r="K843" s="10"/>
       <c r="L843" s="10"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row r="844" spans="1:12" ht="15.75" customHeight="1">
       <c r="A844" s="10"/>
       <c r="B844" s="10"/>
       <c r="C844" s="7"/>
@@ -15283,7 +15318,7 @@
       <c r="K844" s="10"/>
       <c r="L844" s="10"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row r="845" spans="1:12" ht="15.75" customHeight="1">
       <c r="A845" s="10"/>
       <c r="B845" s="10"/>
       <c r="C845" s="7"/>
@@ -15297,7 +15332,7 @@
       <c r="K845" s="10"/>
       <c r="L845" s="10"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row r="846" spans="1:12" ht="15.75" customHeight="1">
       <c r="A846" s="10"/>
       <c r="B846" s="10"/>
       <c r="C846" s="7"/>
@@ -15311,7 +15346,7 @@
       <c r="K846" s="10"/>
       <c r="L846" s="10"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row r="847" spans="1:12" ht="15.75" customHeight="1">
       <c r="A847" s="10"/>
       <c r="B847" s="10"/>
       <c r="C847" s="7"/>
@@ -15325,7 +15360,7 @@
       <c r="K847" s="10"/>
       <c r="L847" s="10"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row r="848" spans="1:12" ht="15.75" customHeight="1">
       <c r="A848" s="10"/>
       <c r="B848" s="10"/>
       <c r="C848" s="7"/>
@@ -15339,7 +15374,7 @@
       <c r="K848" s="10"/>
       <c r="L848" s="10"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row r="849" spans="1:12" ht="15.75" customHeight="1">
       <c r="A849" s="10"/>
       <c r="B849" s="10"/>
       <c r="C849" s="7"/>
@@ -15353,7 +15388,7 @@
       <c r="K849" s="10"/>
       <c r="L849" s="10"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row r="850" spans="1:12" ht="15.75" customHeight="1">
       <c r="A850" s="10"/>
       <c r="B850" s="10"/>
       <c r="C850" s="7"/>
@@ -15367,7 +15402,7 @@
       <c r="K850" s="10"/>
       <c r="L850" s="10"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row r="851" spans="1:12" ht="15.75" customHeight="1">
       <c r="A851" s="10"/>
       <c r="B851" s="10"/>
       <c r="C851" s="7"/>
@@ -15381,7 +15416,7 @@
       <c r="K851" s="10"/>
       <c r="L851" s="10"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row r="852" spans="1:12" ht="15.75" customHeight="1">
       <c r="A852" s="10"/>
       <c r="B852" s="10"/>
       <c r="C852" s="7"/>
@@ -15395,7 +15430,7 @@
       <c r="K852" s="10"/>
       <c r="L852" s="10"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row r="853" spans="1:12" ht="15.75" customHeight="1">
       <c r="A853" s="10"/>
       <c r="B853" s="10"/>
       <c r="C853" s="7"/>
@@ -15409,7 +15444,7 @@
       <c r="K853" s="10"/>
       <c r="L853" s="10"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row r="854" spans="1:12" ht="15.75" customHeight="1">
       <c r="A854" s="10"/>
       <c r="B854" s="10"/>
       <c r="C854" s="7"/>
@@ -15423,7 +15458,7 @@
       <c r="K854" s="10"/>
       <c r="L854" s="10"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row r="855" spans="1:12" ht="15.75" customHeight="1">
       <c r="A855" s="10"/>
       <c r="B855" s="10"/>
       <c r="C855" s="7"/>
@@ -15437,7 +15472,7 @@
       <c r="K855" s="10"/>
       <c r="L855" s="10"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row r="856" spans="1:12" ht="15.75" customHeight="1">
       <c r="A856" s="10"/>
       <c r="B856" s="10"/>
       <c r="C856" s="7"/>
@@ -15451,7 +15486,7 @@
       <c r="K856" s="10"/>
       <c r="L856" s="10"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row r="857" spans="1:12" ht="15.75" customHeight="1">
       <c r="A857" s="10"/>
       <c r="B857" s="10"/>
       <c r="C857" s="7"/>
@@ -15465,7 +15500,7 @@
       <c r="K857" s="10"/>
       <c r="L857" s="10"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row r="858" spans="1:12" ht="15.75" customHeight="1">
       <c r="A858" s="10"/>
       <c r="B858" s="10"/>
       <c r="C858" s="7"/>
@@ -15479,7 +15514,7 @@
       <c r="K858" s="10"/>
       <c r="L858" s="10"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row r="859" spans="1:12" ht="15.75" customHeight="1">
       <c r="A859" s="10"/>
       <c r="B859" s="10"/>
       <c r="C859" s="7"/>
@@ -15493,7 +15528,7 @@
       <c r="K859" s="10"/>
       <c r="L859" s="10"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row r="860" spans="1:12" ht="15.75" customHeight="1">
       <c r="A860" s="10"/>
       <c r="B860" s="10"/>
       <c r="C860" s="7"/>
@@ -15507,7 +15542,7 @@
       <c r="K860" s="10"/>
       <c r="L860" s="10"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row r="861" spans="1:12" ht="15.75" customHeight="1">
       <c r="A861" s="10"/>
       <c r="B861" s="10"/>
       <c r="C861" s="7"/>
@@ -15521,7 +15556,7 @@
       <c r="K861" s="10"/>
       <c r="L861" s="10"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row r="862" spans="1:12" ht="15.75" customHeight="1">
       <c r="A862" s="10"/>
       <c r="B862" s="10"/>
       <c r="C862" s="7"/>
@@ -15535,7 +15570,7 @@
       <c r="K862" s="10"/>
       <c r="L862" s="10"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row r="863" spans="1:12" ht="15.75" customHeight="1">
       <c r="A863" s="10"/>
       <c r="B863" s="10"/>
       <c r="C863" s="7"/>
@@ -15549,7 +15584,7 @@
       <c r="K863" s="10"/>
       <c r="L863" s="10"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row r="864" spans="1:12" ht="15.75" customHeight="1">
       <c r="A864" s="10"/>
       <c r="B864" s="10"/>
       <c r="C864" s="7"/>
@@ -15563,7 +15598,7 @@
       <c r="K864" s="10"/>
       <c r="L864" s="10"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row r="865" spans="1:12" ht="15.75" customHeight="1">
       <c r="A865" s="10"/>
       <c r="B865" s="10"/>
       <c r="C865" s="7"/>
@@ -15577,7 +15612,7 @@
       <c r="K865" s="10"/>
       <c r="L865" s="10"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row r="866" spans="1:12" ht="15.75" customHeight="1">
       <c r="A866" s="10"/>
       <c r="B866" s="10"/>
       <c r="C866" s="7"/>
@@ -15591,7 +15626,7 @@
       <c r="K866" s="10"/>
       <c r="L866" s="10"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row r="867" spans="1:12" ht="15.75" customHeight="1">
       <c r="A867" s="10"/>
       <c r="B867" s="10"/>
       <c r="C867" s="7"/>
@@ -15605,7 +15640,7 @@
       <c r="K867" s="10"/>
       <c r="L867" s="10"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row r="868" spans="1:12" ht="15.75" customHeight="1">
       <c r="A868" s="10"/>
       <c r="B868" s="10"/>
       <c r="C868" s="7"/>
@@ -15619,7 +15654,7 @@
       <c r="K868" s="10"/>
       <c r="L868" s="10"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row r="869" spans="1:12" ht="15.75" customHeight="1">
       <c r="A869" s="10"/>
       <c r="B869" s="10"/>
       <c r="C869" s="7"/>
@@ -15633,7 +15668,7 @@
       <c r="K869" s="10"/>
       <c r="L869" s="10"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row r="870" spans="1:12" ht="15.75" customHeight="1">
       <c r="A870" s="10"/>
       <c r="B870" s="10"/>
       <c r="C870" s="7"/>
@@ -15647,7 +15682,7 @@
       <c r="K870" s="10"/>
       <c r="L870" s="10"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row r="871" spans="1:12" ht="15.75" customHeight="1">
       <c r="A871" s="10"/>
       <c r="B871" s="10"/>
       <c r="C871" s="7"/>
@@ -15661,7 +15696,7 @@
       <c r="K871" s="10"/>
       <c r="L871" s="10"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row r="872" spans="1:12" ht="15.75" customHeight="1">
       <c r="A872" s="10"/>
       <c r="B872" s="10"/>
       <c r="C872" s="7"/>
@@ -15675,7 +15710,7 @@
       <c r="K872" s="10"/>
       <c r="L872" s="10"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row r="873" spans="1:12" ht="15.75" customHeight="1">
       <c r="A873" s="10"/>
       <c r="B873" s="10"/>
       <c r="C873" s="7"/>
@@ -15689,7 +15724,7 @@
       <c r="K873" s="10"/>
       <c r="L873" s="10"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row r="874" spans="1:12" ht="15.75" customHeight="1">
       <c r="A874" s="10"/>
       <c r="B874" s="10"/>
       <c r="C874" s="7"/>
@@ -15703,7 +15738,7 @@
       <c r="K874" s="10"/>
       <c r="L874" s="10"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row r="875" spans="1:12" ht="15.75" customHeight="1">
       <c r="A875" s="10"/>
       <c r="B875" s="10"/>
       <c r="C875" s="7"/>
@@ -15717,7 +15752,7 @@
       <c r="K875" s="10"/>
       <c r="L875" s="10"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row r="876" spans="1:12" ht="15.75" customHeight="1">
       <c r="A876" s="10"/>
       <c r="B876" s="10"/>
       <c r="C876" s="7"/>
@@ -15731,7 +15766,7 @@
       <c r="K876" s="10"/>
       <c r="L876" s="10"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row r="877" spans="1:12" ht="15.75" customHeight="1">
       <c r="A877" s="10"/>
       <c r="B877" s="10"/>
       <c r="C877" s="7"/>
@@ -15745,7 +15780,7 @@
       <c r="K877" s="10"/>
       <c r="L877" s="10"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row r="878" spans="1:12" ht="15.75" customHeight="1">
       <c r="A878" s="10"/>
       <c r="B878" s="10"/>
       <c r="C878" s="7"/>
@@ -15759,7 +15794,7 @@
       <c r="K878" s="10"/>
       <c r="L878" s="10"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row r="879" spans="1:12" ht="15.75" customHeight="1">
       <c r="A879" s="10"/>
       <c r="B879" s="10"/>
       <c r="C879" s="7"/>
@@ -15773,7 +15808,7 @@
       <c r="K879" s="10"/>
       <c r="L879" s="10"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row r="880" spans="1:12" ht="15.75" customHeight="1">
       <c r="A880" s="10"/>
       <c r="B880" s="10"/>
       <c r="C880" s="7"/>
@@ -15787,7 +15822,7 @@
       <c r="K880" s="10"/>
       <c r="L880" s="10"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row r="881" spans="1:12" ht="15.75" customHeight="1">
       <c r="A881" s="10"/>
       <c r="B881" s="10"/>
       <c r="C881" s="7"/>
@@ -15801,7 +15836,7 @@
       <c r="K881" s="10"/>
       <c r="L881" s="10"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row r="882" spans="1:12" ht="15.75" customHeight="1">
       <c r="A882" s="10"/>
       <c r="B882" s="10"/>
       <c r="C882" s="7"/>
@@ -15815,7 +15850,7 @@
       <c r="K882" s="10"/>
       <c r="L882" s="10"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row r="883" spans="1:12" ht="15.75" customHeight="1">
       <c r="A883" s="10"/>
       <c r="B883" s="10"/>
       <c r="C883" s="7"/>
@@ -15829,7 +15864,7 @@
       <c r="K883" s="10"/>
       <c r="L883" s="10"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row r="884" spans="1:12" ht="15.75" customHeight="1">
       <c r="A884" s="10"/>
       <c r="B884" s="10"/>
       <c r="C884" s="7"/>
@@ -15843,7 +15878,7 @@
       <c r="K884" s="10"/>
       <c r="L884" s="10"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row r="885" spans="1:12" ht="15.75" customHeight="1">
       <c r="A885" s="10"/>
       <c r="B885" s="10"/>
       <c r="C885" s="7"/>
@@ -15857,7 +15892,7 @@
       <c r="K885" s="10"/>
       <c r="L885" s="10"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row r="886" spans="1:12" ht="15.75" customHeight="1">
       <c r="A886" s="10"/>
       <c r="B886" s="10"/>
       <c r="C886" s="7"/>
@@ -15871,7 +15906,7 @@
       <c r="K886" s="10"/>
       <c r="L886" s="10"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row r="887" spans="1:12" ht="15.75" customHeight="1">
       <c r="A887" s="10"/>
       <c r="B887" s="10"/>
       <c r="C887" s="7"/>
@@ -15885,7 +15920,7 @@
       <c r="K887" s="10"/>
       <c r="L887" s="10"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row r="888" spans="1:12" ht="15.75" customHeight="1">
       <c r="A888" s="10"/>
       <c r="B888" s="10"/>
       <c r="C888" s="7"/>
@@ -15899,7 +15934,7 @@
       <c r="K888" s="10"/>
       <c r="L888" s="10"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row r="889" spans="1:12" ht="15.75" customHeight="1">
       <c r="A889" s="10"/>
       <c r="B889" s="10"/>
       <c r="C889" s="7"/>
@@ -15913,7 +15948,7 @@
       <c r="K889" s="10"/>
       <c r="L889" s="10"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row r="890" spans="1:12" ht="15.75" customHeight="1">
       <c r="A890" s="10"/>
       <c r="B890" s="10"/>
       <c r="C890" s="7"/>
@@ -15927,7 +15962,7 @@
       <c r="K890" s="10"/>
       <c r="L890" s="10"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row r="891" spans="1:12" ht="15.75" customHeight="1">
       <c r="A891" s="10"/>
       <c r="B891" s="10"/>
       <c r="C891" s="7"/>
@@ -15941,7 +15976,7 @@
       <c r="K891" s="10"/>
       <c r="L891" s="10"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row r="892" spans="1:12" ht="15.75" customHeight="1">
       <c r="A892" s="10"/>
       <c r="B892" s="10"/>
       <c r="C892" s="7"/>
@@ -15955,7 +15990,7 @@
       <c r="K892" s="10"/>
       <c r="L892" s="10"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row r="893" spans="1:12" ht="15.75" customHeight="1">
       <c r="A893" s="10"/>
       <c r="B893" s="10"/>
       <c r="C893" s="7"/>
@@ -15969,7 +16004,7 @@
       <c r="K893" s="10"/>
       <c r="L893" s="10"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row r="894" spans="1:12" ht="15.75" customHeight="1">
       <c r="A894" s="10"/>
       <c r="B894" s="10"/>
       <c r="C894" s="7"/>
@@ -15983,7 +16018,7 @@
       <c r="K894" s="10"/>
       <c r="L894" s="10"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row r="895" spans="1:12" ht="15.75" customHeight="1">
       <c r="A895" s="10"/>
       <c r="B895" s="10"/>
       <c r="C895" s="7"/>
@@ -15997,7 +16032,7 @@
       <c r="K895" s="10"/>
       <c r="L895" s="10"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row r="896" spans="1:12" ht="15.75" customHeight="1">
       <c r="A896" s="10"/>
       <c r="B896" s="10"/>
       <c r="C896" s="7"/>
@@ -16011,7 +16046,7 @@
       <c r="K896" s="10"/>
       <c r="L896" s="10"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row r="897" spans="1:12" ht="15.75" customHeight="1">
       <c r="A897" s="10"/>
       <c r="B897" s="10"/>
       <c r="C897" s="7"/>
@@ -16025,7 +16060,7 @@
       <c r="K897" s="10"/>
       <c r="L897" s="10"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row r="898" spans="1:12" ht="15.75" customHeight="1">
       <c r="A898" s="10"/>
       <c r="B898" s="10"/>
       <c r="C898" s="7"/>
@@ -16039,7 +16074,7 @@
       <c r="K898" s="10"/>
       <c r="L898" s="10"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row r="899" spans="1:12" ht="15.75" customHeight="1">
       <c r="A899" s="10"/>
       <c r="B899" s="10"/>
       <c r="C899" s="7"/>
@@ -16053,7 +16088,7 @@
       <c r="K899" s="10"/>
       <c r="L899" s="10"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row r="900" spans="1:12" ht="15.75" customHeight="1">
       <c r="A900" s="10"/>
       <c r="B900" s="10"/>
       <c r="C900" s="7"/>
@@ -16067,7 +16102,7 @@
       <c r="K900" s="10"/>
       <c r="L900" s="10"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row r="901" spans="1:12" ht="15.75" customHeight="1">
       <c r="A901" s="10"/>
       <c r="B901" s="10"/>
       <c r="C901" s="7"/>
@@ -16081,7 +16116,7 @@
       <c r="K901" s="10"/>
       <c r="L901" s="10"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row r="902" spans="1:12" ht="15.75" customHeight="1">
       <c r="A902" s="10"/>
       <c r="B902" s="10"/>
       <c r="C902" s="7"/>
@@ -16095,7 +16130,7 @@
       <c r="K902" s="10"/>
       <c r="L902" s="10"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row r="903" spans="1:12" ht="15.75" customHeight="1">
       <c r="A903" s="10"/>
       <c r="B903" s="10"/>
       <c r="C903" s="7"/>
@@ -16109,7 +16144,7 @@
       <c r="K903" s="10"/>
       <c r="L903" s="10"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row r="904" spans="1:12" ht="15.75" customHeight="1">
       <c r="A904" s="10"/>
       <c r="B904" s="10"/>
       <c r="C904" s="7"/>
@@ -16123,7 +16158,7 @@
       <c r="K904" s="10"/>
       <c r="L904" s="10"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row r="905" spans="1:12" ht="15.75" customHeight="1">
       <c r="A905" s="10"/>
       <c r="B905" s="10"/>
       <c r="C905" s="7"/>
@@ -16137,7 +16172,7 @@
       <c r="K905" s="10"/>
       <c r="L905" s="10"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row r="906" spans="1:12" ht="15.75" customHeight="1">
       <c r="A906" s="10"/>
       <c r="B906" s="10"/>
       <c r="C906" s="7"/>
@@ -16151,7 +16186,7 @@
       <c r="K906" s="10"/>
       <c r="L906" s="10"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row r="907" spans="1:12" ht="15.75" customHeight="1">
       <c r="A907" s="10"/>
       <c r="B907" s="10"/>
       <c r="C907" s="7"/>
@@ -16165,7 +16200,7 @@
       <c r="K907" s="10"/>
       <c r="L907" s="10"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row r="908" spans="1:12" ht="15.75" customHeight="1">
       <c r="A908" s="10"/>
       <c r="B908" s="10"/>
       <c r="C908" s="7"/>
@@ -16179,7 +16214,7 @@
       <c r="K908" s="10"/>
       <c r="L908" s="10"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row r="909" spans="1:12" ht="15.75" customHeight="1">
       <c r="A909" s="10"/>
       <c r="B909" s="10"/>
       <c r="C909" s="7"/>
@@ -16193,7 +16228,7 @@
       <c r="K909" s="10"/>
       <c r="L909" s="10"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row r="910" spans="1:12" ht="15.75" customHeight="1">
       <c r="A910" s="10"/>
       <c r="B910" s="10"/>
       <c r="C910" s="7"/>
@@ -16207,7 +16242,7 @@
       <c r="K910" s="10"/>
       <c r="L910" s="10"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row r="911" spans="1:12" ht="15.75" customHeight="1">
       <c r="A911" s="10"/>
       <c r="B911" s="10"/>
       <c r="C911" s="7"/>
@@ -16221,7 +16256,7 @@
       <c r="K911" s="10"/>
       <c r="L911" s="10"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row r="912" spans="1:12" ht="15.75" customHeight="1">
       <c r="A912" s="10"/>
       <c r="B912" s="10"/>
       <c r="C912" s="7"/>
@@ -16235,7 +16270,7 @@
       <c r="K912" s="10"/>
       <c r="L912" s="10"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row r="913" spans="1:12" ht="15.75" customHeight="1">
       <c r="A913" s="10"/>
       <c r="B913" s="10"/>
       <c r="C913" s="7"/>
@@ -16249,7 +16284,7 @@
       <c r="K913" s="10"/>
       <c r="L913" s="10"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row r="914" spans="1:12" ht="15.75" customHeight="1">
       <c r="A914" s="10"/>
       <c r="B914" s="10"/>
       <c r="C914" s="7"/>
@@ -16263,7 +16298,7 @@
       <c r="K914" s="10"/>
       <c r="L914" s="10"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row r="915" spans="1:12" ht="15.75" customHeight="1">
       <c r="A915" s="10"/>
       <c r="B915" s="10"/>
       <c r="C915" s="7"/>
@@ -16277,7 +16312,7 @@
       <c r="K915" s="10"/>
       <c r="L915" s="10"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row r="916" spans="1:12" ht="15.75" customHeight="1">
       <c r="A916" s="10"/>
       <c r="B916" s="10"/>
       <c r="C916" s="7"/>
@@ -16291,7 +16326,7 @@
       <c r="K916" s="10"/>
       <c r="L916" s="10"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row r="917" spans="1:12" ht="15.75" customHeight="1">
       <c r="A917" s="10"/>
       <c r="B917" s="10"/>
       <c r="C917" s="7"/>
@@ -16305,7 +16340,7 @@
       <c r="K917" s="10"/>
       <c r="L917" s="10"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row r="918" spans="1:12" ht="15.75" customHeight="1">
       <c r="A918" s="10"/>
       <c r="B918" s="10"/>
       <c r="C918" s="7"/>
@@ -16319,7 +16354,7 @@
       <c r="K918" s="10"/>
       <c r="L918" s="10"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row r="919" spans="1:12" ht="15.75" customHeight="1">
       <c r="A919" s="10"/>
       <c r="B919" s="10"/>
       <c r="C919" s="7"/>
@@ -16333,7 +16368,7 @@
       <c r="K919" s="10"/>
       <c r="L919" s="10"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row r="920" spans="1:12" ht="15.75" customHeight="1">
       <c r="A920" s="10"/>
       <c r="B920" s="10"/>
       <c r="C920" s="7"/>
@@ -16347,7 +16382,7 @@
       <c r="K920" s="10"/>
       <c r="L920" s="10"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row r="921" spans="1:12" ht="15.75" customHeight="1">
       <c r="A921" s="10"/>
       <c r="B921" s="10"/>
       <c r="C921" s="7"/>
@@ -16361,7 +16396,7 @@
       <c r="K921" s="10"/>
       <c r="L921" s="10"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row r="922" spans="1:12" ht="15.75" customHeight="1">
       <c r="A922" s="10"/>
       <c r="B922" s="10"/>
       <c r="C922" s="7"/>
@@ -16375,7 +16410,7 @@
       <c r="K922" s="10"/>
       <c r="L922" s="10"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row r="923" spans="1:12" ht="15.75" customHeight="1">
       <c r="A923" s="10"/>
       <c r="B923" s="10"/>
       <c r="C923" s="7"/>
@@ -16389,7 +16424,7 @@
       <c r="K923" s="10"/>
       <c r="L923" s="10"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row r="924" spans="1:12" ht="15.75" customHeight="1">
       <c r="A924" s="10"/>
       <c r="B924" s="10"/>
       <c r="C924" s="7"/>
@@ -16403,7 +16438,7 @@
       <c r="K924" s="10"/>
       <c r="L924" s="10"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row r="925" spans="1:12" ht="15.75" customHeight="1">
       <c r="A925" s="10"/>
       <c r="B925" s="10"/>
       <c r="C925" s="7"/>
@@ -16417,7 +16452,7 @@
       <c r="K925" s="10"/>
       <c r="L925" s="10"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row r="926" spans="1:12" ht="15.75" customHeight="1">
       <c r="A926" s="10"/>
       <c r="B926" s="10"/>
       <c r="C926" s="7"/>
@@ -16431,7 +16466,7 @@
       <c r="K926" s="10"/>
       <c r="L926" s="10"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row r="927" spans="1:12" ht="15.75" customHeight="1">
       <c r="A927" s="10"/>
       <c r="B927" s="10"/>
       <c r="C927" s="7"/>
@@ -16445,7 +16480,7 @@
       <c r="K927" s="10"/>
       <c r="L927" s="10"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" spans="1:12" ht="15.75" customHeight="1">
       <c r="A928" s="10"/>
       <c r="B928" s="10"/>
       <c r="C928" s="7"/>
@@ -16459,7 +16494,7 @@
       <c r="K928" s="10"/>
       <c r="L928" s="10"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" spans="1:12" ht="15.75" customHeight="1">
       <c r="A929" s="10"/>
       <c r="B929" s="10"/>
       <c r="C929" s="7"/>
@@ -16473,7 +16508,7 @@
       <c r="K929" s="10"/>
       <c r="L929" s="10"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" spans="1:12" ht="15.75" customHeight="1">
       <c r="A930" s="10"/>
       <c r="B930" s="10"/>
       <c r="C930" s="7"/>
@@ -16487,7 +16522,7 @@
       <c r="K930" s="10"/>
       <c r="L930" s="10"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" spans="1:12" ht="15.75" customHeight="1">
       <c r="A931" s="10"/>
       <c r="B931" s="10"/>
       <c r="C931" s="7"/>
@@ -16501,7 +16536,7 @@
       <c r="K931" s="10"/>
       <c r="L931" s="10"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" spans="1:12" ht="15.75" customHeight="1">
       <c r="A932" s="10"/>
       <c r="B932" s="10"/>
       <c r="C932" s="7"/>
@@ -16515,7 +16550,7 @@
       <c r="K932" s="10"/>
       <c r="L932" s="10"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" spans="1:12" ht="15.75" customHeight="1">
       <c r="A933" s="10"/>
       <c r="B933" s="10"/>
       <c r="C933" s="7"/>
@@ -16529,7 +16564,7 @@
       <c r="K933" s="10"/>
       <c r="L933" s="10"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" spans="1:12" ht="15.75" customHeight="1">
       <c r="A934" s="10"/>
       <c r="B934" s="10"/>
       <c r="C934" s="7"/>
@@ -16543,7 +16578,7 @@
       <c r="K934" s="10"/>
       <c r="L934" s="10"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" spans="1:12" ht="15.75" customHeight="1">
       <c r="A935" s="10"/>
       <c r="B935" s="10"/>
       <c r="C935" s="7"/>
@@ -16557,7 +16592,7 @@
       <c r="K935" s="10"/>
       <c r="L935" s="10"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" spans="1:12" ht="15.75" customHeight="1">
       <c r="A936" s="10"/>
       <c r="B936" s="10"/>
       <c r="C936" s="7"/>
@@ -16571,7 +16606,7 @@
       <c r="K936" s="10"/>
       <c r="L936" s="10"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" spans="1:12" ht="15.75" customHeight="1">
       <c r="A937" s="10"/>
       <c r="B937" s="10"/>
       <c r="C937" s="7"/>
@@ -16585,7 +16620,7 @@
       <c r="K937" s="10"/>
       <c r="L937" s="10"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" spans="1:12" ht="15.75" customHeight="1">
       <c r="A938" s="10"/>
       <c r="B938" s="10"/>
       <c r="C938" s="7"/>
@@ -16599,7 +16634,7 @@
       <c r="K938" s="10"/>
       <c r="L938" s="10"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" spans="1:12" ht="15.75" customHeight="1">
       <c r="A939" s="10"/>
       <c r="B939" s="10"/>
       <c r="C939" s="7"/>
@@ -16613,7 +16648,7 @@
       <c r="K939" s="10"/>
       <c r="L939" s="10"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" spans="1:12" ht="15.75" customHeight="1">
       <c r="A940" s="10"/>
       <c r="B940" s="10"/>
       <c r="C940" s="7"/>
@@ -16627,7 +16662,7 @@
       <c r="K940" s="10"/>
       <c r="L940" s="10"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" spans="1:12" ht="15.75" customHeight="1">
       <c r="A941" s="10"/>
       <c r="B941" s="10"/>
       <c r="C941" s="7"/>
@@ -16641,7 +16676,7 @@
       <c r="K941" s="10"/>
       <c r="L941" s="10"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" spans="1:12" ht="15.75" customHeight="1">
       <c r="A942" s="10"/>
       <c r="B942" s="10"/>
       <c r="C942" s="7"/>
@@ -16655,7 +16690,7 @@
       <c r="K942" s="10"/>
       <c r="L942" s="10"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" spans="1:12" ht="15.75" customHeight="1">
       <c r="A943" s="10"/>
       <c r="B943" s="10"/>
       <c r="C943" s="7"/>
@@ -16669,7 +16704,7 @@
       <c r="K943" s="10"/>
       <c r="L943" s="10"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" spans="1:12" ht="15.75" customHeight="1">
       <c r="A944" s="10"/>
       <c r="B944" s="10"/>
       <c r="C944" s="7"/>
@@ -16683,7 +16718,7 @@
       <c r="K944" s="10"/>
       <c r="L944" s="10"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" spans="1:12" ht="15.75" customHeight="1">
       <c r="A945" s="10"/>
       <c r="B945" s="10"/>
       <c r="C945" s="7"/>
@@ -16697,7 +16732,7 @@
       <c r="K945" s="10"/>
       <c r="L945" s="10"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" spans="1:12" ht="15.75" customHeight="1">
       <c r="A946" s="10"/>
       <c r="B946" s="10"/>
       <c r="C946" s="7"/>
@@ -16711,7 +16746,7 @@
       <c r="K946" s="10"/>
       <c r="L946" s="10"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" spans="1:12" ht="15.75" customHeight="1">
       <c r="A947" s="10"/>
       <c r="B947" s="10"/>
       <c r="C947" s="7"/>
@@ -16725,7 +16760,7 @@
       <c r="K947" s="10"/>
       <c r="L947" s="10"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" spans="1:12" ht="15.75" customHeight="1">
       <c r="A948" s="10"/>
       <c r="B948" s="10"/>
       <c r="C948" s="7"/>
@@ -16739,7 +16774,7 @@
       <c r="K948" s="10"/>
       <c r="L948" s="10"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" spans="1:12" ht="15.75" customHeight="1">
       <c r="A949" s="10"/>
       <c r="B949" s="10"/>
       <c r="C949" s="7"/>
@@ -16753,7 +16788,7 @@
       <c r="K949" s="10"/>
       <c r="L949" s="10"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" spans="1:12" ht="15.75" customHeight="1">
       <c r="A950" s="10"/>
       <c r="B950" s="10"/>
       <c r="C950" s="7"/>
@@ -16767,7 +16802,7 @@
       <c r="K950" s="10"/>
       <c r="L950" s="10"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" spans="1:12" ht="15.75" customHeight="1">
       <c r="A951" s="10"/>
       <c r="B951" s="10"/>
       <c r="C951" s="7"/>
@@ -16781,7 +16816,7 @@
       <c r="K951" s="10"/>
       <c r="L951" s="10"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" spans="1:12" ht="15.75" customHeight="1">
       <c r="A952" s="10"/>
       <c r="B952" s="10"/>
       <c r="C952" s="7"/>
@@ -16795,7 +16830,7 @@
       <c r="K952" s="10"/>
       <c r="L952" s="10"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" spans="1:12" ht="15.75" customHeight="1">
       <c r="A953" s="10"/>
       <c r="B953" s="10"/>
       <c r="C953" s="7"/>
@@ -16809,7 +16844,7 @@
       <c r="K953" s="10"/>
       <c r="L953" s="10"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" spans="1:12" ht="15.75" customHeight="1">
       <c r="A954" s="10"/>
       <c r="B954" s="10"/>
       <c r="C954" s="7"/>
@@ -16823,7 +16858,7 @@
       <c r="K954" s="10"/>
       <c r="L954" s="10"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" spans="1:12" ht="15.75" customHeight="1">
       <c r="A955" s="10"/>
       <c r="B955" s="10"/>
       <c r="C955" s="7"/>
@@ -16837,7 +16872,7 @@
       <c r="K955" s="10"/>
       <c r="L955" s="10"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" spans="1:12" ht="15.75" customHeight="1">
       <c r="A956" s="10"/>
       <c r="B956" s="10"/>
       <c r="C956" s="7"/>
@@ -16851,7 +16886,7 @@
       <c r="K956" s="10"/>
       <c r="L956" s="10"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" spans="1:12" ht="15.75" customHeight="1">
       <c r="A957" s="10"/>
       <c r="B957" s="10"/>
       <c r="C957" s="7"/>
@@ -16865,7 +16900,7 @@
       <c r="K957" s="10"/>
       <c r="L957" s="10"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" spans="1:12" ht="15.75" customHeight="1">
       <c r="A958" s="10"/>
       <c r="B958" s="10"/>
       <c r="C958" s="7"/>
@@ -16879,7 +16914,7 @@
       <c r="K958" s="10"/>
       <c r="L958" s="10"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" spans="1:12" ht="15.75" customHeight="1">
       <c r="A959" s="10"/>
       <c r="B959" s="10"/>
       <c r="C959" s="7"/>
@@ -16893,7 +16928,7 @@
       <c r="K959" s="10"/>
       <c r="L959" s="10"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" spans="1:12" ht="15.75" customHeight="1">
       <c r="A960" s="10"/>
       <c r="B960" s="10"/>
       <c r="C960" s="7"/>
@@ -16907,7 +16942,7 @@
       <c r="K960" s="10"/>
       <c r="L960" s="10"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row r="961" spans="1:12" ht="15.75" customHeight="1">
       <c r="A961" s="10"/>
       <c r="B961" s="10"/>
       <c r="C961" s="7"/>
@@ -16921,7 +16956,7 @@
       <c r="K961" s="10"/>
       <c r="L961" s="10"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row r="962" spans="1:12" ht="15.75" customHeight="1">
       <c r="A962" s="10"/>
       <c r="B962" s="10"/>
       <c r="C962" s="7"/>
@@ -16935,7 +16970,7 @@
       <c r="K962" s="10"/>
       <c r="L962" s="10"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row r="963" spans="1:12" ht="15.75" customHeight="1">
       <c r="A963" s="10"/>
       <c r="B963" s="10"/>
       <c r="C963" s="7"/>
@@ -16949,7 +16984,7 @@
       <c r="K963" s="10"/>
       <c r="L963" s="10"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row r="964" spans="1:12" ht="15.75" customHeight="1">
       <c r="A964" s="10"/>
       <c r="B964" s="10"/>
       <c r="C964" s="7"/>
@@ -16963,7 +16998,7 @@
       <c r="K964" s="10"/>
       <c r="L964" s="10"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row r="965" spans="1:12" ht="15.75" customHeight="1">
       <c r="A965" s="10"/>
       <c r="B965" s="10"/>
       <c r="C965" s="7"/>
@@ -16977,7 +17012,7 @@
       <c r="K965" s="10"/>
       <c r="L965" s="10"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row r="966" spans="1:12" ht="15.75" customHeight="1">
       <c r="A966" s="10"/>
       <c r="B966" s="10"/>
       <c r="C966" s="7"/>
@@ -16991,7 +17026,7 @@
       <c r="K966" s="10"/>
       <c r="L966" s="10"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row r="967" spans="1:12" ht="15.75" customHeight="1">
       <c r="A967" s="10"/>
       <c r="B967" s="10"/>
       <c r="C967" s="7"/>
@@ -17005,7 +17040,7 @@
       <c r="K967" s="10"/>
       <c r="L967" s="10"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row r="968" spans="1:12" ht="15.75" customHeight="1">
       <c r="A968" s="10"/>
       <c r="B968" s="10"/>
       <c r="C968" s="7"/>
@@ -17019,7 +17054,7 @@
       <c r="K968" s="10"/>
       <c r="L968" s="10"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row r="969" spans="1:12" ht="15.75" customHeight="1">
       <c r="A969" s="10"/>
       <c r="B969" s="10"/>
       <c r="C969" s="7"/>
@@ -17033,7 +17068,7 @@
       <c r="K969" s="10"/>
       <c r="L969" s="10"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row r="970" spans="1:12" ht="15.75" customHeight="1">
       <c r="A970" s="10"/>
       <c r="B970" s="10"/>
       <c r="C970" s="7"/>
@@ -17047,7 +17082,7 @@
       <c r="K970" s="10"/>
       <c r="L970" s="10"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row r="971" spans="1:12" ht="15.75" customHeight="1">
       <c r="A971" s="10"/>
       <c r="B971" s="10"/>
       <c r="C971" s="7"/>
@@ -17061,7 +17096,7 @@
       <c r="K971" s="10"/>
       <c r="L971" s="10"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row r="972" spans="1:12" ht="15.75" customHeight="1">
       <c r="A972" s="10"/>
       <c r="B972" s="10"/>
       <c r="C972" s="7"/>
@@ -17075,7 +17110,7 @@
       <c r="K972" s="10"/>
       <c r="L972" s="10"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row r="973" spans="1:12" ht="15.75" customHeight="1">
       <c r="A973" s="10"/>
       <c r="B973" s="10"/>
       <c r="C973" s="7"/>
@@ -17089,7 +17124,7 @@
       <c r="K973" s="10"/>
       <c r="L973" s="10"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row r="974" spans="1:12" ht="15.75" customHeight="1">
       <c r="A974" s="10"/>
       <c r="B974" s="10"/>
       <c r="C974" s="7"/>
@@ -17103,7 +17138,7 @@
       <c r="K974" s="10"/>
       <c r="L974" s="10"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row r="975" spans="1:12" ht="15.75" customHeight="1">
       <c r="A975" s="10"/>
       <c r="B975" s="10"/>
       <c r="C975" s="7"/>
@@ -17117,7 +17152,7 @@
       <c r="K975" s="10"/>
       <c r="L975" s="10"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row r="976" spans="1:12" ht="15.75" customHeight="1">
       <c r="A976" s="10"/>
       <c r="B976" s="10"/>
       <c r="C976" s="7"/>
@@ -17131,7 +17166,7 @@
       <c r="K976" s="10"/>
       <c r="L976" s="10"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row r="977" spans="1:12" ht="15.75" customHeight="1">
       <c r="A977" s="10"/>
       <c r="B977" s="10"/>
       <c r="C977" s="7"/>
@@ -17145,7 +17180,7 @@
       <c r="K977" s="10"/>
       <c r="L977" s="10"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row r="978" spans="1:12" ht="15.75" customHeight="1">
       <c r="A978" s="10"/>
       <c r="B978" s="10"/>
       <c r="C978" s="7"/>
@@ -17159,7 +17194,7 @@
       <c r="K978" s="10"/>
       <c r="L978" s="10"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row r="979" spans="1:12" ht="15.75" customHeight="1">
       <c r="A979" s="10"/>
       <c r="B979" s="10"/>
       <c r="C979" s="7"/>
@@ -17173,7 +17208,7 @@
       <c r="K979" s="10"/>
       <c r="L979" s="10"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row r="980" spans="1:12" ht="15.75" customHeight="1">
       <c r="A980" s="10"/>
       <c r="B980" s="10"/>
       <c r="C980" s="7"/>
@@ -17187,7 +17222,7 @@
       <c r="K980" s="10"/>
       <c r="L980" s="10"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row r="981" spans="1:12" ht="15.75" customHeight="1">
       <c r="A981" s="10"/>
       <c r="B981" s="10"/>
       <c r="C981" s="7"/>
@@ -17201,7 +17236,7 @@
       <c r="K981" s="10"/>
       <c r="L981" s="10"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row r="982" spans="1:12" ht="15.75" customHeight="1">
       <c r="A982" s="10"/>
       <c r="B982" s="10"/>
       <c r="C982" s="7"/>
@@ -17215,7 +17250,7 @@
       <c r="K982" s="10"/>
       <c r="L982" s="10"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row r="983" spans="1:12" ht="15.75" customHeight="1">
       <c r="A983" s="10"/>
       <c r="B983" s="10"/>
       <c r="C983" s="7"/>
@@ -17229,7 +17264,7 @@
       <c r="K983" s="10"/>
       <c r="L983" s="10"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row r="984" spans="1:12" ht="15.75" customHeight="1">
       <c r="A984" s="10"/>
       <c r="B984" s="10"/>
       <c r="C984" s="7"/>
@@ -17243,7 +17278,7 @@
       <c r="K984" s="10"/>
       <c r="L984" s="10"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row r="985" spans="1:12" ht="15.75" customHeight="1">
       <c r="A985" s="10"/>
       <c r="B985" s="10"/>
       <c r="C985" s="7"/>
@@ -17257,7 +17292,7 @@
       <c r="K985" s="10"/>
       <c r="L985" s="10"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row r="986" spans="1:12" ht="15.75" customHeight="1">
       <c r="A986" s="10"/>
       <c r="B986" s="10"/>
       <c r="C986" s="7"/>
@@ -17271,7 +17306,7 @@
       <c r="K986" s="10"/>
       <c r="L986" s="10"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row r="987" spans="1:12" ht="15.75" customHeight="1">
       <c r="A987" s="10"/>
       <c r="B987" s="10"/>
       <c r="C987" s="7"/>
@@ -17285,7 +17320,7 @@
       <c r="K987" s="10"/>
       <c r="L987" s="10"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row r="988" spans="1:12" ht="15.75" customHeight="1">
       <c r="A988" s="10"/>
       <c r="B988" s="10"/>
       <c r="C988" s="7"/>
@@ -17299,7 +17334,7 @@
       <c r="K988" s="10"/>
       <c r="L988" s="10"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row r="989" spans="1:12" ht="15.75" customHeight="1">
       <c r="A989" s="10"/>
       <c r="B989" s="10"/>
       <c r="C989" s="7"/>
@@ -17313,7 +17348,7 @@
       <c r="K989" s="10"/>
       <c r="L989" s="10"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row r="990" spans="1:12" ht="15.75" customHeight="1">
       <c r="A990" s="10"/>
       <c r="B990" s="10"/>
       <c r="C990" s="7"/>
@@ -17327,7 +17362,7 @@
       <c r="K990" s="10"/>
       <c r="L990" s="10"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row r="991" spans="1:12" ht="15.75" customHeight="1">
       <c r="A991" s="10"/>
       <c r="B991" s="10"/>
       <c r="C991" s="7"/>
@@ -17341,7 +17376,7 @@
       <c r="K991" s="10"/>
       <c r="L991" s="10"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row r="992" spans="1:12" ht="15.75" customHeight="1">
       <c r="A992" s="10"/>
       <c r="B992" s="10"/>
       <c r="C992" s="7"/>
@@ -17355,7 +17390,7 @@
       <c r="K992" s="10"/>
       <c r="L992" s="10"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row r="993" spans="1:12" ht="15.75" customHeight="1">
       <c r="A993" s="10"/>
       <c r="B993" s="10"/>
       <c r="C993" s="7"/>
@@ -17369,7 +17404,7 @@
       <c r="K993" s="10"/>
       <c r="L993" s="10"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row r="994" spans="1:12" ht="15.75" customHeight="1">
       <c r="A994" s="10"/>
       <c r="B994" s="10"/>
       <c r="C994" s="7"/>
@@ -17383,7 +17418,7 @@
       <c r="K994" s="10"/>
       <c r="L994" s="10"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row r="995" spans="1:12" ht="15.75" customHeight="1">
       <c r="A995" s="10"/>
       <c r="B995" s="10"/>
       <c r="C995" s="7"/>
@@ -17397,7 +17432,7 @@
       <c r="K995" s="10"/>
       <c r="L995" s="10"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row r="996" spans="1:12" ht="15.75" customHeight="1">
       <c r="A996" s="10"/>
       <c r="B996" s="10"/>
       <c r="C996" s="7"/>
@@ -17411,7 +17446,7 @@
       <c r="K996" s="10"/>
       <c r="L996" s="10"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row r="997" spans="1:12" ht="15.75" customHeight="1">
       <c r="A997" s="10"/>
       <c r="B997" s="10"/>
       <c r="C997" s="7"/>
@@ -17425,7 +17460,7 @@
       <c r="K997" s="10"/>
       <c r="L997" s="10"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row r="998" spans="1:12" ht="15.75" customHeight="1">
       <c r="A998" s="10"/>
       <c r="B998" s="10"/>
       <c r="C998" s="7"/>
@@ -17439,7 +17474,7 @@
       <c r="K998" s="10"/>
       <c r="L998" s="10"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row r="999" spans="1:12" ht="15.75" customHeight="1">
       <c r="A999" s="10"/>
       <c r="B999" s="10"/>
       <c r="C999" s="7"/>
@@ -17453,7 +17488,7 @@
       <c r="K999" s="10"/>
       <c r="L999" s="10"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" spans="1:12" ht="15.75" customHeight="1">
       <c r="A1000" s="10"/>
       <c r="B1000" s="10"/>
       <c r="C1000" s="7"/>
@@ -17468,9 +17503,7 @@
       <c r="L1000" s="10"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>